--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{977414B1-1E03-445E-9029-4301A02576F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{7590F9AE-E53B-4116-B7D9-D7BFC917E030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{227873E5-F242-4047-AF44-B4AAC863E2C1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="480">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1229,9 +1229,6 @@
     <t>822 S. Robertson Suite #200  Los Angeles CA 90035</t>
   </si>
   <si>
-    <t>Relocation Permanent</t>
-  </si>
-  <si>
     <t>John Muir Physician Network - 5860 Owens Drive</t>
   </si>
   <si>
@@ -1386,6 +1383,99 @@
   </si>
   <si>
     <t>200 N. Pacific Coast Highway, Suite 300  El Segundo CA 90245</t>
+  </si>
+  <si>
+    <t>Renewal by Andersen LLC</t>
+  </si>
+  <si>
+    <t>18700 Crenshaw Blvd  Torrance CA 90504</t>
+  </si>
+  <si>
+    <t>PayPal</t>
+  </si>
+  <si>
+    <t>2211 N. First Street  San Jose CA 95131</t>
+  </si>
+  <si>
+    <t>22982 Alcalde Drive, Suite 100  Laguna Hills CA 92653</t>
+  </si>
+  <si>
+    <t>Clarmil Manufacturing Corporation</t>
+  </si>
+  <si>
+    <t>30865 San Clemente Street  Hayward CA 94544</t>
+  </si>
+  <si>
+    <t>Arsenal Biosciences, Inc.</t>
+  </si>
+  <si>
+    <t>329 Oyster Point Blvd  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>654 N Harington Dr.  Orange CA 92868</t>
+  </si>
+  <si>
+    <t>Foundation for California Community Colleges</t>
+  </si>
+  <si>
+    <t>1102 Q Street, Suite 4800  Sacramento CA 95811</t>
+  </si>
+  <si>
+    <t>San Luis Obispo County</t>
+  </si>
+  <si>
+    <t>Ventana Grill</t>
+  </si>
+  <si>
+    <t>2575 Price Street  Pismo Beach CA 93449</t>
+  </si>
+  <si>
+    <t>OVG Hospitality</t>
+  </si>
+  <si>
+    <t>10 W. Harbor Boulevard  Ventura CA 93001</t>
+  </si>
+  <si>
+    <t>Homeless Health Care Los Angeles - Crocker Street</t>
+  </si>
+  <si>
+    <t>442 Crocker Street  Los Angeles CA 90013</t>
+  </si>
+  <si>
+    <t>Homeless Health Care Los Angeles - Maple Ave.</t>
+  </si>
+  <si>
+    <t>655 Maple Ave.  Los Angeles CA 90014</t>
+  </si>
+  <si>
+    <t>Homeless Health Care Los Angeles - 2nd Street</t>
+  </si>
+  <si>
+    <t>1282 W 2nd Street  Los Angeles CA 90026</t>
+  </si>
+  <si>
+    <t>Grain Craft, LLC</t>
+  </si>
+  <si>
+    <t>8790 Rochester Ave # B  Rancho Cucamonga CA 91730</t>
+  </si>
+  <si>
+    <t>SonTek (Xylem, Inc.)</t>
+  </si>
+  <si>
+    <t>9940 Summers Ridge Rd.  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>Eggo Company dba Kellanova</t>
+  </si>
+  <si>
+    <t>475 Eggo Way  San Jose CA 95116</t>
+  </si>
+  <si>
+    <t>Ruiz Food Products, Inc.</t>
+  </si>
+  <si>
+    <t>501 South Alta Avenue  Dinuba CA 93618</t>
   </si>
   <si>
     <r>
@@ -1407,7 +1497,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 09/02/2026
+01/01/2023 - 09/09/2026
 </t>
     </r>
     <r>
@@ -1421,40 +1511,88 @@
     </r>
   </si>
   <si>
-    <t>Renewal by Andersen LLC</t>
-  </si>
-  <si>
-    <t>18700 Crenshaw Blvd  Torrance CA 90504</t>
-  </si>
-  <si>
-    <t>PayPal</t>
-  </si>
-  <si>
-    <t>2211 N. First Street  San Jose CA 95131</t>
-  </si>
-  <si>
-    <t>22982 Alcalde Drive, Suite 100  Laguna Hills CA 92653</t>
-  </si>
-  <si>
-    <t>Clarmil Manufacturing Corporation</t>
-  </si>
-  <si>
-    <t>30865 San Clemente Street  Hayward CA 94544</t>
-  </si>
-  <si>
-    <t>Arsenal Biosciences, Inc.</t>
-  </si>
-  <si>
-    <t>329 Oyster Point Blvd  South San Francisco CA 94080</t>
-  </si>
-  <si>
-    <t>654 N Harington Dr.  Orange CA 92868</t>
-  </si>
-  <si>
-    <t>Foundation for California Community Colleges</t>
-  </si>
-  <si>
-    <t>1102 Q Street, Suite 4800  Sacramento CA 95811</t>
+    <t>Shell Catalyst &amp; Technologies</t>
+  </si>
+  <si>
+    <t>10 Mococo Road  Martinez CA 94553</t>
+  </si>
+  <si>
+    <t>Trailer Park, Inc.</t>
+  </si>
+  <si>
+    <t>6922 Hollywood Blvd, 10th Floor  Los Angeles CA 90028</t>
+  </si>
+  <si>
+    <t>University of Southern California (1042 Downey Way)</t>
+  </si>
+  <si>
+    <t>1042 Downey Way  Los Angeles CA 90089</t>
+  </si>
+  <si>
+    <t>University of Southern California (1149 S. Hill Street)</t>
+  </si>
+  <si>
+    <t>1149 S. Hill Street  Los Angeles CA 90089</t>
+  </si>
+  <si>
+    <t>University of Southern California (1150 S. Olive Street)</t>
+  </si>
+  <si>
+    <t>1150 S. Olive Street  Los Angeles CA 90015</t>
+  </si>
+  <si>
+    <t>University of Southern California (12015 E Waterfront Dr.)</t>
+  </si>
+  <si>
+    <t>12015 E Waterfront Dr.  Playa Vista CA 90094</t>
+  </si>
+  <si>
+    <t>University of Southern California (3649 McClintock Ave.)</t>
+  </si>
+  <si>
+    <t>3649 McClintock Ave.  Los Angeles CA 90089</t>
+  </si>
+  <si>
+    <t>University of Southern California (3740 McClintock Ave)</t>
+  </si>
+  <si>
+    <t>3740 McClintock Ave  Los Angeles CA 90089</t>
+  </si>
+  <si>
+    <t>University of Southern California (4676 Admiralty Way)</t>
+  </si>
+  <si>
+    <t>4676 Admiralty Way  Marina Del Rey CA 90292</t>
+  </si>
+  <si>
+    <t>University of Southern California (746 W Adams Blvd.)</t>
+  </si>
+  <si>
+    <t>746 W Adams Blvd.  Los Angeles CA 90007</t>
+  </si>
+  <si>
+    <t>University of Southern California (854 Downey Way)</t>
+  </si>
+  <si>
+    <t>854 Downey Way  Los Angeles CA 90089</t>
+  </si>
+  <si>
+    <t>University of Southern California (941 Bloom Walk)</t>
+  </si>
+  <si>
+    <t>941 Bloom Walk  Los Angeles CA 90089</t>
+  </si>
+  <si>
+    <t>Sapporo U.S.A. (1999 Citracado Parkway)</t>
+  </si>
+  <si>
+    <t>Sapporo U.S.A. (2865 Executive Place)</t>
+  </si>
+  <si>
+    <t>Sapporo U.S.A. (2005 Harmony Grove Rd)</t>
+  </si>
+  <si>
+    <t>2005 Harmony Grove Rd  Escondido CA 92029</t>
   </si>
   <si>
     <r>
@@ -1468,7 +1606,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 09/02/2026</t>
+      <t>07/01/26 to 09/09/2026</t>
     </r>
     <r>
       <rPr>
@@ -1488,7 +1626,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I194.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I218.</t>
     </r>
   </si>
 </sst>
@@ -1603,7 +1741,6 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2655,8 +2792,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I194" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I194" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I218" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I218" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -3077,7 +3214,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>10304</v>
+        <v>11435</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3086,7 +3223,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>134</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3113,7 +3250,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3122,7 +3259,7 @@
       </c>
       <c r="B8" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3145,7 +3282,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I194"/>
+  <dimension ref="A1:I218"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -3153,7 +3290,7 @@
     <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="45.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="50.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -3166,7 +3303,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>433</v>
+        <v>479</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -7218,7 +7355,7 @@
         <v>338</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>367</v>
+        <v>6</v>
       </c>
       <c r="G141" s="30">
         <v>73</v>
@@ -7708,7 +7845,7 @@
         <v>46323</v>
       </c>
       <c r="E158" s="28" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F158" s="28" t="s">
         <v>6</v>
@@ -7717,7 +7854,7 @@
         <v>1</v>
       </c>
       <c r="H158" s="30" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I158" s="32" t="s">
         <v>45</v>
@@ -7737,7 +7874,7 @@
         <v>46323</v>
       </c>
       <c r="E159" s="28" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F159" s="28" t="s">
         <v>6</v>
@@ -7746,7 +7883,7 @@
         <v>23</v>
       </c>
       <c r="H159" s="30" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I159" s="32" t="s">
         <v>45</v>
@@ -7766,7 +7903,7 @@
         <v>46323</v>
       </c>
       <c r="E160" s="28" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F160" s="28" t="s">
         <v>6</v>
@@ -7775,7 +7912,7 @@
         <v>4</v>
       </c>
       <c r="H160" s="30" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I160" s="32" t="s">
         <v>45</v>
@@ -7795,7 +7932,7 @@
         <v>46323</v>
       </c>
       <c r="E161" s="28" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F161" s="28" t="s">
         <v>6</v>
@@ -7804,7 +7941,7 @@
         <v>15</v>
       </c>
       <c r="H161" s="30" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I161" s="32" t="s">
         <v>45</v>
@@ -7824,7 +7961,7 @@
         <v>46323</v>
       </c>
       <c r="E162" s="28" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F162" s="28" t="s">
         <v>6</v>
@@ -7833,7 +7970,7 @@
         <v>2</v>
       </c>
       <c r="H162" s="30" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I162" s="32" t="s">
         <v>45</v>
@@ -7853,7 +7990,7 @@
         <v>46323</v>
       </c>
       <c r="E163" s="28" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F163" s="28" t="s">
         <v>6</v>
@@ -7862,7 +7999,7 @@
         <v>15</v>
       </c>
       <c r="H163" s="30" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I163" s="32" t="s">
         <v>45</v>
@@ -7882,7 +8019,7 @@
         <v>46323</v>
       </c>
       <c r="E164" s="28" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F164" s="28" t="s">
         <v>6</v>
@@ -7891,7 +8028,7 @@
         <v>3</v>
       </c>
       <c r="H164" s="30" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I164" s="32" t="s">
         <v>45</v>
@@ -7911,7 +8048,7 @@
         <v>46323</v>
       </c>
       <c r="E165" s="28" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F165" s="28" t="s">
         <v>6</v>
@@ -7920,7 +8057,7 @@
         <v>2</v>
       </c>
       <c r="H165" s="30" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I165" s="32" t="s">
         <v>45</v>
@@ -7940,7 +8077,7 @@
         <v>46323</v>
       </c>
       <c r="E166" s="28" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F166" s="28" t="s">
         <v>6</v>
@@ -7949,7 +8086,7 @@
         <v>1</v>
       </c>
       <c r="H166" s="30" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I166" s="32" t="s">
         <v>45</v>
@@ -7969,7 +8106,7 @@
         <v>46323</v>
       </c>
       <c r="E167" s="28" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F167" s="28" t="s">
         <v>6</v>
@@ -7978,7 +8115,7 @@
         <v>2</v>
       </c>
       <c r="H167" s="30" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I167" s="32" t="s">
         <v>45</v>
@@ -7998,7 +8135,7 @@
         <v>46323</v>
       </c>
       <c r="E168" s="28" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F168" s="28" t="s">
         <v>6</v>
@@ -8007,7 +8144,7 @@
         <v>6</v>
       </c>
       <c r="H168" s="30" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I168" s="32" t="s">
         <v>45</v>
@@ -8027,7 +8164,7 @@
         <v>46323</v>
       </c>
       <c r="E169" s="28" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F169" s="28" t="s">
         <v>6</v>
@@ -8036,7 +8173,7 @@
         <v>1</v>
       </c>
       <c r="H169" s="30" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I169" s="32" t="s">
         <v>45</v>
@@ -8056,7 +8193,7 @@
         <v>46323</v>
       </c>
       <c r="E170" s="28" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F170" s="28" t="s">
         <v>6</v>
@@ -8065,7 +8202,7 @@
         <v>1</v>
       </c>
       <c r="H170" s="30" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I170" s="32" t="s">
         <v>45</v>
@@ -8085,7 +8222,7 @@
         <v>46323</v>
       </c>
       <c r="E171" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F171" s="28" t="s">
         <v>6</v>
@@ -8094,7 +8231,7 @@
         <v>1</v>
       </c>
       <c r="H171" s="30" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I171" s="32" t="s">
         <v>45</v>
@@ -8114,7 +8251,7 @@
         <v>46323</v>
       </c>
       <c r="E172" s="28" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F172" s="28" t="s">
         <v>6</v>
@@ -8123,7 +8260,7 @@
         <v>1</v>
       </c>
       <c r="H172" s="30" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I172" s="32" t="s">
         <v>45</v>
@@ -8143,7 +8280,7 @@
         <v>46318</v>
       </c>
       <c r="E173" s="28" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F173" s="28" t="s">
         <v>6</v>
@@ -8152,7 +8289,7 @@
         <v>7</v>
       </c>
       <c r="H173" s="30" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I173" s="32" t="s">
         <v>34</v>
@@ -8172,7 +8309,7 @@
         <v>46329</v>
       </c>
       <c r="E174" s="28" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F174" s="28" t="s">
         <v>52</v>
@@ -8181,7 +8318,7 @@
         <v>51</v>
       </c>
       <c r="H174" s="30" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I174" s="32" t="s">
         <v>36</v>
@@ -8201,7 +8338,7 @@
         <v>46328</v>
       </c>
       <c r="E175" s="28" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F175" s="28" t="s">
         <v>6</v>
@@ -8210,7 +8347,7 @@
         <v>79</v>
       </c>
       <c r="H175" s="30" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I175" s="32" t="s">
         <v>45</v>
@@ -8230,7 +8367,7 @@
         <v>46328</v>
       </c>
       <c r="E176" s="28" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F176" s="28" t="s">
         <v>6</v>
@@ -8239,7 +8376,7 @@
         <v>16</v>
       </c>
       <c r="H176" s="30" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I176" s="32" t="s">
         <v>45</v>
@@ -8288,7 +8425,7 @@
         <v>46332</v>
       </c>
       <c r="E178" s="28" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F178" s="28" t="s">
         <v>52</v>
@@ -8297,7 +8434,7 @@
         <v>189</v>
       </c>
       <c r="H178" s="30" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I178" s="32" t="s">
         <v>41</v>
@@ -8317,7 +8454,7 @@
         <v>46324</v>
       </c>
       <c r="E179" s="28" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F179" s="28" t="s">
         <v>6</v>
@@ -8326,7 +8463,7 @@
         <v>23</v>
       </c>
       <c r="H179" s="30" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I179" s="32" t="s">
         <v>45</v>
@@ -8346,7 +8483,7 @@
         <v>46324</v>
       </c>
       <c r="E180" s="28" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F180" s="28" t="s">
         <v>6</v>
@@ -8355,7 +8492,7 @@
         <v>16</v>
       </c>
       <c r="H180" s="30" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I180" s="32" t="s">
         <v>45</v>
@@ -8375,7 +8512,7 @@
         <v>46324</v>
       </c>
       <c r="E181" s="28" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F181" s="28" t="s">
         <v>6</v>
@@ -8384,7 +8521,7 @@
         <v>16</v>
       </c>
       <c r="H181" s="30" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I181" s="32" t="s">
         <v>45</v>
@@ -8404,7 +8541,7 @@
         <v>46324</v>
       </c>
       <c r="E182" s="28" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F182" s="28" t="s">
         <v>6</v>
@@ -8413,7 +8550,7 @@
         <v>13</v>
       </c>
       <c r="H182" s="30" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I182" s="32" t="s">
         <v>45</v>
@@ -8433,7 +8570,7 @@
         <v>46295</v>
       </c>
       <c r="E183" s="28" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F183" s="28" t="s">
         <v>6</v>
@@ -8442,7 +8579,7 @@
         <v>28</v>
       </c>
       <c r="H183" s="30" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I183" s="32" t="s">
         <v>41</v>
@@ -8462,7 +8599,7 @@
         <v>46315</v>
       </c>
       <c r="E184" s="28" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F184" s="28" t="s">
         <v>6</v>
@@ -8471,7 +8608,7 @@
         <v>70</v>
       </c>
       <c r="H184" s="30" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I184" s="32" t="s">
         <v>41</v>
@@ -8491,7 +8628,7 @@
         <v>46372</v>
       </c>
       <c r="E185" s="28" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F185" s="28" t="s">
         <v>6</v>
@@ -8500,7 +8637,7 @@
         <v>128</v>
       </c>
       <c r="H185" s="30" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I185" s="32" t="s">
         <v>38</v>
@@ -8520,7 +8657,7 @@
         <v>46315</v>
       </c>
       <c r="E186" s="28" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F186" s="28" t="s">
         <v>6</v>
@@ -8529,7 +8666,7 @@
         <v>78</v>
       </c>
       <c r="H186" s="30" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I186" s="32" t="s">
         <v>41</v>
@@ -8549,7 +8686,7 @@
         <v>46280</v>
       </c>
       <c r="E187" s="28" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F187" s="28" t="s">
         <v>6</v>
@@ -8558,7 +8695,7 @@
         <v>738</v>
       </c>
       <c r="H187" s="30" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I187" s="32" t="s">
         <v>45</v>
@@ -8578,7 +8715,7 @@
         <v>46325</v>
       </c>
       <c r="E188" s="28" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F188" s="28" t="s">
         <v>52</v>
@@ -8587,7 +8724,7 @@
         <v>108</v>
       </c>
       <c r="H188" s="30" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I188" s="32" t="s">
         <v>34</v>
@@ -8607,7 +8744,7 @@
         <v>46324</v>
       </c>
       <c r="E189" s="28" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F189" s="28" t="s">
         <v>6</v>
@@ -8616,7 +8753,7 @@
         <v>58</v>
       </c>
       <c r="H189" s="30" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I189" s="32" t="s">
         <v>41</v>
@@ -8636,7 +8773,7 @@
         <v>46325</v>
       </c>
       <c r="E190" s="28" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F190" s="28" t="s">
         <v>6</v>
@@ -8645,7 +8782,7 @@
         <v>251</v>
       </c>
       <c r="H190" s="30" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I190" s="32" t="s">
         <v>39</v>
@@ -8665,7 +8802,7 @@
         <v>46328</v>
       </c>
       <c r="E191" s="28" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F191" s="28" t="s">
         <v>6</v>
@@ -8674,7 +8811,7 @@
         <v>153</v>
       </c>
       <c r="H191" s="30" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I191" s="32" t="s">
         <v>34</v>
@@ -8694,7 +8831,7 @@
         <v>46328</v>
       </c>
       <c r="E192" s="28" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F192" s="28" t="s">
         <v>6</v>
@@ -8703,7 +8840,7 @@
         <v>79</v>
       </c>
       <c r="H192" s="30" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I192" s="32" t="s">
         <v>34</v>
@@ -8723,7 +8860,7 @@
         <v>46328</v>
       </c>
       <c r="E193" s="28" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F193" s="28" t="s">
         <v>6</v>
@@ -8732,7 +8869,7 @@
         <v>52</v>
       </c>
       <c r="H193" s="30" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I193" s="32" t="s">
         <v>34</v>
@@ -8752,7 +8889,7 @@
         <v>46325</v>
       </c>
       <c r="E194" s="28" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F194" s="28" t="s">
         <v>6</v>
@@ -8761,10 +8898,706 @@
         <v>178</v>
       </c>
       <c r="H194" s="30" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I194" s="32" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="28" t="s">
+        <v>431</v>
+      </c>
+      <c r="B195" s="29">
+        <v>46267</v>
+      </c>
+      <c r="C195" s="29">
+        <v>46268</v>
+      </c>
+      <c r="D195" s="29">
+        <v>46283</v>
+      </c>
+      <c r="E195" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="F195" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G195" s="30">
+        <v>82</v>
+      </c>
+      <c r="H195" s="30" t="s">
+        <v>433</v>
+      </c>
+      <c r="I195" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B196" s="29">
+        <v>46268</v>
+      </c>
+      <c r="C196" s="29">
+        <v>46268</v>
+      </c>
+      <c r="D196" s="29">
+        <v>46341</v>
+      </c>
+      <c r="E196" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="F196" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G196" s="30">
+        <v>128</v>
+      </c>
+      <c r="H196" s="30" t="s">
+        <v>435</v>
+      </c>
+      <c r="I196" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B197" s="29">
+        <v>46267</v>
+      </c>
+      <c r="C197" s="29">
+        <v>46269</v>
+      </c>
+      <c r="D197" s="29">
+        <v>46329</v>
+      </c>
+      <c r="E197" s="28" t="s">
+        <v>436</v>
+      </c>
+      <c r="F197" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G197" s="30">
+        <v>117</v>
+      </c>
+      <c r="H197" s="30" t="s">
+        <v>437</v>
+      </c>
+      <c r="I197" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B198" s="29">
+        <v>46267</v>
+      </c>
+      <c r="C198" s="29">
+        <v>46269</v>
+      </c>
+      <c r="D198" s="29">
+        <v>46329</v>
+      </c>
+      <c r="E198" s="28" t="s">
+        <v>438</v>
+      </c>
+      <c r="F198" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G198" s="30">
+        <v>16</v>
+      </c>
+      <c r="H198" s="30" t="s">
+        <v>439</v>
+      </c>
+      <c r="I198" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B199" s="29">
+        <v>46267</v>
+      </c>
+      <c r="C199" s="29">
+        <v>46269</v>
+      </c>
+      <c r="D199" s="29">
+        <v>46329</v>
+      </c>
+      <c r="E199" s="28" t="s">
+        <v>440</v>
+      </c>
+      <c r="F199" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G199" s="30">
+        <v>1</v>
+      </c>
+      <c r="H199" s="30" t="s">
+        <v>441</v>
+      </c>
+      <c r="I199" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B200" s="29">
+        <v>46266</v>
+      </c>
+      <c r="C200" s="29">
+        <v>46269</v>
+      </c>
+      <c r="D200" s="29">
+        <v>46325</v>
+      </c>
+      <c r="E200" s="28" t="s">
+        <v>442</v>
+      </c>
+      <c r="F200" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G200" s="30">
+        <v>3</v>
+      </c>
+      <c r="H200" s="30" t="s">
+        <v>443</v>
+      </c>
+      <c r="I200" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B201" s="29">
+        <v>46269</v>
+      </c>
+      <c r="C201" s="29">
+        <v>46269</v>
+      </c>
+      <c r="D201" s="29">
+        <v>46332</v>
+      </c>
+      <c r="E201" s="28" t="s">
+        <v>444</v>
+      </c>
+      <c r="F201" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G201" s="30">
+        <v>36</v>
+      </c>
+      <c r="H201" s="30" t="s">
+        <v>445</v>
+      </c>
+      <c r="I201" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B202" s="29">
+        <v>46269</v>
+      </c>
+      <c r="C202" s="29">
+        <v>46269</v>
+      </c>
+      <c r="D202" s="29">
+        <v>46330</v>
+      </c>
+      <c r="E202" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="F202" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G202" s="30">
+        <v>112</v>
+      </c>
+      <c r="H202" s="30" t="s">
+        <v>447</v>
+      </c>
+      <c r="I202" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B203" s="29">
+        <v>46269</v>
+      </c>
+      <c r="C203" s="29">
+        <v>46269</v>
+      </c>
+      <c r="D203" s="29">
+        <v>46330</v>
+      </c>
+      <c r="E203" s="28" t="s">
+        <v>448</v>
+      </c>
+      <c r="F203" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G203" s="30">
+        <v>176</v>
+      </c>
+      <c r="H203" s="30" t="s">
+        <v>449</v>
+      </c>
+      <c r="I203" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B204" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C204" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D204" s="29">
+        <v>46356</v>
+      </c>
+      <c r="E204" s="28" t="s">
+        <v>451</v>
+      </c>
+      <c r="F204" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G204" s="30">
+        <v>64</v>
+      </c>
+      <c r="H204" s="30" t="s">
+        <v>452</v>
+      </c>
+      <c r="I204" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B205" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C205" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D205" s="29">
+        <v>46210</v>
+      </c>
+      <c r="E205" s="28" t="s">
+        <v>453</v>
+      </c>
+      <c r="F205" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G205" s="30">
+        <v>119</v>
+      </c>
+      <c r="H205" s="30" t="s">
+        <v>454</v>
+      </c>
+      <c r="I205" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B206" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C206" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D206" s="29">
+        <v>46330</v>
+      </c>
+      <c r="E206" s="28" t="s">
+        <v>455</v>
+      </c>
+      <c r="F206" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G206" s="30">
+        <v>7</v>
+      </c>
+      <c r="H206" s="30" t="s">
+        <v>456</v>
+      </c>
+      <c r="I206" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B207" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C207" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D207" s="29">
+        <v>46330</v>
+      </c>
+      <c r="E207" s="28" t="s">
+        <v>457</v>
+      </c>
+      <c r="F207" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G207" s="30">
+        <v>1</v>
+      </c>
+      <c r="H207" s="30" t="s">
+        <v>458</v>
+      </c>
+      <c r="I207" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B208" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C208" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D208" s="29">
+        <v>46330</v>
+      </c>
+      <c r="E208" s="28" t="s">
+        <v>459</v>
+      </c>
+      <c r="F208" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G208" s="30">
+        <v>5</v>
+      </c>
+      <c r="H208" s="30" t="s">
+        <v>460</v>
+      </c>
+      <c r="I208" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B209" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C209" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D209" s="29">
+        <v>46330</v>
+      </c>
+      <c r="E209" s="28" t="s">
+        <v>461</v>
+      </c>
+      <c r="F209" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G209" s="30">
+        <v>8</v>
+      </c>
+      <c r="H209" s="30" t="s">
+        <v>462</v>
+      </c>
+      <c r="I209" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B210" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C210" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D210" s="29">
+        <v>46330</v>
+      </c>
+      <c r="E210" s="28" t="s">
+        <v>463</v>
+      </c>
+      <c r="F210" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G210" s="30">
+        <v>21</v>
+      </c>
+      <c r="H210" s="30" t="s">
+        <v>464</v>
+      </c>
+      <c r="I210" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B211" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C211" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D211" s="29">
+        <v>46330</v>
+      </c>
+      <c r="E211" s="28" t="s">
+        <v>465</v>
+      </c>
+      <c r="F211" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G211" s="30">
+        <v>2</v>
+      </c>
+      <c r="H211" s="30" t="s">
+        <v>466</v>
+      </c>
+      <c r="I211" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B212" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C212" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D212" s="29">
+        <v>46330</v>
+      </c>
+      <c r="E212" s="28" t="s">
+        <v>467</v>
+      </c>
+      <c r="F212" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G212" s="30">
+        <v>15</v>
+      </c>
+      <c r="H212" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="I212" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B213" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C213" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D213" s="29">
+        <v>46330</v>
+      </c>
+      <c r="E213" s="28" t="s">
+        <v>469</v>
+      </c>
+      <c r="F213" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G213" s="30">
+        <v>1</v>
+      </c>
+      <c r="H213" s="30" t="s">
+        <v>470</v>
+      </c>
+      <c r="I213" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B214" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C214" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D214" s="29">
+        <v>46330</v>
+      </c>
+      <c r="E214" s="28" t="s">
+        <v>471</v>
+      </c>
+      <c r="F214" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G214" s="30">
+        <v>1</v>
+      </c>
+      <c r="H214" s="30" t="s">
+        <v>472</v>
+      </c>
+      <c r="I214" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B215" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C215" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D215" s="29">
+        <v>46330</v>
+      </c>
+      <c r="E215" s="28" t="s">
+        <v>473</v>
+      </c>
+      <c r="F215" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G215" s="30">
+        <v>4</v>
+      </c>
+      <c r="H215" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="I215" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B216" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C216" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D216" s="29">
+        <v>46339</v>
+      </c>
+      <c r="E216" s="28" t="s">
+        <v>475</v>
+      </c>
+      <c r="F216" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G216" s="30">
+        <v>200</v>
+      </c>
+      <c r="H216" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="I216" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B217" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C217" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D217" s="29">
+        <v>46339</v>
+      </c>
+      <c r="E217" s="28" t="s">
+        <v>476</v>
+      </c>
+      <c r="F217" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G217" s="30">
+        <v>6</v>
+      </c>
+      <c r="H217" s="30" t="s">
+        <v>330</v>
+      </c>
+      <c r="I217" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B218" s="29">
+        <v>46274</v>
+      </c>
+      <c r="C218" s="29">
+        <v>46274</v>
+      </c>
+      <c r="D218" s="29">
+        <v>46339</v>
+      </c>
+      <c r="E218" s="28" t="s">
+        <v>477</v>
+      </c>
+      <c r="F218" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G218" s="30">
+        <v>6</v>
+      </c>
+      <c r="H218" s="30" t="s">
+        <v>478</v>
+      </c>
+      <c r="I218" s="32" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -8781,7 +9614,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I194</xm:sqref>
+          <xm:sqref>I3:I218</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8902,7 +9735,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="E1"/>
     </row>
@@ -9317,7 +10150,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76B6A9E8-AD51-41FA-8B02-23E48CE4D608}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04742B8B-EF9C-4AD3-90FC-1E5DA2BFE8B0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -9336,7 +10169,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA7AD1B3-404A-4EEA-9271-4F03D692E459}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3BDCC9B-2188-4BA0-9B64-3D7DE26BB377}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -9344,24 +10177,24 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39B02763-705B-493C-839B-26A069D90AFA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58496AB6-41EC-40A7-B185-55DA0F0F8F77}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" contentBits="0" removed="0"/>
+  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" removed="0"/>
 </clbl:labelList>
 </file>
--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{7590F9AE-E53B-4116-B7D9-D7BFC917E030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{227873E5-F242-4047-AF44-B4AAC863E2C1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19B4AD77-A87F-4673-8195-E0F886C5D21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="488">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1478,6 +1478,90 @@
     <t>501 South Alta Avenue  Dinuba CA 93618</t>
   </si>
   <si>
+    <t>Shell Catalyst &amp; Technologies</t>
+  </si>
+  <si>
+    <t>10 Mococo Road  Martinez CA 94553</t>
+  </si>
+  <si>
+    <t>Trailer Park, Inc.</t>
+  </si>
+  <si>
+    <t>6922 Hollywood Blvd, 10th Floor  Los Angeles CA 90028</t>
+  </si>
+  <si>
+    <t>University of Southern California (1042 Downey Way)</t>
+  </si>
+  <si>
+    <t>1042 Downey Way  Los Angeles CA 90089</t>
+  </si>
+  <si>
+    <t>University of Southern California (1149 S. Hill Street)</t>
+  </si>
+  <si>
+    <t>1149 S. Hill Street  Los Angeles CA 90089</t>
+  </si>
+  <si>
+    <t>University of Southern California (1150 S. Olive Street)</t>
+  </si>
+  <si>
+    <t>1150 S. Olive Street  Los Angeles CA 90015</t>
+  </si>
+  <si>
+    <t>University of Southern California (12015 E Waterfront Dr.)</t>
+  </si>
+  <si>
+    <t>12015 E Waterfront Dr.  Playa Vista CA 90094</t>
+  </si>
+  <si>
+    <t>University of Southern California (3649 McClintock Ave.)</t>
+  </si>
+  <si>
+    <t>3649 McClintock Ave.  Los Angeles CA 90089</t>
+  </si>
+  <si>
+    <t>University of Southern California (3740 McClintock Ave)</t>
+  </si>
+  <si>
+    <t>3740 McClintock Ave  Los Angeles CA 90089</t>
+  </si>
+  <si>
+    <t>University of Southern California (4676 Admiralty Way)</t>
+  </si>
+  <si>
+    <t>4676 Admiralty Way  Marina Del Rey CA 90292</t>
+  </si>
+  <si>
+    <t>University of Southern California (746 W Adams Blvd.)</t>
+  </si>
+  <si>
+    <t>746 W Adams Blvd.  Los Angeles CA 90007</t>
+  </si>
+  <si>
+    <t>University of Southern California (854 Downey Way)</t>
+  </si>
+  <si>
+    <t>854 Downey Way  Los Angeles CA 90089</t>
+  </si>
+  <si>
+    <t>University of Southern California (941 Bloom Walk)</t>
+  </si>
+  <si>
+    <t>941 Bloom Walk  Los Angeles CA 90089</t>
+  </si>
+  <si>
+    <t>Sapporo U.S.A. (1999 Citracado Parkway)</t>
+  </si>
+  <si>
+    <t>Sapporo U.S.A. (2865 Executive Place)</t>
+  </si>
+  <si>
+    <t>Sapporo U.S.A. (2005 Harmony Grove Rd)</t>
+  </si>
+  <si>
+    <t>2005 Harmony Grove Rd  Escondido CA 92029</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1497,7 +1581,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 09/09/2026
+01/01/2023 - 09/14/2026
 </t>
     </r>
     <r>
@@ -1511,88 +1595,28 @@
     </r>
   </si>
   <si>
-    <t>Shell Catalyst &amp; Technologies</t>
-  </si>
-  <si>
-    <t>10 Mococo Road  Martinez CA 94553</t>
-  </si>
-  <si>
-    <t>Trailer Park, Inc.</t>
-  </si>
-  <si>
-    <t>6922 Hollywood Blvd, 10th Floor  Los Angeles CA 90028</t>
-  </si>
-  <si>
-    <t>University of Southern California (1042 Downey Way)</t>
-  </si>
-  <si>
-    <t>1042 Downey Way  Los Angeles CA 90089</t>
-  </si>
-  <si>
-    <t>University of Southern California (1149 S. Hill Street)</t>
-  </si>
-  <si>
-    <t>1149 S. Hill Street  Los Angeles CA 90089</t>
-  </si>
-  <si>
-    <t>University of Southern California (1150 S. Olive Street)</t>
-  </si>
-  <si>
-    <t>1150 S. Olive Street  Los Angeles CA 90015</t>
-  </si>
-  <si>
-    <t>University of Southern California (12015 E Waterfront Dr.)</t>
-  </si>
-  <si>
-    <t>12015 E Waterfront Dr.  Playa Vista CA 90094</t>
-  </si>
-  <si>
-    <t>University of Southern California (3649 McClintock Ave.)</t>
-  </si>
-  <si>
-    <t>3649 McClintock Ave.  Los Angeles CA 90089</t>
-  </si>
-  <si>
-    <t>University of Southern California (3740 McClintock Ave)</t>
-  </si>
-  <si>
-    <t>3740 McClintock Ave  Los Angeles CA 90089</t>
-  </si>
-  <si>
-    <t>University of Southern California (4676 Admiralty Way)</t>
-  </si>
-  <si>
-    <t>4676 Admiralty Way  Marina Del Rey CA 90292</t>
-  </si>
-  <si>
-    <t>University of Southern California (746 W Adams Blvd.)</t>
-  </si>
-  <si>
-    <t>746 W Adams Blvd.  Los Angeles CA 90007</t>
-  </si>
-  <si>
-    <t>University of Southern California (854 Downey Way)</t>
-  </si>
-  <si>
-    <t>854 Downey Way  Los Angeles CA 90089</t>
-  </si>
-  <si>
-    <t>University of Southern California (941 Bloom Walk)</t>
-  </si>
-  <si>
-    <t>941 Bloom Walk  Los Angeles CA 90089</t>
-  </si>
-  <si>
-    <t>Sapporo U.S.A. (1999 Citracado Parkway)</t>
-  </si>
-  <si>
-    <t>Sapporo U.S.A. (2865 Executive Place)</t>
-  </si>
-  <si>
-    <t>Sapporo U.S.A. (2005 Harmony Grove Rd)</t>
-  </si>
-  <si>
-    <t>2005 Harmony Grove Rd  Escondido CA 92029</t>
+    <t>Fuji Food Products, Inc.</t>
+  </si>
+  <si>
+    <t>14420 Bloomfield Ave.  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>LeeMah Electronics</t>
+  </si>
+  <si>
+    <t>15 South Hill Drive  Brisbane CA 94005</t>
+  </si>
+  <si>
+    <t>Uber Technologies, Inc. - 200 Mathilda Place</t>
+  </si>
+  <si>
+    <t>200 Mathilda Place  Sunnyvale CA 94086</t>
+  </si>
+  <si>
+    <t>Uber technologies, Inc. - 190 Mathilda Place</t>
+  </si>
+  <si>
+    <t>190 Mathilda Place  Sunnyvale CA 94086</t>
   </si>
   <si>
     <r>
@@ -1606,7 +1630,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 09/09/2026</t>
+      <t>07/01/26 to 09/14/2026</t>
     </r>
     <r>
       <rPr>
@@ -1626,7 +1650,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I218.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I222.</t>
     </r>
   </si>
 </sst>
@@ -2792,8 +2816,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I218" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I218" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I222" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I222" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -3214,7 +3238,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>11435</v>
+        <v>11669</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3223,7 +3247,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3250,7 +3274,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3282,7 +3306,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I218"/>
+  <dimension ref="A1:I222"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -3303,7 +3327,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -9179,7 +9203,7 @@
         <v>46356</v>
       </c>
       <c r="E204" s="28" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F204" s="28" t="s">
         <v>52</v>
@@ -9188,7 +9212,7 @@
         <v>64</v>
       </c>
       <c r="H204" s="30" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I204" s="32" t="s">
         <v>34</v>
@@ -9208,7 +9232,7 @@
         <v>46210</v>
       </c>
       <c r="E205" s="28" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F205" s="28" t="s">
         <v>6</v>
@@ -9217,7 +9241,7 @@
         <v>119</v>
       </c>
       <c r="H205" s="30" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I205" s="32" t="s">
         <v>41</v>
@@ -9237,7 +9261,7 @@
         <v>46330</v>
       </c>
       <c r="E206" s="28" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F206" s="28" t="s">
         <v>6</v>
@@ -9246,7 +9270,7 @@
         <v>7</v>
       </c>
       <c r="H206" s="30" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I206" s="32" t="s">
         <v>44</v>
@@ -9266,7 +9290,7 @@
         <v>46330</v>
       </c>
       <c r="E207" s="28" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F207" s="28" t="s">
         <v>6</v>
@@ -9275,7 +9299,7 @@
         <v>1</v>
       </c>
       <c r="H207" s="30" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I207" s="32" t="s">
         <v>44</v>
@@ -9295,7 +9319,7 @@
         <v>46330</v>
       </c>
       <c r="E208" s="28" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F208" s="28" t="s">
         <v>6</v>
@@ -9304,7 +9328,7 @@
         <v>5</v>
       </c>
       <c r="H208" s="30" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I208" s="32" t="s">
         <v>44</v>
@@ -9324,7 +9348,7 @@
         <v>46330</v>
       </c>
       <c r="E209" s="28" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F209" s="28" t="s">
         <v>6</v>
@@ -9333,7 +9357,7 @@
         <v>8</v>
       </c>
       <c r="H209" s="30" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I209" s="32" t="s">
         <v>44</v>
@@ -9353,7 +9377,7 @@
         <v>46330</v>
       </c>
       <c r="E210" s="28" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F210" s="28" t="s">
         <v>6</v>
@@ -9362,7 +9386,7 @@
         <v>21</v>
       </c>
       <c r="H210" s="30" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I210" s="32" t="s">
         <v>44</v>
@@ -9382,7 +9406,7 @@
         <v>46330</v>
       </c>
       <c r="E211" s="28" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F211" s="28" t="s">
         <v>6</v>
@@ -9391,7 +9415,7 @@
         <v>2</v>
       </c>
       <c r="H211" s="30" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I211" s="32" t="s">
         <v>44</v>
@@ -9411,7 +9435,7 @@
         <v>46330</v>
       </c>
       <c r="E212" s="28" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F212" s="28" t="s">
         <v>6</v>
@@ -9420,7 +9444,7 @@
         <v>15</v>
       </c>
       <c r="H212" s="30" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I212" s="32" t="s">
         <v>44</v>
@@ -9440,7 +9464,7 @@
         <v>46330</v>
       </c>
       <c r="E213" s="28" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F213" s="28" t="s">
         <v>6</v>
@@ -9449,7 +9473,7 @@
         <v>1</v>
       </c>
       <c r="H213" s="30" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I213" s="32" t="s">
         <v>44</v>
@@ -9469,7 +9493,7 @@
         <v>46330</v>
       </c>
       <c r="E214" s="28" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F214" s="28" t="s">
         <v>6</v>
@@ -9478,7 +9502,7 @@
         <v>1</v>
       </c>
       <c r="H214" s="30" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I214" s="32" t="s">
         <v>44</v>
@@ -9498,7 +9522,7 @@
         <v>46330</v>
       </c>
       <c r="E215" s="28" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F215" s="28" t="s">
         <v>6</v>
@@ -9507,7 +9531,7 @@
         <v>4</v>
       </c>
       <c r="H215" s="30" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I215" s="32" t="s">
         <v>44</v>
@@ -9527,7 +9551,7 @@
         <v>46339</v>
       </c>
       <c r="E216" s="28" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F216" s="28" t="s">
         <v>52</v>
@@ -9556,7 +9580,7 @@
         <v>46339</v>
       </c>
       <c r="E217" s="28" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F217" s="28" t="s">
         <v>52</v>
@@ -9585,7 +9609,7 @@
         <v>46339</v>
       </c>
       <c r="E218" s="28" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F218" s="28" t="s">
         <v>52</v>
@@ -9594,10 +9618,126 @@
         <v>6</v>
       </c>
       <c r="H218" s="30" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I218" s="32" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B219" s="29">
+        <v>46275</v>
+      </c>
+      <c r="C219" s="29">
+        <v>46276</v>
+      </c>
+      <c r="D219" s="29">
+        <v>46339</v>
+      </c>
+      <c r="E219" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="F219" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G219" s="30">
+        <v>35</v>
+      </c>
+      <c r="H219" s="30" t="s">
+        <v>480</v>
+      </c>
+      <c r="I219" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B220" s="29">
+        <v>46276</v>
+      </c>
+      <c r="C220" s="29">
+        <v>46279</v>
+      </c>
+      <c r="D220" s="29">
+        <v>46377</v>
+      </c>
+      <c r="E220" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="F220" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G220" s="30">
+        <v>62</v>
+      </c>
+      <c r="H220" s="30" t="s">
+        <v>482</v>
+      </c>
+      <c r="I220" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B221" s="29">
+        <v>46267</v>
+      </c>
+      <c r="C221" s="29">
+        <v>46279</v>
+      </c>
+      <c r="D221" s="29">
+        <v>46328</v>
+      </c>
+      <c r="E221" s="28" t="s">
+        <v>483</v>
+      </c>
+      <c r="F221" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G221" s="30">
+        <v>94</v>
+      </c>
+      <c r="H221" s="30" t="s">
+        <v>484</v>
+      </c>
+      <c r="I221" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B222" s="29">
+        <v>46267</v>
+      </c>
+      <c r="C222" s="29">
+        <v>46279</v>
+      </c>
+      <c r="D222" s="29">
+        <v>46328</v>
+      </c>
+      <c r="E222" s="28" t="s">
+        <v>485</v>
+      </c>
+      <c r="F222" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G222" s="30">
+        <v>43</v>
+      </c>
+      <c r="H222" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="I222" s="32" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -9614,7 +9754,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I218</xm:sqref>
+          <xm:sqref>I3:I222</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -9735,7 +9875,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>450</v>
+        <v>478</v>
       </c>
       <c r="E1"/>
     </row>
@@ -10150,7 +10290,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04742B8B-EF9C-4AD3-90FC-1E5DA2BFE8B0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76D33AEE-9071-43B6-9638-C0186BEA8438}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -10169,7 +10309,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3BDCC9B-2188-4BA0-9B64-3D7DE26BB377}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAEC2EC9-DE68-4EF0-83E3-C802B9036C98}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -10177,24 +10317,24 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58496AB6-41EC-40A7-B185-55DA0F0F8F77}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A580377C-71F4-4AF5-86F0-F1312E71DF4E}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" removed="0"/>
+  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" contentBits="0" removed="0"/>
 </clbl:labelList>
 </file>
--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19B4AD77-A87F-4673-8195-E0F886C5D21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{433E8CBC-9486-44C1-9951-318B0786ED4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="505">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1562,6 +1562,113 @@
     <t>2005 Harmony Grove Rd  Escondido CA 92029</t>
   </si>
   <si>
+    <t>Fuji Food Products, Inc.</t>
+  </si>
+  <si>
+    <t>14420 Bloomfield Ave.  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>LeeMah Electronics</t>
+  </si>
+  <si>
+    <t>15 South Hill Drive  Brisbane CA 94005</t>
+  </si>
+  <si>
+    <t>Uber Technologies, Inc. - 200 Mathilda Place</t>
+  </si>
+  <si>
+    <t>200 Mathilda Place  Sunnyvale CA 94086</t>
+  </si>
+  <si>
+    <t>Uber technologies, Inc. - 190 Mathilda Place</t>
+  </si>
+  <si>
+    <t>190 Mathilda Place  Sunnyvale CA 94086</t>
+  </si>
+  <si>
+    <t>Oracle Pleasanton Campus (Pleasanton Campus)</t>
+  </si>
+  <si>
+    <t>5815 Owens Drive  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>Oracle America, Inc.</t>
+  </si>
+  <si>
+    <t>500 Oracle Parkway  Redwood City CA 94065</t>
+  </si>
+  <si>
+    <t>4230 Leonard Stocking Drive  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>Uber Technologies, Inc. - 1655 3rd Street</t>
+  </si>
+  <si>
+    <t>Uber Technologies, Inc. 1725 3rd Street</t>
+  </si>
+  <si>
+    <t>1725 3rd Street  San Francisco CA 94158</t>
+  </si>
+  <si>
+    <t>Full Steam Staffing (2121 Boeing Way)</t>
+  </si>
+  <si>
+    <t>2121 Boeing Way  Stockton CA 95206</t>
+  </si>
+  <si>
+    <t>Full Steam Staffing (4239 Pock Lane)</t>
+  </si>
+  <si>
+    <t>4239 Pock Lane  Stockton CA 95206</t>
+  </si>
+  <si>
+    <t>DesigneRx Pharmaceuticals, Inc.</t>
+  </si>
+  <si>
+    <t>Pathways Community Services dba Clarvida</t>
+  </si>
+  <si>
+    <t>1360 S. Anaheim Blvd. Suite 101  Anaheim CA 92805</t>
+  </si>
+  <si>
+    <t>1401 N Tustin Ave #225  Santa Ana CA 92706</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">WARN REPORT - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>07/01/26 to 09/16/2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I232.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1581,7 +1688,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 09/14/2026
+01/01/2023 - 09/16/2026
 </t>
     </r>
     <r>
@@ -1595,63 +1702,7 @@
     </r>
   </si>
   <si>
-    <t>Fuji Food Products, Inc.</t>
-  </si>
-  <si>
-    <t>14420 Bloomfield Ave.  Santa Fe Springs CA 90670</t>
-  </si>
-  <si>
-    <t>LeeMah Electronics</t>
-  </si>
-  <si>
-    <t>15 South Hill Drive  Brisbane CA 94005</t>
-  </si>
-  <si>
-    <t>Uber Technologies, Inc. - 200 Mathilda Place</t>
-  </si>
-  <si>
-    <t>200 Mathilda Place  Sunnyvale CA 94086</t>
-  </si>
-  <si>
-    <t>Uber technologies, Inc. - 190 Mathilda Place</t>
-  </si>
-  <si>
-    <t>190 Mathilda Place  Sunnyvale CA 94086</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">WARN REPORT - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>07/01/26 to 09/14/2026</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I222.</t>
-    </r>
+    <t>Relocation</t>
   </si>
 </sst>
 </file>
@@ -1767,7 +1818,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1784,6 +1835,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+        <bgColor rgb="FFF0F0F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1908,7 +1965,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2022,6 +2079,30 @@
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -2816,8 +2897,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I222" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I222" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I232" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I232" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -3238,7 +3319,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>11669</v>
+        <v>12547</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3247,7 +3328,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3274,7 +3355,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3306,7 +3387,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I222"/>
+  <dimension ref="A1:I232"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -3327,7 +3408,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -7379,7 +7460,7 @@
         <v>338</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>6</v>
+        <v>504</v>
       </c>
       <c r="G141" s="30">
         <v>73</v>
@@ -9638,7 +9719,7 @@
         <v>46339</v>
       </c>
       <c r="E219" s="28" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F219" s="28" t="s">
         <v>6</v>
@@ -9647,7 +9728,7 @@
         <v>35</v>
       </c>
       <c r="H219" s="30" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I219" s="32" t="s">
         <v>34</v>
@@ -9667,7 +9748,7 @@
         <v>46377</v>
       </c>
       <c r="E220" s="28" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F220" s="28" t="s">
         <v>52</v>
@@ -9676,7 +9757,7 @@
         <v>62</v>
       </c>
       <c r="H220" s="30" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I220" s="32" t="s">
         <v>34</v>
@@ -9696,7 +9777,7 @@
         <v>46328</v>
       </c>
       <c r="E221" s="28" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F221" s="28" t="s">
         <v>6</v>
@@ -9705,7 +9786,7 @@
         <v>94</v>
       </c>
       <c r="H221" s="30" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I221" s="32" t="s">
         <v>43</v>
@@ -9725,7 +9806,7 @@
         <v>46328</v>
       </c>
       <c r="E222" s="28" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F222" s="28" t="s">
         <v>6</v>
@@ -9734,10 +9815,300 @@
         <v>43</v>
       </c>
       <c r="H222" s="30" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I222" s="32" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B223" s="41">
+        <v>46279</v>
+      </c>
+      <c r="C223" s="42">
+        <v>46280</v>
+      </c>
+      <c r="D223" s="41">
+        <v>46339</v>
+      </c>
+      <c r="E223" s="43" t="s">
+        <v>486</v>
+      </c>
+      <c r="F223" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="G223" s="30">
+        <v>63</v>
+      </c>
+      <c r="H223" s="43" t="s">
+        <v>487</v>
+      </c>
+      <c r="I223" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B224" s="41">
+        <v>46279</v>
+      </c>
+      <c r="C224" s="42">
+        <v>46280</v>
+      </c>
+      <c r="D224" s="41">
+        <v>46339</v>
+      </c>
+      <c r="E224" s="43" t="s">
+        <v>488</v>
+      </c>
+      <c r="F224" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="G224" s="44">
+        <v>279</v>
+      </c>
+      <c r="H224" s="43" t="s">
+        <v>489</v>
+      </c>
+      <c r="I224" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B225" s="45">
+        <v>46279</v>
+      </c>
+      <c r="C225" s="46">
+        <v>46280</v>
+      </c>
+      <c r="D225" s="45">
+        <v>46339</v>
+      </c>
+      <c r="E225" s="47" t="s">
+        <v>488</v>
+      </c>
+      <c r="F225" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="G225" s="48">
+        <v>99</v>
+      </c>
+      <c r="H225" s="47" t="s">
+        <v>490</v>
+      </c>
+      <c r="I225" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B226" s="41">
+        <v>46267</v>
+      </c>
+      <c r="C226" s="42">
+        <v>46280</v>
+      </c>
+      <c r="D226" s="41">
+        <v>46328</v>
+      </c>
+      <c r="E226" s="43" t="s">
+        <v>491</v>
+      </c>
+      <c r="F226" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="G226" s="44">
+        <v>151</v>
+      </c>
+      <c r="H226" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="I226" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B227" s="45">
+        <v>46267</v>
+      </c>
+      <c r="C227" s="46">
+        <v>46280</v>
+      </c>
+      <c r="D227" s="45">
+        <v>46328</v>
+      </c>
+      <c r="E227" s="47" t="s">
+        <v>492</v>
+      </c>
+      <c r="F227" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="G227" s="48">
+        <v>102</v>
+      </c>
+      <c r="H227" s="47" t="s">
+        <v>493</v>
+      </c>
+      <c r="I227" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" s="33" t="s">
+        <v>323</v>
+      </c>
+      <c r="B228" s="41">
+        <v>46280</v>
+      </c>
+      <c r="C228" s="42">
+        <v>46280</v>
+      </c>
+      <c r="D228" s="41">
+        <v>46330</v>
+      </c>
+      <c r="E228" s="43" t="s">
+        <v>494</v>
+      </c>
+      <c r="F228" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G228" s="44">
+        <v>91</v>
+      </c>
+      <c r="H228" s="43" t="s">
+        <v>495</v>
+      </c>
+      <c r="I228" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" s="33" t="s">
+        <v>323</v>
+      </c>
+      <c r="B229" s="45">
+        <v>46280</v>
+      </c>
+      <c r="C229" s="46">
+        <v>46280</v>
+      </c>
+      <c r="D229" s="45">
+        <v>46330</v>
+      </c>
+      <c r="E229" s="47" t="s">
+        <v>496</v>
+      </c>
+      <c r="F229" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="G229" s="48">
+        <v>19</v>
+      </c>
+      <c r="H229" s="47" t="s">
+        <v>497</v>
+      </c>
+      <c r="I229" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="B230" s="41">
+        <v>46279</v>
+      </c>
+      <c r="C230" s="42">
+        <v>46280</v>
+      </c>
+      <c r="D230" s="41">
+        <v>46341</v>
+      </c>
+      <c r="E230" s="43" t="s">
+        <v>498</v>
+      </c>
+      <c r="F230" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G230" s="44">
+        <v>7</v>
+      </c>
+      <c r="H230" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="I230" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B231" s="41">
+        <v>46266</v>
+      </c>
+      <c r="C231" s="42">
+        <v>46281</v>
+      </c>
+      <c r="D231" s="41">
+        <v>46327</v>
+      </c>
+      <c r="E231" s="43" t="s">
+        <v>499</v>
+      </c>
+      <c r="F231" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G231" s="44">
+        <v>35</v>
+      </c>
+      <c r="H231" s="43" t="s">
+        <v>500</v>
+      </c>
+      <c r="I231" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B232" s="45">
+        <v>46266</v>
+      </c>
+      <c r="C232" s="46">
+        <v>46281</v>
+      </c>
+      <c r="D232" s="45">
+        <v>46327</v>
+      </c>
+      <c r="E232" s="47" t="s">
+        <v>499</v>
+      </c>
+      <c r="F232" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="G232" s="48">
+        <v>32</v>
+      </c>
+      <c r="H232" s="47" t="s">
+        <v>501</v>
+      </c>
+      <c r="I232" s="32" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -9754,7 +10125,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I222</xm:sqref>
+          <xm:sqref>I3:I232</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -9875,7 +10246,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>478</v>
+        <v>503</v>
       </c>
       <c r="E1"/>
     </row>
@@ -10290,7 +10661,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76D33AEE-9071-43B6-9638-C0186BEA8438}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9646D4B6-BDF5-412D-9E18-4F8C60CC4F22}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -10309,7 +10680,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAEC2EC9-DE68-4EF0-83E3-C802B9036C98}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40E193B2-5068-43B7-ABC1-72CBE9DE0AD1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -10317,18 +10688,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A580377C-71F4-4AF5-86F0-F1312E71DF4E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF2164DD-2934-449D-B327-2858E8EBEE4B}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{433E8CBC-9486-44C1-9951-318B0786ED4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{67E9327B-19F6-4ED4-B380-DB1D40B7B3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="579">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1634,6 +1634,264 @@
     <t>1401 N Tustin Ave #225  Santa Ana CA 92706</t>
   </si>
   <si>
+    <t>Fresno County</t>
+  </si>
+  <si>
+    <t>Maya Cinemas Fresno 16</t>
+  </si>
+  <si>
+    <t>3090 E. Campus Pointe Dr.  Fresno CA 93710</t>
+  </si>
+  <si>
+    <t>Levine Management Group, Inc. - 822 SRobertson</t>
+  </si>
+  <si>
+    <t>Layoff Not known at this time</t>
+  </si>
+  <si>
+    <t>822 S Robertson Blvd. Ste 200  Los Angeles CA 90035</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Candlewood</t>
+  </si>
+  <si>
+    <t>4051 Candlewood St.  Lakewood CA 90712</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - San Dimas</t>
+  </si>
+  <si>
+    <t>2400 San Dimas Canyon Rd.  La Verne CA 91750</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Ratner St.</t>
+  </si>
+  <si>
+    <t>10986 W. Ratner St.  Sun Valley CA 91352</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. 95th Street</t>
+  </si>
+  <si>
+    <t>1351 W. 95th Street  Los Angeles CA 90044</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Towne Avenue</t>
+  </si>
+  <si>
+    <t>425 Towne Avenue  Los Angeles CA 90013</t>
+  </si>
+  <si>
+    <t>Levine management Groups, Inc. - Normandie Ave</t>
+  </si>
+  <si>
+    <t>6525 Normandie Ave.  Los Angeles CA 90044</t>
+  </si>
+  <si>
+    <t>Levine Management Group, Inc. - Rural Dr.</t>
+  </si>
+  <si>
+    <t>234 N. Rural Dr.  Monterey Park CA 91755</t>
+  </si>
+  <si>
+    <t>Levine Management Group, Inc. - James M. Wood Blvd</t>
+  </si>
+  <si>
+    <t>2300 James M. Wood Blvd.  Los Angeles CA 90006</t>
+  </si>
+  <si>
+    <t>Levine Management Group, Inc. - Gale Ave.</t>
+  </si>
+  <si>
+    <t>15554 Gale Ave.  Hacienda Heights CA 91745</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Potrero Grande</t>
+  </si>
+  <si>
+    <t>1301 Potrero Grande Dr.  Rosemead CA 91770</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Mesa St.</t>
+  </si>
+  <si>
+    <t>805 S. Mesa St.  San Pedro CA 90731</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - 900-906 Crenshaw Blvd</t>
+  </si>
+  <si>
+    <t>900-906 Crenshaw Blvd.  Los Angeles CA 90019</t>
+  </si>
+  <si>
+    <t>Levine Management Groups. Inc. - Kingsley Dr.</t>
+  </si>
+  <si>
+    <t>540-542 Kingsley Dr.  Los Angeles CA 90020</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Beachwood Dr.</t>
+  </si>
+  <si>
+    <t>2100 N. Beachwood Dr.  Los Angeles CA 90068</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Manhattan Pl</t>
+  </si>
+  <si>
+    <t>1257 S. Manhattan Pl.  Los Angeles CA 90019</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Valley Blvd.</t>
+  </si>
+  <si>
+    <t>2775 E. Valley Blvd.  West Covina CA 91792</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - 1053 S. New Hampshire Ave.-</t>
+  </si>
+  <si>
+    <t>1053 S. New Hampshire Ave.  Los Angeles CA 90006</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - 1057 S, New Hampshire Ave</t>
+  </si>
+  <si>
+    <t>1057 New Hampshire Ave.  Los Angeles CA 90006</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - 980 Palm Ave.</t>
+  </si>
+  <si>
+    <t>980 Palm Ave.  West Hollywood CA 90069</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Arrow Highway</t>
+  </si>
+  <si>
+    <t>837 E. Arrow Highway  Pomona CA 91767</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Glendale Blvd</t>
+  </si>
+  <si>
+    <t>153 Glendale Blvd.  Los Angeles CA 90026</t>
+  </si>
+  <si>
+    <t>Leveine Management Groups - 415 S. Oleander Ave.</t>
+  </si>
+  <si>
+    <t>415 S. Oleander Ave,  Compton CA 90220</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - 425 S. Oleander Ave.</t>
+  </si>
+  <si>
+    <t>425 S. Oleander Ave.  Compton CA 90220</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Canada Blvd.</t>
+  </si>
+  <si>
+    <t>2615 Canada Blvd.  Glendale CA 91208</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Sunset Pl.</t>
+  </si>
+  <si>
+    <t>2848 Sunset Pl.  Los Angeles CA 90005</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Cypress Road</t>
+  </si>
+  <si>
+    <t>5493 Cypress Road  Oxnard CA 93033</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Ponderosa Dr.</t>
+  </si>
+  <si>
+    <t>2105 E. Ponderosa Dr.  Camarillo CA 93010</t>
+  </si>
+  <si>
+    <t>Levine Management Groups, Inc. - Carmelita Ct.</t>
+  </si>
+  <si>
+    <t>201 Carmelita Ct.  Oxnard CA 93030</t>
+  </si>
+  <si>
+    <t>Amy's Kitchen, LLC</t>
+  </si>
+  <si>
+    <t>2330 Northpoint Parkway  Santa Rosa CA 95407</t>
+  </si>
+  <si>
+    <t>Safeway, Inc. - Stoneridge Mall Road</t>
+  </si>
+  <si>
+    <t>5918 Stoneridge Mall Road  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>Safeway, Inc. - Dublin Canyon Road</t>
+  </si>
+  <si>
+    <t>11555 Dublin Canyon Road  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>2200 Mission College Boulevard  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>Intel Corporation, Inc. - SC-9</t>
+  </si>
+  <si>
+    <t>Intel Corporation - SC-11</t>
+  </si>
+  <si>
+    <t>IPS Nationwide, Inc.</t>
+  </si>
+  <si>
+    <t>39899 Balentine Dr., Unit 200, Suite #228  Newark CA 94560</t>
+  </si>
+  <si>
+    <t>3186 Airway Ave., Suite F  Costa Mesa CA 92626</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WARN REPORT -</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+01/01/2023 - 09/21/2026
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through H3.</t>
+    </r>
+  </si>
+  <si>
+    <t>Relocation Permanent</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -1645,7 +1903,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 09/16/2026</t>
+      <t>07/01/26 to 09/21/2026</t>
     </r>
     <r>
       <rPr>
@@ -1665,44 +1923,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I232.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I271.</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>WARN REPORT -</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-01/01/2023 - 09/16/2026
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through H3.</t>
-    </r>
-  </si>
-  <si>
-    <t>Relocation</t>
   </si>
 </sst>
 </file>
@@ -2897,8 +3119,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I232" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I232" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I271" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I271" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -3319,7 +3541,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>12547</v>
+        <v>13265</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3328,7 +3550,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3346,7 +3568,7 @@
       </c>
       <c r="B6" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Not known at this time")</f>
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3355,7 +3577,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3387,28 +3609,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I232"/>
-  <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I271"/>
+  <sheetFormatPr defaultColWidth="150.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="50.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>502</v>
+        <v>578</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -7460,7 +7677,7 @@
         <v>338</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>504</v>
+        <v>577</v>
       </c>
       <c r="G141" s="30">
         <v>73</v>
@@ -10109,6 +10326,1137 @@
       </c>
       <c r="I232" s="32" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" s="28" t="s">
+        <v>502</v>
+      </c>
+      <c r="B233" s="29">
+        <v>46281</v>
+      </c>
+      <c r="C233" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D233" s="29">
+        <v>46280</v>
+      </c>
+      <c r="E233" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="F233" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G233" s="30">
+        <v>86</v>
+      </c>
+      <c r="H233" s="30" t="s">
+        <v>504</v>
+      </c>
+      <c r="I233" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B234" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C234" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D234" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E234" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="F234" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G234" s="30">
+        <v>17</v>
+      </c>
+      <c r="H234" s="30" t="s">
+        <v>507</v>
+      </c>
+      <c r="I234" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B235" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C235" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D235" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E235" s="28" t="s">
+        <v>508</v>
+      </c>
+      <c r="F235" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G235" s="30">
+        <v>2</v>
+      </c>
+      <c r="H235" s="30" t="s">
+        <v>509</v>
+      </c>
+      <c r="I235" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B236" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C236" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D236" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E236" s="28" t="s">
+        <v>510</v>
+      </c>
+      <c r="F236" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G236" s="30">
+        <v>3</v>
+      </c>
+      <c r="H236" s="30" t="s">
+        <v>511</v>
+      </c>
+      <c r="I236" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B237" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C237" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D237" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E237" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="F237" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G237" s="30">
+        <v>1</v>
+      </c>
+      <c r="H237" s="30" t="s">
+        <v>513</v>
+      </c>
+      <c r="I237" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B238" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C238" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D238" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E238" s="28" t="s">
+        <v>514</v>
+      </c>
+      <c r="F238" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G238" s="30">
+        <v>2</v>
+      </c>
+      <c r="H238" s="30" t="s">
+        <v>515</v>
+      </c>
+      <c r="I238" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B239" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C239" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D239" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E239" s="28" t="s">
+        <v>516</v>
+      </c>
+      <c r="F239" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G239" s="30">
+        <v>4</v>
+      </c>
+      <c r="H239" s="30" t="s">
+        <v>517</v>
+      </c>
+      <c r="I239" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B240" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C240" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D240" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E240" s="28" t="s">
+        <v>518</v>
+      </c>
+      <c r="F240" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G240" s="30">
+        <v>2</v>
+      </c>
+      <c r="H240" s="30" t="s">
+        <v>519</v>
+      </c>
+      <c r="I240" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B241" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C241" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D241" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E241" s="28" t="s">
+        <v>520</v>
+      </c>
+      <c r="F241" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G241" s="30">
+        <v>4</v>
+      </c>
+      <c r="H241" s="30" t="s">
+        <v>521</v>
+      </c>
+      <c r="I241" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B242" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C242" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D242" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E242" s="28" t="s">
+        <v>522</v>
+      </c>
+      <c r="F242" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G242" s="30">
+        <v>2</v>
+      </c>
+      <c r="H242" s="30" t="s">
+        <v>523</v>
+      </c>
+      <c r="I242" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B243" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C243" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D243" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E243" s="28" t="s">
+        <v>524</v>
+      </c>
+      <c r="F243" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G243" s="30">
+        <v>2</v>
+      </c>
+      <c r="H243" s="30" t="s">
+        <v>525</v>
+      </c>
+      <c r="I243" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B244" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C244" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D244" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E244" s="28" t="s">
+        <v>526</v>
+      </c>
+      <c r="F244" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G244" s="30">
+        <v>1</v>
+      </c>
+      <c r="H244" s="30" t="s">
+        <v>527</v>
+      </c>
+      <c r="I244" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B245" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C245" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D245" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E245" s="28" t="s">
+        <v>528</v>
+      </c>
+      <c r="F245" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G245" s="30">
+        <v>2</v>
+      </c>
+      <c r="H245" s="30" t="s">
+        <v>529</v>
+      </c>
+      <c r="I245" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B246" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C246" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D246" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E246" s="28" t="s">
+        <v>530</v>
+      </c>
+      <c r="F246" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G246" s="30">
+        <v>1</v>
+      </c>
+      <c r="H246" s="30" t="s">
+        <v>531</v>
+      </c>
+      <c r="I246" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B247" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C247" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D247" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E247" s="28" t="s">
+        <v>532</v>
+      </c>
+      <c r="F247" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G247" s="30">
+        <v>1</v>
+      </c>
+      <c r="H247" s="30" t="s">
+        <v>533</v>
+      </c>
+      <c r="I247" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B248" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C248" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D248" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E248" s="28" t="s">
+        <v>534</v>
+      </c>
+      <c r="F248" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G248" s="30">
+        <v>1</v>
+      </c>
+      <c r="H248" s="30" t="s">
+        <v>535</v>
+      </c>
+      <c r="I248" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B249" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C249" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D249" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E249" s="28" t="s">
+        <v>536</v>
+      </c>
+      <c r="F249" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G249" s="30">
+        <v>1</v>
+      </c>
+      <c r="H249" s="30" t="s">
+        <v>537</v>
+      </c>
+      <c r="I249" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B250" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C250" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D250" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E250" s="28" t="s">
+        <v>538</v>
+      </c>
+      <c r="F250" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G250" s="30">
+        <v>4</v>
+      </c>
+      <c r="H250" s="30" t="s">
+        <v>539</v>
+      </c>
+      <c r="I250" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A251" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B251" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C251" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D251" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E251" s="28" t="s">
+        <v>540</v>
+      </c>
+      <c r="F251" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G251" s="30">
+        <v>1</v>
+      </c>
+      <c r="H251" s="30" t="s">
+        <v>541</v>
+      </c>
+      <c r="I251" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A252" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B252" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C252" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D252" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E252" s="28" t="s">
+        <v>542</v>
+      </c>
+      <c r="F252" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G252" s="30">
+        <v>1</v>
+      </c>
+      <c r="H252" s="30" t="s">
+        <v>543</v>
+      </c>
+      <c r="I252" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A253" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B253" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C253" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D253" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E253" s="28" t="s">
+        <v>544</v>
+      </c>
+      <c r="F253" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G253" s="30">
+        <v>2</v>
+      </c>
+      <c r="H253" s="30" t="s">
+        <v>545</v>
+      </c>
+      <c r="I253" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A254" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B254" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C254" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D254" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E254" s="28" t="s">
+        <v>546</v>
+      </c>
+      <c r="F254" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G254" s="30">
+        <v>1</v>
+      </c>
+      <c r="H254" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="I254" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A255" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B255" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C255" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D255" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E255" s="28" t="s">
+        <v>548</v>
+      </c>
+      <c r="F255" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G255" s="30">
+        <v>1</v>
+      </c>
+      <c r="H255" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="I255" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A256" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B256" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C256" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D256" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E256" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="F256" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G256" s="30">
+        <v>1</v>
+      </c>
+      <c r="H256" s="30" t="s">
+        <v>551</v>
+      </c>
+      <c r="I256" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B257" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C257" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D257" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E257" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="F257" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G257" s="30">
+        <v>3</v>
+      </c>
+      <c r="H257" s="30" t="s">
+        <v>553</v>
+      </c>
+      <c r="I257" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B258" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C258" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D258" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E258" s="28" t="s">
+        <v>554</v>
+      </c>
+      <c r="F258" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G258" s="30">
+        <v>1</v>
+      </c>
+      <c r="H258" s="30" t="s">
+        <v>555</v>
+      </c>
+      <c r="I258" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B259" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C259" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D259" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E259" s="28" t="s">
+        <v>556</v>
+      </c>
+      <c r="F259" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G259" s="30">
+        <v>2</v>
+      </c>
+      <c r="H259" s="30" t="s">
+        <v>557</v>
+      </c>
+      <c r="I259" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B260" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C260" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D260" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E260" s="28" t="s">
+        <v>558</v>
+      </c>
+      <c r="F260" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G260" s="30">
+        <v>2</v>
+      </c>
+      <c r="H260" s="30" t="s">
+        <v>559</v>
+      </c>
+      <c r="I260" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B261" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C261" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D261" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E261" s="28" t="s">
+        <v>560</v>
+      </c>
+      <c r="F261" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G261" s="30">
+        <v>2</v>
+      </c>
+      <c r="H261" s="30" t="s">
+        <v>561</v>
+      </c>
+      <c r="I261" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B262" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C262" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D262" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E262" s="28" t="s">
+        <v>562</v>
+      </c>
+      <c r="F262" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G262" s="30">
+        <v>1</v>
+      </c>
+      <c r="H262" s="30" t="s">
+        <v>563</v>
+      </c>
+      <c r="I262" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B263" s="29">
+        <v>46282</v>
+      </c>
+      <c r="C263" s="29">
+        <v>46282</v>
+      </c>
+      <c r="D263" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E263" s="28" t="s">
+        <v>564</v>
+      </c>
+      <c r="F263" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G263" s="30">
+        <v>200</v>
+      </c>
+      <c r="H263" s="30" t="s">
+        <v>565</v>
+      </c>
+      <c r="I263" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B264" s="29">
+        <v>46282</v>
+      </c>
+      <c r="C264" s="29">
+        <v>46283</v>
+      </c>
+      <c r="D264" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E264" s="28" t="s">
+        <v>566</v>
+      </c>
+      <c r="F264" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G264" s="30">
+        <v>4</v>
+      </c>
+      <c r="H264" s="30" t="s">
+        <v>567</v>
+      </c>
+      <c r="I264" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B265" s="29">
+        <v>46282</v>
+      </c>
+      <c r="C265" s="29">
+        <v>46283</v>
+      </c>
+      <c r="D265" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E265" s="28" t="s">
+        <v>568</v>
+      </c>
+      <c r="F265" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G265" s="30">
+        <v>46</v>
+      </c>
+      <c r="H265" s="30" t="s">
+        <v>569</v>
+      </c>
+      <c r="I265" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B266" s="29">
+        <v>46283</v>
+      </c>
+      <c r="C266" s="29">
+        <v>46283</v>
+      </c>
+      <c r="D266" s="29">
+        <v>46295</v>
+      </c>
+      <c r="E266" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="F266" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G266" s="30">
+        <v>22</v>
+      </c>
+      <c r="H266" s="30" t="s">
+        <v>570</v>
+      </c>
+      <c r="I266" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B267" s="29">
+        <v>46283</v>
+      </c>
+      <c r="C267" s="29">
+        <v>46283</v>
+      </c>
+      <c r="D267" s="29">
+        <v>46295</v>
+      </c>
+      <c r="E267" s="28" t="s">
+        <v>571</v>
+      </c>
+      <c r="F267" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G267" s="30">
+        <v>5</v>
+      </c>
+      <c r="H267" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="I267" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B268" s="29">
+        <v>46283</v>
+      </c>
+      <c r="C268" s="29">
+        <v>46283</v>
+      </c>
+      <c r="D268" s="29">
+        <v>46295</v>
+      </c>
+      <c r="E268" s="28" t="s">
+        <v>572</v>
+      </c>
+      <c r="F268" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G268" s="30">
+        <v>1</v>
+      </c>
+      <c r="H268" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="I268" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B269" s="29">
+        <v>46283</v>
+      </c>
+      <c r="C269" s="29">
+        <v>46283</v>
+      </c>
+      <c r="D269" s="29">
+        <v>46295</v>
+      </c>
+      <c r="E269" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="F269" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G269" s="30">
+        <v>24</v>
+      </c>
+      <c r="H269" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="I269" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B270" s="29">
+        <v>46283</v>
+      </c>
+      <c r="C270" s="29">
+        <v>46283</v>
+      </c>
+      <c r="D270" s="29">
+        <v>46343</v>
+      </c>
+      <c r="E270" s="28" t="s">
+        <v>573</v>
+      </c>
+      <c r="F270" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G270" s="30">
+        <v>212</v>
+      </c>
+      <c r="H270" s="30" t="s">
+        <v>574</v>
+      </c>
+      <c r="I270" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B271" s="29">
+        <v>46283</v>
+      </c>
+      <c r="C271" s="29">
+        <v>46283</v>
+      </c>
+      <c r="D271" s="29">
+        <v>46343</v>
+      </c>
+      <c r="E271" s="28" t="s">
+        <v>573</v>
+      </c>
+      <c r="F271" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G271" s="30">
+        <v>50</v>
+      </c>
+      <c r="H271" s="30" t="s">
+        <v>575</v>
+      </c>
+      <c r="I271" s="32" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -10125,7 +11473,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I232</xm:sqref>
+          <xm:sqref>I3:I271</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10246,7 +11594,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>503</v>
+        <v>576</v>
       </c>
       <c r="E1"/>
     </row>
@@ -10661,7 +12009,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9646D4B6-BDF5-412D-9E18-4F8C60CC4F22}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD67808B-C578-46B0-BA38-8B1368DDEF79}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -10680,7 +12028,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40E193B2-5068-43B7-ABC1-72CBE9DE0AD1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3E7DA0C-0FF1-495C-8B3A-B3D0E5B82778}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -10688,18 +12036,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF2164DD-2934-449D-B327-2858E8EBEE4B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA33669-60E1-43A7-A872-44A5DB367147}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67E9327B-19F6-4ED4-B380-DB1D40B7B3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3AECD60-72AD-4932-A777-C7ACE9C50F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="617">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1875,7 +1875,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 09/21/2026
+01/01/2023 - 09/23/2026
 </t>
     </r>
     <r>
@@ -1889,7 +1889,121 @@
     </r>
   </si>
   <si>
-    <t>Relocation Permanent</t>
+    <t>Kaiser (1800 Harrison St.)</t>
+  </si>
+  <si>
+    <t>1800 Harrison St.  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>Kaiser (One Kaiser Plaza)</t>
+  </si>
+  <si>
+    <t>One Kaiser Plaza  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>Kaiser</t>
+  </si>
+  <si>
+    <t>4460 Hacienda Dr.  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>3000 S. Robertson Blvd.  Los Angeles CA 90034</t>
+  </si>
+  <si>
+    <t>Kaiser (393 E. Walnut St.)</t>
+  </si>
+  <si>
+    <t>393 E. Walnut St.  Pasadena CA 91188</t>
+  </si>
+  <si>
+    <t>Kaiser (74 N. Pasadena Ave.)</t>
+  </si>
+  <si>
+    <t>74 N. Pasadena Ave.  Pasadena CA 91103</t>
+  </si>
+  <si>
+    <t>Kaiser (75N. Fair Oaks Ave.)</t>
+  </si>
+  <si>
+    <t>75 N. Fair Oaks Ave.  Pasadena CA 91103</t>
+  </si>
+  <si>
+    <t>Kaiser (99 S. Oakland Ave.)</t>
+  </si>
+  <si>
+    <t>99 S. Oakland Ave.  Pasadena CA 91101</t>
+  </si>
+  <si>
+    <t>17836 Gillette Ave.  Irvine CA 92614</t>
+  </si>
+  <si>
+    <t>Kaiser (1830 California Ave.)</t>
+  </si>
+  <si>
+    <t>1830 California Ave.  Corona CA 92881</t>
+  </si>
+  <si>
+    <t>Kaiser (1840 California Ave.)</t>
+  </si>
+  <si>
+    <t>1840 California Ave.  Corona CA 92881</t>
+  </si>
+  <si>
+    <t>50 Iron Point Cir.  Folsom CA 95630</t>
+  </si>
+  <si>
+    <t>3240 Arden Wy.  Sacramento CA 95825</t>
+  </si>
+  <si>
+    <t>Kaiser (17140 Bernardo Center Dr.)</t>
+  </si>
+  <si>
+    <t>17140 Bernardo Center Dr.  San Diego CA 92128</t>
+  </si>
+  <si>
+    <t>Kaiser (3840 Murphy Canyon Rd.)</t>
+  </si>
+  <si>
+    <t>3840 Murphy Canyon Rd.  San Diego CA 92123</t>
+  </si>
+  <si>
+    <t>Kaiser (8954 Rio San Diego Dr.)</t>
+  </si>
+  <si>
+    <t>8954 Rio San Diego Dr.  San Diego CA 92108</t>
+  </si>
+  <si>
+    <t>2000 E El Segundo Blvd  El Segundo CA 90245</t>
+  </si>
+  <si>
+    <t>Capstone Delivery Inc.</t>
+  </si>
+  <si>
+    <t>9350 Rayo Avenue  South Gate CA 90280</t>
+  </si>
+  <si>
+    <t>Quixote Studio Services - North Valley Campus A</t>
+  </si>
+  <si>
+    <t>12137 Montague St.  Pacoima CA 91331</t>
+  </si>
+  <si>
+    <t>Quixote Studio Services - North Valley</t>
+  </si>
+  <si>
+    <t>10252 Norris Ave.  Pacoima CA 91331</t>
+  </si>
+  <si>
+    <t>Quixote Studio Services - Sylmar South</t>
+  </si>
+  <si>
+    <t>13334 Ralston Avenue  Sylmar CA 91342</t>
+  </si>
+  <si>
+    <t>Quixote Studio Services - Sylmar North</t>
+  </si>
+  <si>
+    <t>14002 Balboa  Sylmar CA 91342</t>
   </si>
   <si>
     <r>
@@ -1903,7 +2017,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 09/21/2026</t>
+      <t>07/01/26 to 09/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -1923,7 +2037,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I271.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I293.</t>
     </r>
   </si>
 </sst>
@@ -3119,8 +3233,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I271" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I271" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I293" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I293" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -3541,7 +3655,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>13265</v>
+        <v>13576</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3550,7 +3664,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3577,7 +3691,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3609,7 +3723,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I271"/>
+  <dimension ref="A1:I293"/>
   <sheetFormatPr defaultColWidth="150.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -3625,7 +3739,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>578</v>
+        <v>616</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -7677,7 +7791,7 @@
         <v>338</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>577</v>
+        <v>6</v>
       </c>
       <c r="G141" s="30">
         <v>73</v>
@@ -11457,6 +11571,644 @@
       </c>
       <c r="I271" s="32" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B272" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C272" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D272" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E272" s="28" t="s">
+        <v>577</v>
+      </c>
+      <c r="F272" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G272" s="30">
+        <v>1</v>
+      </c>
+      <c r="H272" s="30" t="s">
+        <v>578</v>
+      </c>
+      <c r="I272" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B273" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C273" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D273" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E273" s="28" t="s">
+        <v>579</v>
+      </c>
+      <c r="F273" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G273" s="30">
+        <v>11</v>
+      </c>
+      <c r="H273" s="30" t="s">
+        <v>580</v>
+      </c>
+      <c r="I273" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B274" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C274" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D274" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E274" s="28" t="s">
+        <v>581</v>
+      </c>
+      <c r="F274" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G274" s="30">
+        <v>22</v>
+      </c>
+      <c r="H274" s="30" t="s">
+        <v>582</v>
+      </c>
+      <c r="I274" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B275" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C275" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D275" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E275" s="28" t="s">
+        <v>581</v>
+      </c>
+      <c r="F275" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G275" s="30">
+        <v>1</v>
+      </c>
+      <c r="H275" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="I275" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B276" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C276" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D276" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E276" s="28" t="s">
+        <v>584</v>
+      </c>
+      <c r="F276" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G276" s="30">
+        <v>2</v>
+      </c>
+      <c r="H276" s="30" t="s">
+        <v>585</v>
+      </c>
+      <c r="I276" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B277" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C277" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D277" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E277" s="28" t="s">
+        <v>586</v>
+      </c>
+      <c r="F277" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G277" s="30">
+        <v>1</v>
+      </c>
+      <c r="H277" s="30" t="s">
+        <v>587</v>
+      </c>
+      <c r="I277" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B278" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C278" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D278" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E278" s="28" t="s">
+        <v>588</v>
+      </c>
+      <c r="F278" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G278" s="30">
+        <v>3</v>
+      </c>
+      <c r="H278" s="30" t="s">
+        <v>589</v>
+      </c>
+      <c r="I278" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B279" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C279" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D279" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E279" s="28" t="s">
+        <v>590</v>
+      </c>
+      <c r="F279" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G279" s="30">
+        <v>20</v>
+      </c>
+      <c r="H279" s="30" t="s">
+        <v>591</v>
+      </c>
+      <c r="I279" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B280" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C280" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D280" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E280" s="28" t="s">
+        <v>581</v>
+      </c>
+      <c r="F280" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G280" s="30">
+        <v>2</v>
+      </c>
+      <c r="H280" s="30" t="s">
+        <v>592</v>
+      </c>
+      <c r="I280" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B281" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C281" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D281" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E281" s="28" t="s">
+        <v>593</v>
+      </c>
+      <c r="F281" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G281" s="30">
+        <v>2</v>
+      </c>
+      <c r="H281" s="30" t="s">
+        <v>594</v>
+      </c>
+      <c r="I281" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A282" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B282" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C282" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D282" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E282" s="28" t="s">
+        <v>595</v>
+      </c>
+      <c r="F282" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G282" s="30">
+        <v>4</v>
+      </c>
+      <c r="H282" s="30" t="s">
+        <v>596</v>
+      </c>
+      <c r="I282" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B283" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C283" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D283" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E283" s="28" t="s">
+        <v>581</v>
+      </c>
+      <c r="F283" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G283" s="30">
+        <v>2</v>
+      </c>
+      <c r="H283" s="30" t="s">
+        <v>597</v>
+      </c>
+      <c r="I283" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B284" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C284" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D284" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E284" s="28" t="s">
+        <v>581</v>
+      </c>
+      <c r="F284" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G284" s="30">
+        <v>1</v>
+      </c>
+      <c r="H284" s="30" t="s">
+        <v>598</v>
+      </c>
+      <c r="I284" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B285" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C285" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D285" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E285" s="28" t="s">
+        <v>599</v>
+      </c>
+      <c r="F285" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G285" s="30">
+        <v>1</v>
+      </c>
+      <c r="H285" s="30" t="s">
+        <v>600</v>
+      </c>
+      <c r="I285" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A286" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B286" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C286" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D286" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E286" s="28" t="s">
+        <v>601</v>
+      </c>
+      <c r="F286" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G286" s="30">
+        <v>2</v>
+      </c>
+      <c r="H286" s="30" t="s">
+        <v>602</v>
+      </c>
+      <c r="I286" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B287" s="29">
+        <v>46286</v>
+      </c>
+      <c r="C287" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D287" s="29">
+        <v>46346</v>
+      </c>
+      <c r="E287" s="28" t="s">
+        <v>603</v>
+      </c>
+      <c r="F287" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G287" s="30">
+        <v>72</v>
+      </c>
+      <c r="H287" s="30" t="s">
+        <v>604</v>
+      </c>
+      <c r="I287" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B288" s="29">
+        <v>46287</v>
+      </c>
+      <c r="C288" s="29">
+        <v>46287</v>
+      </c>
+      <c r="D288" s="29">
+        <v>46353</v>
+      </c>
+      <c r="E288" s="28" t="s">
+        <v>391</v>
+      </c>
+      <c r="F288" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G288" s="30">
+        <v>1</v>
+      </c>
+      <c r="H288" s="30" t="s">
+        <v>605</v>
+      </c>
+      <c r="I288" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B289" s="29">
+        <v>46288</v>
+      </c>
+      <c r="C289" s="29">
+        <v>46288</v>
+      </c>
+      <c r="D289" s="29">
+        <v>46347</v>
+      </c>
+      <c r="E289" s="28" t="s">
+        <v>606</v>
+      </c>
+      <c r="F289" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G289" s="30">
+        <v>106</v>
+      </c>
+      <c r="H289" s="30" t="s">
+        <v>607</v>
+      </c>
+      <c r="I289" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B290" s="29">
+        <v>46280</v>
+      </c>
+      <c r="C290" s="29">
+        <v>46288</v>
+      </c>
+      <c r="D290" s="29">
+        <v>46340</v>
+      </c>
+      <c r="E290" s="28" t="s">
+        <v>608</v>
+      </c>
+      <c r="F290" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G290" s="30">
+        <v>24</v>
+      </c>
+      <c r="H290" s="30" t="s">
+        <v>609</v>
+      </c>
+      <c r="I290" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B291" s="29">
+        <v>46280</v>
+      </c>
+      <c r="C291" s="29">
+        <v>46288</v>
+      </c>
+      <c r="D291" s="29">
+        <v>46340</v>
+      </c>
+      <c r="E291" s="28" t="s">
+        <v>610</v>
+      </c>
+      <c r="F291" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G291" s="30">
+        <v>29</v>
+      </c>
+      <c r="H291" s="30" t="s">
+        <v>611</v>
+      </c>
+      <c r="I291" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B292" s="29">
+        <v>46280</v>
+      </c>
+      <c r="C292" s="29">
+        <v>46288</v>
+      </c>
+      <c r="D292" s="29">
+        <v>46340</v>
+      </c>
+      <c r="E292" s="28" t="s">
+        <v>612</v>
+      </c>
+      <c r="F292" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G292" s="30">
+        <v>3</v>
+      </c>
+      <c r="H292" s="30" t="s">
+        <v>613</v>
+      </c>
+      <c r="I292" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B293" s="29">
+        <v>46280</v>
+      </c>
+      <c r="C293" s="29">
+        <v>46288</v>
+      </c>
+      <c r="D293" s="29">
+        <v>46340</v>
+      </c>
+      <c r="E293" s="28" t="s">
+        <v>614</v>
+      </c>
+      <c r="F293" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G293" s="30">
+        <v>1</v>
+      </c>
+      <c r="H293" s="30" t="s">
+        <v>615</v>
+      </c>
+      <c r="I293" s="32" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -11473,7 +12225,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I271</xm:sqref>
+          <xm:sqref>I3:I293</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12009,7 +12761,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD67808B-C578-46B0-BA38-8B1368DDEF79}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E6DBBA-054B-45F8-9A84-15046247332D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -12028,7 +12780,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3E7DA0C-0FF1-495C-8B3A-B3D0E5B82778}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE16F10D-B753-42CE-8A8A-B1A6B341740E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -12036,17 +12788,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA33669-60E1-43A7-A872-44A5DB367147}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36EA53F4-7FBD-4129-BEA1-73C6FB9B4B41}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
     <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3AECD60-72AD-4932-A777-C7ACE9C50F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E823B74A-78A7-4E69-AAEE-0422C5DA0A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="639">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1856,6 +1856,123 @@
     <t>3186 Airway Ave., Suite F  Costa Mesa CA 92626</t>
   </si>
   <si>
+    <t>Kaiser (1800 Harrison St.)</t>
+  </si>
+  <si>
+    <t>1800 Harrison St.  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>Kaiser (One Kaiser Plaza)</t>
+  </si>
+  <si>
+    <t>One Kaiser Plaza  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>Kaiser</t>
+  </si>
+  <si>
+    <t>4460 Hacienda Dr.  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>3000 S. Robertson Blvd.  Los Angeles CA 90034</t>
+  </si>
+  <si>
+    <t>Kaiser (393 E. Walnut St.)</t>
+  </si>
+  <si>
+    <t>393 E. Walnut St.  Pasadena CA 91188</t>
+  </si>
+  <si>
+    <t>Kaiser (74 N. Pasadena Ave.)</t>
+  </si>
+  <si>
+    <t>74 N. Pasadena Ave.  Pasadena CA 91103</t>
+  </si>
+  <si>
+    <t>Kaiser (75N. Fair Oaks Ave.)</t>
+  </si>
+  <si>
+    <t>75 N. Fair Oaks Ave.  Pasadena CA 91103</t>
+  </si>
+  <si>
+    <t>Kaiser (99 S. Oakland Ave.)</t>
+  </si>
+  <si>
+    <t>99 S. Oakland Ave.  Pasadena CA 91101</t>
+  </si>
+  <si>
+    <t>17836 Gillette Ave.  Irvine CA 92614</t>
+  </si>
+  <si>
+    <t>Kaiser (1830 California Ave.)</t>
+  </si>
+  <si>
+    <t>1830 California Ave.  Corona CA 92881</t>
+  </si>
+  <si>
+    <t>Kaiser (1840 California Ave.)</t>
+  </si>
+  <si>
+    <t>1840 California Ave.  Corona CA 92881</t>
+  </si>
+  <si>
+    <t>50 Iron Point Cir.  Folsom CA 95630</t>
+  </si>
+  <si>
+    <t>3240 Arden Wy.  Sacramento CA 95825</t>
+  </si>
+  <si>
+    <t>Kaiser (17140 Bernardo Center Dr.)</t>
+  </si>
+  <si>
+    <t>17140 Bernardo Center Dr.  San Diego CA 92128</t>
+  </si>
+  <si>
+    <t>Kaiser (3840 Murphy Canyon Rd.)</t>
+  </si>
+  <si>
+    <t>3840 Murphy Canyon Rd.  San Diego CA 92123</t>
+  </si>
+  <si>
+    <t>Kaiser (8954 Rio San Diego Dr.)</t>
+  </si>
+  <si>
+    <t>8954 Rio San Diego Dr.  San Diego CA 92108</t>
+  </si>
+  <si>
+    <t>2000 E El Segundo Blvd  El Segundo CA 90245</t>
+  </si>
+  <si>
+    <t>Capstone Delivery Inc.</t>
+  </si>
+  <si>
+    <t>9350 Rayo Avenue  South Gate CA 90280</t>
+  </si>
+  <si>
+    <t>Quixote Studio Services - North Valley Campus A</t>
+  </si>
+  <si>
+    <t>12137 Montague St.  Pacoima CA 91331</t>
+  </si>
+  <si>
+    <t>Quixote Studio Services - North Valley</t>
+  </si>
+  <si>
+    <t>10252 Norris Ave.  Pacoima CA 91331</t>
+  </si>
+  <si>
+    <t>Quixote Studio Services - Sylmar South</t>
+  </si>
+  <si>
+    <t>13334 Ralston Avenue  Sylmar CA 91342</t>
+  </si>
+  <si>
+    <t>Quixote Studio Services - Sylmar North</t>
+  </si>
+  <si>
+    <t>14002 Balboa  Sylmar CA 91342</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1875,7 +1992,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 09/23/2026
+01/01/2023 - 09/28/2026
 </t>
     </r>
     <r>
@@ -1889,121 +2006,70 @@
     </r>
   </si>
   <si>
-    <t>Kaiser (1800 Harrison St.)</t>
-  </si>
-  <si>
-    <t>1800 Harrison St.  Oakland CA 94612</t>
-  </si>
-  <si>
-    <t>Kaiser (One Kaiser Plaza)</t>
-  </si>
-  <si>
-    <t>One Kaiser Plaza  Oakland CA 94612</t>
-  </si>
-  <si>
-    <t>Kaiser</t>
-  </si>
-  <si>
-    <t>4460 Hacienda Dr.  Pleasanton CA 94588</t>
-  </si>
-  <si>
-    <t>3000 S. Robertson Blvd.  Los Angeles CA 90034</t>
-  </si>
-  <si>
-    <t>Kaiser (393 E. Walnut St.)</t>
-  </si>
-  <si>
-    <t>393 E. Walnut St.  Pasadena CA 91188</t>
-  </si>
-  <si>
-    <t>Kaiser (74 N. Pasadena Ave.)</t>
-  </si>
-  <si>
-    <t>74 N. Pasadena Ave.  Pasadena CA 91103</t>
-  </si>
-  <si>
-    <t>Kaiser (75N. Fair Oaks Ave.)</t>
-  </si>
-  <si>
-    <t>75 N. Fair Oaks Ave.  Pasadena CA 91103</t>
-  </si>
-  <si>
-    <t>Kaiser (99 S. Oakland Ave.)</t>
-  </si>
-  <si>
-    <t>99 S. Oakland Ave.  Pasadena CA 91101</t>
-  </si>
-  <si>
-    <t>17836 Gillette Ave.  Irvine CA 92614</t>
-  </si>
-  <si>
-    <t>Kaiser (1830 California Ave.)</t>
-  </si>
-  <si>
-    <t>1830 California Ave.  Corona CA 92881</t>
-  </si>
-  <si>
-    <t>Kaiser (1840 California Ave.)</t>
-  </si>
-  <si>
-    <t>1840 California Ave.  Corona CA 92881</t>
-  </si>
-  <si>
-    <t>50 Iron Point Cir.  Folsom CA 95630</t>
-  </si>
-  <si>
-    <t>3240 Arden Wy.  Sacramento CA 95825</t>
-  </si>
-  <si>
-    <t>Kaiser (17140 Bernardo Center Dr.)</t>
-  </si>
-  <si>
-    <t>17140 Bernardo Center Dr.  San Diego CA 92128</t>
-  </si>
-  <si>
-    <t>Kaiser (3840 Murphy Canyon Rd.)</t>
-  </si>
-  <si>
-    <t>3840 Murphy Canyon Rd.  San Diego CA 92123</t>
-  </si>
-  <si>
-    <t>Kaiser (8954 Rio San Diego Dr.)</t>
-  </si>
-  <si>
-    <t>8954 Rio San Diego Dr.  San Diego CA 92108</t>
-  </si>
-  <si>
-    <t>2000 E El Segundo Blvd  El Segundo CA 90245</t>
-  </si>
-  <si>
-    <t>Capstone Delivery Inc.</t>
-  </si>
-  <si>
-    <t>9350 Rayo Avenue  South Gate CA 90280</t>
-  </si>
-  <si>
-    <t>Quixote Studio Services - North Valley Campus A</t>
-  </si>
-  <si>
-    <t>12137 Montague St.  Pacoima CA 91331</t>
-  </si>
-  <si>
-    <t>Quixote Studio Services - North Valley</t>
-  </si>
-  <si>
-    <t>10252 Norris Ave.  Pacoima CA 91331</t>
-  </si>
-  <si>
-    <t>Quixote Studio Services - Sylmar South</t>
-  </si>
-  <si>
-    <t>13334 Ralston Avenue  Sylmar CA 91342</t>
-  </si>
-  <si>
-    <t>Quixote Studio Services - Sylmar North</t>
-  </si>
-  <si>
-    <t>14002 Balboa  Sylmar CA 91342</t>
+    <t>Key Energy Services, LLC - Bakersfield Location</t>
+  </si>
+  <si>
+    <t>18835 Highway 65  Bakersfield CA 93308</t>
+  </si>
+  <si>
+    <t>Dreyer's Grand Ice Cream</t>
+  </si>
+  <si>
+    <t>7301 District Boulevard  Bakersfield CA 93313</t>
+  </si>
+  <si>
+    <t>Key Energy Services, LLC - Ventura Location</t>
+  </si>
+  <si>
+    <t>2951 N. Ventura Avenue  Ventura CA 93002</t>
+  </si>
+  <si>
+    <t>City of Hope</t>
+  </si>
+  <si>
+    <t>4900 Rivergrade Road  Irwindale CA 91706</t>
+  </si>
+  <si>
+    <t>SAC Health (1003 East Brier Drive)</t>
+  </si>
+  <si>
+    <t>1003 East Brier Drive  San Bernardino CA 92408</t>
+  </si>
+  <si>
+    <t>SAC Health (250 South G St.)</t>
+  </si>
+  <si>
+    <t>250 South G St.  San Bernardino CA 92410</t>
+  </si>
+  <si>
+    <t>970 E. Continental Ave.  Tulare CA 93274</t>
+  </si>
+  <si>
+    <t>City National Bank - Flower Street</t>
+  </si>
+  <si>
+    <t>555 S. Flower St.  Los Angeles CA 90071</t>
+  </si>
+  <si>
+    <t>City National Bank - Grand Ave.</t>
+  </si>
+  <si>
+    <t>350 S. Grand Ave.  Los Angeles CA 90071</t>
+  </si>
+  <si>
+    <t>Covenant Aviation Security, LLC</t>
+  </si>
+  <si>
+    <t>Highway 101  San Francisco CA 94128</t>
+  </si>
+  <si>
+    <t>Marin County</t>
+  </si>
+  <si>
+    <t>BioMarin Pharmaceutical Inc.</t>
+  </si>
+  <si>
+    <t>105 Digital Drive  Novato CA 94949</t>
   </si>
   <si>
     <r>
@@ -2017,7 +2083,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 09/23/2026</t>
+      <t>07/01/26 to 09/28/2026</t>
     </r>
     <r>
       <rPr>
@@ -2037,7 +2103,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I293.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I305.</t>
     </r>
   </si>
 </sst>
@@ -3233,8 +3299,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I293" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I293" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I305" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I305" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -3655,7 +3721,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>13576</v>
+        <v>15909</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3664,7 +3730,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3682,7 +3748,7 @@
       </c>
       <c r="B6" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Not known at this time")</f>
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3700,7 +3766,7 @@
       </c>
       <c r="B8" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3723,7 +3789,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I293"/>
+  <dimension ref="A1:I305"/>
   <sheetFormatPr defaultColWidth="150.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -3739,7 +3805,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -11587,7 +11653,7 @@
         <v>46346</v>
       </c>
       <c r="E272" s="28" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F272" s="28" t="s">
         <v>6</v>
@@ -11596,7 +11662,7 @@
         <v>1</v>
       </c>
       <c r="H272" s="30" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="I272" s="32" t="s">
         <v>45</v>
@@ -11616,7 +11682,7 @@
         <v>46346</v>
       </c>
       <c r="E273" s="28" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F273" s="28" t="s">
         <v>6</v>
@@ -11625,7 +11691,7 @@
         <v>11</v>
       </c>
       <c r="H273" s="30" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="I273" s="32" t="s">
         <v>45</v>
@@ -11645,7 +11711,7 @@
         <v>46346</v>
       </c>
       <c r="E274" s="28" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F274" s="28" t="s">
         <v>6</v>
@@ -11654,7 +11720,7 @@
         <v>22</v>
       </c>
       <c r="H274" s="30" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="I274" s="32" t="s">
         <v>45</v>
@@ -11674,7 +11740,7 @@
         <v>46346</v>
       </c>
       <c r="E275" s="28" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F275" s="28" t="s">
         <v>6</v>
@@ -11683,7 +11749,7 @@
         <v>1</v>
       </c>
       <c r="H275" s="30" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I275" s="32" t="s">
         <v>45</v>
@@ -11703,7 +11769,7 @@
         <v>46346</v>
       </c>
       <c r="E276" s="28" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F276" s="28" t="s">
         <v>6</v>
@@ -11712,7 +11778,7 @@
         <v>2</v>
       </c>
       <c r="H276" s="30" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="I276" s="32" t="s">
         <v>45</v>
@@ -11732,7 +11798,7 @@
         <v>46346</v>
       </c>
       <c r="E277" s="28" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F277" s="28" t="s">
         <v>6</v>
@@ -11741,7 +11807,7 @@
         <v>1</v>
       </c>
       <c r="H277" s="30" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="I277" s="32" t="s">
         <v>45</v>
@@ -11761,7 +11827,7 @@
         <v>46346</v>
       </c>
       <c r="E278" s="28" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F278" s="28" t="s">
         <v>6</v>
@@ -11770,7 +11836,7 @@
         <v>3</v>
       </c>
       <c r="H278" s="30" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I278" s="32" t="s">
         <v>45</v>
@@ -11790,7 +11856,7 @@
         <v>46346</v>
       </c>
       <c r="E279" s="28" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F279" s="28" t="s">
         <v>6</v>
@@ -11799,7 +11865,7 @@
         <v>20</v>
       </c>
       <c r="H279" s="30" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="I279" s="32" t="s">
         <v>45</v>
@@ -11819,7 +11885,7 @@
         <v>46346</v>
       </c>
       <c r="E280" s="28" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F280" s="28" t="s">
         <v>6</v>
@@ -11828,7 +11894,7 @@
         <v>2</v>
       </c>
       <c r="H280" s="30" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="I280" s="32" t="s">
         <v>45</v>
@@ -11848,7 +11914,7 @@
         <v>46346</v>
       </c>
       <c r="E281" s="28" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F281" s="28" t="s">
         <v>6</v>
@@ -11857,7 +11923,7 @@
         <v>2</v>
       </c>
       <c r="H281" s="30" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="I281" s="32" t="s">
         <v>45</v>
@@ -11877,7 +11943,7 @@
         <v>46346</v>
       </c>
       <c r="E282" s="28" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F282" s="28" t="s">
         <v>6</v>
@@ -11886,7 +11952,7 @@
         <v>4</v>
       </c>
       <c r="H282" s="30" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I282" s="32" t="s">
         <v>45</v>
@@ -11906,7 +11972,7 @@
         <v>46346</v>
       </c>
       <c r="E283" s="28" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F283" s="28" t="s">
         <v>6</v>
@@ -11915,7 +11981,7 @@
         <v>2</v>
       </c>
       <c r="H283" s="30" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="I283" s="32" t="s">
         <v>45</v>
@@ -11935,7 +12001,7 @@
         <v>46346</v>
       </c>
       <c r="E284" s="28" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F284" s="28" t="s">
         <v>6</v>
@@ -11944,7 +12010,7 @@
         <v>1</v>
       </c>
       <c r="H284" s="30" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I284" s="32" t="s">
         <v>45</v>
@@ -11964,7 +12030,7 @@
         <v>46346</v>
       </c>
       <c r="E285" s="28" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F285" s="28" t="s">
         <v>6</v>
@@ -11973,7 +12039,7 @@
         <v>1</v>
       </c>
       <c r="H285" s="30" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="I285" s="32" t="s">
         <v>45</v>
@@ -11993,7 +12059,7 @@
         <v>46346</v>
       </c>
       <c r="E286" s="28" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F286" s="28" t="s">
         <v>6</v>
@@ -12002,7 +12068,7 @@
         <v>2</v>
       </c>
       <c r="H286" s="30" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="I286" s="32" t="s">
         <v>45</v>
@@ -12022,7 +12088,7 @@
         <v>46346</v>
       </c>
       <c r="E287" s="28" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F287" s="28" t="s">
         <v>6</v>
@@ -12031,7 +12097,7 @@
         <v>72</v>
       </c>
       <c r="H287" s="30" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I287" s="32" t="s">
         <v>45</v>
@@ -12060,7 +12126,7 @@
         <v>1</v>
       </c>
       <c r="H288" s="30" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I288" s="32" t="s">
         <v>41</v>
@@ -12080,7 +12146,7 @@
         <v>46347</v>
       </c>
       <c r="E289" s="28" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F289" s="28" t="s">
         <v>52</v>
@@ -12089,7 +12155,7 @@
         <v>106</v>
       </c>
       <c r="H289" s="30" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I289" s="32" t="s">
         <v>37</v>
@@ -12109,7 +12175,7 @@
         <v>46340</v>
       </c>
       <c r="E290" s="28" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F290" s="28" t="s">
         <v>6</v>
@@ -12118,7 +12184,7 @@
         <v>24</v>
       </c>
       <c r="H290" s="30" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I290" s="32" t="s">
         <v>46</v>
@@ -12138,7 +12204,7 @@
         <v>46340</v>
       </c>
       <c r="E291" s="28" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F291" s="28" t="s">
         <v>6</v>
@@ -12147,7 +12213,7 @@
         <v>29</v>
       </c>
       <c r="H291" s="30" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="I291" s="32" t="s">
         <v>46</v>
@@ -12167,7 +12233,7 @@
         <v>46340</v>
       </c>
       <c r="E292" s="28" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F292" s="28" t="s">
         <v>6</v>
@@ -12176,7 +12242,7 @@
         <v>3</v>
       </c>
       <c r="H292" s="30" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="I292" s="32" t="s">
         <v>46</v>
@@ -12196,7 +12262,7 @@
         <v>46340</v>
       </c>
       <c r="E293" s="28" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F293" s="28" t="s">
         <v>6</v>
@@ -12205,10 +12271,358 @@
         <v>1</v>
       </c>
       <c r="H293" s="30" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="I293" s="32" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B294" s="29">
+        <v>46288</v>
+      </c>
+      <c r="C294" s="29">
+        <v>46289</v>
+      </c>
+      <c r="D294" s="29">
+        <v>46348</v>
+      </c>
+      <c r="E294" s="28" t="s">
+        <v>616</v>
+      </c>
+      <c r="F294" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G294" s="30">
+        <v>53</v>
+      </c>
+      <c r="H294" s="30" t="s">
+        <v>617</v>
+      </c>
+      <c r="I294" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B295" s="29">
+        <v>46289</v>
+      </c>
+      <c r="C295" s="29">
+        <v>46289</v>
+      </c>
+      <c r="D295" s="29">
+        <v>46345</v>
+      </c>
+      <c r="E295" s="28" t="s">
+        <v>618</v>
+      </c>
+      <c r="F295" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G295" s="30">
+        <v>426</v>
+      </c>
+      <c r="H295" s="30" t="s">
+        <v>619</v>
+      </c>
+      <c r="I295" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B296" s="29">
+        <v>46288</v>
+      </c>
+      <c r="C296" s="29">
+        <v>46289</v>
+      </c>
+      <c r="D296" s="29">
+        <v>46348</v>
+      </c>
+      <c r="E296" s="28" t="s">
+        <v>620</v>
+      </c>
+      <c r="F296" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G296" s="30">
+        <v>4</v>
+      </c>
+      <c r="H296" s="30" t="s">
+        <v>621</v>
+      </c>
+      <c r="I296" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B297" s="29">
+        <v>46288</v>
+      </c>
+      <c r="C297" s="29">
+        <v>46289</v>
+      </c>
+      <c r="D297" s="29">
+        <v>46350</v>
+      </c>
+      <c r="E297" s="28" t="s">
+        <v>622</v>
+      </c>
+      <c r="F297" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G297" s="30">
+        <v>73</v>
+      </c>
+      <c r="H297" s="30" t="s">
+        <v>623</v>
+      </c>
+      <c r="I297" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B298" s="29">
+        <v>46287</v>
+      </c>
+      <c r="C298" s="29">
+        <v>46289</v>
+      </c>
+      <c r="D298" s="29">
+        <v>46293</v>
+      </c>
+      <c r="E298" s="28" t="s">
+        <v>624</v>
+      </c>
+      <c r="F298" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G298" s="30">
+        <v>42</v>
+      </c>
+      <c r="H298" s="30" t="s">
+        <v>625</v>
+      </c>
+      <c r="I298" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B299" s="29">
+        <v>46287</v>
+      </c>
+      <c r="C299" s="29">
+        <v>46289</v>
+      </c>
+      <c r="D299" s="29">
+        <v>46293</v>
+      </c>
+      <c r="E299" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="F299" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G299" s="30">
+        <v>9</v>
+      </c>
+      <c r="H299" s="30" t="s">
+        <v>627</v>
+      </c>
+      <c r="I299" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B300" s="29">
+        <v>46289</v>
+      </c>
+      <c r="C300" s="29">
+        <v>46289</v>
+      </c>
+      <c r="D300" s="29">
+        <v>46348</v>
+      </c>
+      <c r="E300" s="28" t="s">
+        <v>618</v>
+      </c>
+      <c r="F300" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G300" s="30">
+        <v>90</v>
+      </c>
+      <c r="H300" s="30" t="s">
+        <v>628</v>
+      </c>
+      <c r="I300" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B301" s="29">
+        <v>46287</v>
+      </c>
+      <c r="C301" s="29">
+        <v>46290</v>
+      </c>
+      <c r="D301" s="29">
+        <v>46345</v>
+      </c>
+      <c r="E301" s="28" t="s">
+        <v>618</v>
+      </c>
+      <c r="F301" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G301" s="30">
+        <v>221</v>
+      </c>
+      <c r="H301" s="30" t="s">
+        <v>619</v>
+      </c>
+      <c r="I301" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B302" s="29">
+        <v>46289</v>
+      </c>
+      <c r="C302" s="29">
+        <v>46290</v>
+      </c>
+      <c r="D302" s="29">
+        <v>46349</v>
+      </c>
+      <c r="E302" s="28" t="s">
+        <v>629</v>
+      </c>
+      <c r="F302" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G302" s="30">
+        <v>4</v>
+      </c>
+      <c r="H302" s="30" t="s">
+        <v>630</v>
+      </c>
+      <c r="I302" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B303" s="29">
+        <v>46289</v>
+      </c>
+      <c r="C303" s="29">
+        <v>46290</v>
+      </c>
+      <c r="D303" s="29">
+        <v>46349</v>
+      </c>
+      <c r="E303" s="28" t="s">
+        <v>631</v>
+      </c>
+      <c r="F303" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G303" s="30">
+        <v>15</v>
+      </c>
+      <c r="H303" s="30" t="s">
+        <v>632</v>
+      </c>
+      <c r="I303" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B304" s="29">
+        <v>46293</v>
+      </c>
+      <c r="C304" s="29">
+        <v>46293</v>
+      </c>
+      <c r="D304" s="29">
+        <v>46356</v>
+      </c>
+      <c r="E304" s="28" t="s">
+        <v>633</v>
+      </c>
+      <c r="F304" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G304" s="30">
+        <v>1279</v>
+      </c>
+      <c r="H304" s="30" t="s">
+        <v>634</v>
+      </c>
+      <c r="I304" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" s="28" t="s">
+        <v>635</v>
+      </c>
+      <c r="B305" s="29">
+        <v>46289</v>
+      </c>
+      <c r="C305" s="29">
+        <v>46293</v>
+      </c>
+      <c r="D305" s="29">
+        <v>46360</v>
+      </c>
+      <c r="E305" s="28" t="s">
+        <v>636</v>
+      </c>
+      <c r="F305" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G305" s="30">
+        <v>117</v>
+      </c>
+      <c r="H305" s="30" t="s">
+        <v>637</v>
+      </c>
+      <c r="I305" s="32" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -12225,7 +12639,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I293</xm:sqref>
+          <xm:sqref>I3:I305</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12346,7 +12760,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>576</v>
+        <v>615</v>
       </c>
       <c r="E1"/>
     </row>
@@ -12761,7 +13175,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E6DBBA-054B-45F8-9A84-15046247332D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{202114B2-B4C7-4DBF-9F73-E14E8E209566}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -12780,7 +13194,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE16F10D-B753-42CE-8A8A-B1A6B341740E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54E8684A-C4C3-4B91-9CDE-763B0A462F40}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -12788,17 +13202,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36EA53F4-7FBD-4129-BEA1-73C6FB9B4B41}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAF17A57-25F4-4A94-85EE-ED09DEE3C1C6}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E823B74A-78A7-4E69-AAEE-0422C5DA0A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0171CBA-2858-45DD-9D42-832A6C8771C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="703">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1973,6 +1973,72 @@
     <t>14002 Balboa  Sylmar CA 91342</t>
   </si>
   <si>
+    <t>Key Energy Services, LLC - Bakersfield Location</t>
+  </si>
+  <si>
+    <t>18835 Highway 65  Bakersfield CA 93308</t>
+  </si>
+  <si>
+    <t>Dreyer's Grand Ice Cream</t>
+  </si>
+  <si>
+    <t>7301 District Boulevard  Bakersfield CA 93313</t>
+  </si>
+  <si>
+    <t>Key Energy Services, LLC - Ventura Location</t>
+  </si>
+  <si>
+    <t>2951 N. Ventura Avenue  Ventura CA 93002</t>
+  </si>
+  <si>
+    <t>City of Hope</t>
+  </si>
+  <si>
+    <t>4900 Rivergrade Road  Irwindale CA 91706</t>
+  </si>
+  <si>
+    <t>SAC Health (1003 East Brier Drive)</t>
+  </si>
+  <si>
+    <t>1003 East Brier Drive  San Bernardino CA 92408</t>
+  </si>
+  <si>
+    <t>SAC Health (250 South G St.)</t>
+  </si>
+  <si>
+    <t>250 South G St.  San Bernardino CA 92410</t>
+  </si>
+  <si>
+    <t>970 E. Continental Ave.  Tulare CA 93274</t>
+  </si>
+  <si>
+    <t>City National Bank - Flower Street</t>
+  </si>
+  <si>
+    <t>555 S. Flower St.  Los Angeles CA 90071</t>
+  </si>
+  <si>
+    <t>City National Bank - Grand Ave.</t>
+  </si>
+  <si>
+    <t>350 S. Grand Ave.  Los Angeles CA 90071</t>
+  </si>
+  <si>
+    <t>Covenant Aviation Security, LLC</t>
+  </si>
+  <si>
+    <t>Highway 101  San Francisco CA 94128</t>
+  </si>
+  <si>
+    <t>Marin County</t>
+  </si>
+  <si>
+    <t>BioMarin Pharmaceutical Inc.</t>
+  </si>
+  <si>
+    <t>105 Digital Drive  Novato CA 94949</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1992,7 +2058,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 09/28/2026
+01/01/2023 - 09/30/2026
 </t>
     </r>
     <r>
@@ -2006,70 +2072,196 @@
     </r>
   </si>
   <si>
-    <t>Key Energy Services, LLC - Bakersfield Location</t>
-  </si>
-  <si>
-    <t>18835 Highway 65  Bakersfield CA 93308</t>
-  </si>
-  <si>
-    <t>Dreyer's Grand Ice Cream</t>
-  </si>
-  <si>
-    <t>7301 District Boulevard  Bakersfield CA 93313</t>
-  </si>
-  <si>
-    <t>Key Energy Services, LLC - Ventura Location</t>
-  </si>
-  <si>
-    <t>2951 N. Ventura Avenue  Ventura CA 93002</t>
-  </si>
-  <si>
-    <t>City of Hope</t>
-  </si>
-  <si>
-    <t>4900 Rivergrade Road  Irwindale CA 91706</t>
-  </si>
-  <si>
-    <t>SAC Health (1003 East Brier Drive)</t>
-  </si>
-  <si>
-    <t>1003 East Brier Drive  San Bernardino CA 92408</t>
-  </si>
-  <si>
-    <t>SAC Health (250 South G St.)</t>
-  </si>
-  <si>
-    <t>250 South G St.  San Bernardino CA 92410</t>
-  </si>
-  <si>
-    <t>970 E. Continental Ave.  Tulare CA 93274</t>
-  </si>
-  <si>
-    <t>City National Bank - Flower Street</t>
-  </si>
-  <si>
-    <t>555 S. Flower St.  Los Angeles CA 90071</t>
-  </si>
-  <si>
-    <t>City National Bank - Grand Ave.</t>
-  </si>
-  <si>
-    <t>350 S. Grand Ave.  Los Angeles CA 90071</t>
-  </si>
-  <si>
-    <t>Covenant Aviation Security, LLC</t>
-  </si>
-  <si>
-    <t>Highway 101  San Francisco CA 94128</t>
-  </si>
-  <si>
-    <t>Marin County</t>
-  </si>
-  <si>
-    <t>BioMarin Pharmaceutical Inc.</t>
-  </si>
-  <si>
-    <t>105 Digital Drive  Novato CA 94949</t>
+    <t>Randstad Inhouse Services, LLC (Dreyer's)</t>
+  </si>
+  <si>
+    <t>Workday Inc.</t>
+  </si>
+  <si>
+    <t>6110 Stoneridge Mall Road  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (1060 N Eastern Ave.)</t>
+  </si>
+  <si>
+    <t>1060 N Eastern Ave.  Los Angeles CA 90063</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (1104 N. Eastern Ave.)</t>
+  </si>
+  <si>
+    <t>1104 N. Eastern Ave.  Los Angeles CA 90063</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (11515 S. Colima Rd.)</t>
+  </si>
+  <si>
+    <t>11515 S. Colima Rd.  Whittier CA 90604</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (11700 S. Alameda St.)</t>
+  </si>
+  <si>
+    <t>11700 S. Alameda St.  Lynwood CA 90262</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (11703 S. Alameda St.)</t>
+  </si>
+  <si>
+    <t>11703 S. Alameda St.  Lynwood CA 90262</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (11703 W. Alameda St.)</t>
+  </si>
+  <si>
+    <t>11703 W. Alameda St.  Lynwood CA 90262</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (12335 Civic Center Dr.)</t>
+  </si>
+  <si>
+    <t>12335 Civic Center Dr.  Norwalk CA 90650</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (1310 W Imperial Hwy)</t>
+  </si>
+  <si>
+    <t>1310 W Imperial Hwy  Los Angeles CA 90044</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (13483 Fiji Way)</t>
+  </si>
+  <si>
+    <t>13483 Fiji Way  Marina Del Rey CA 90242</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (1445 McKinley Ave.)</t>
+  </si>
+  <si>
+    <t>1445 McKinley Ave.  Pomona CA 91767</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (150 N Hudson Ave.)</t>
+  </si>
+  <si>
+    <t>150 N Hudson Ave.  Industry CA 91774</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (21356 S. Avalon Blvd.)</t>
+  </si>
+  <si>
+    <t>21356 S. Avalon Blvd.  Carson CA 90745</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (21695 Valley Blvd.)</t>
+  </si>
+  <si>
+    <t>21695 Valley Blvd.  Walnut CA 91789</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (26123 S. Narbonne Ave.)</t>
+  </si>
+  <si>
+    <t>26123 S. Narbonne Ave.  Lomita CA 90717</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (26201 Golden Valley Rd.)</t>
+  </si>
+  <si>
+    <t>26201 Golden Valley Rd.  Santa Clarita CA 91350</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (270 S. Walnut Ave.)</t>
+  </si>
+  <si>
+    <t>270 S. Walnut Ave.  San Dimas CA 91773</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (270 W. Walnut Ave.)</t>
+  </si>
+  <si>
+    <t>270 W. Walnut Ave.  San Dimas CA 91773</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (27050 Agoura Rd.)</t>
+  </si>
+  <si>
+    <t>27050 Agoura Rd.  Agoura CA 91301</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (29380 The Old Road)</t>
+  </si>
+  <si>
+    <t>29380 The Old Road  Castaic CA 91310</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (441 Bauchet St.)</t>
+  </si>
+  <si>
+    <t>441 Bauchet St.  Los Angeles CA 90012</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (4554 N. Briggs Ave.)</t>
+  </si>
+  <si>
+    <t>4554 N. Briggs Ave.  La Crescenta CA 91214</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (501 W. Lancaster Blvd.)</t>
+  </si>
+  <si>
+    <t>501 W. Lancaster Blvd.  Lancaster CA 93534</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (5019 E 3rd St.)</t>
+  </si>
+  <si>
+    <t>5019 E 3rd St.  Los Angeles CA 90022</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (5130 N. Clark Ave.)</t>
+  </si>
+  <si>
+    <t>5130 N. Clark Ave.  Lakewood CA 90712</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (6631 S Passons Ave.)</t>
+  </si>
+  <si>
+    <t>6631 S Passons Ave.  Pico Riva CA 90660</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (750 E Ave Q)</t>
+  </si>
+  <si>
+    <t>750 E Ave Q  Palmdale CA 93550</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (780 N. San Vicenta Blvd.)</t>
+  </si>
+  <si>
+    <t>780 N. San Vicenta Blvd.  W. Hollywood CA 90069</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (8838 E. Las Tunas Dr.)</t>
+  </si>
+  <si>
+    <t>8838 E. Las Tunas Dr.  Temple City CA 90069</t>
+  </si>
+  <si>
+    <t>970 E Continental Ave  Tulare CA 93274</t>
+  </si>
+  <si>
+    <t>DLVR (A Corp)</t>
+  </si>
+  <si>
+    <t>5750 Mesmer Avenue  Culver City CA 90230</t>
+  </si>
+  <si>
+    <t>McKinley Paper and Packaging Company</t>
+  </si>
+  <si>
+    <t>13012 Midway Place  Cerritos CA 90703</t>
   </si>
   <si>
     <r>
@@ -2083,7 +2275,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 09/28/2026</t>
+      <t>07/01/26 to 09/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -2103,7 +2295,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I305.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I339.</t>
     </r>
   </si>
 </sst>
@@ -3299,8 +3491,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I305" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I305" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I339" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I339" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -3721,7 +3913,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>15909</v>
+        <v>16524</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3730,7 +3922,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>193</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3757,7 +3949,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3766,7 +3958,7 @@
       </c>
       <c r="B8" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3789,7 +3981,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I305"/>
+  <dimension ref="A1:I339"/>
   <sheetFormatPr defaultColWidth="150.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -3805,7 +3997,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>638</v>
+        <v>702</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -12291,7 +12483,7 @@
         <v>46348</v>
       </c>
       <c r="E294" s="28" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F294" s="28" t="s">
         <v>101</v>
@@ -12300,7 +12492,7 @@
         <v>53</v>
       </c>
       <c r="H294" s="30" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="I294" s="32" t="s">
         <v>31</v>
@@ -12320,7 +12512,7 @@
         <v>46345</v>
       </c>
       <c r="E295" s="28" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="F295" s="28" t="s">
         <v>101</v>
@@ -12329,7 +12521,7 @@
         <v>426</v>
       </c>
       <c r="H295" s="30" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I295" s="32" t="s">
         <v>34</v>
@@ -12349,7 +12541,7 @@
         <v>46348</v>
       </c>
       <c r="E296" s="28" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F296" s="28" t="s">
         <v>101</v>
@@ -12358,7 +12550,7 @@
         <v>4</v>
       </c>
       <c r="H296" s="30" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I296" s="32" t="s">
         <v>31</v>
@@ -12378,7 +12570,7 @@
         <v>46350</v>
       </c>
       <c r="E297" s="28" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F297" s="28" t="s">
         <v>6</v>
@@ -12387,7 +12579,7 @@
         <v>73</v>
       </c>
       <c r="H297" s="30" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="I297" s="32" t="s">
         <v>45</v>
@@ -12407,7 +12599,7 @@
         <v>46293</v>
       </c>
       <c r="E298" s="28" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F298" s="28" t="s">
         <v>6</v>
@@ -12416,7 +12608,7 @@
         <v>42</v>
       </c>
       <c r="H298" s="30" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I298" s="32" t="s">
         <v>45</v>
@@ -12436,7 +12628,7 @@
         <v>46293</v>
       </c>
       <c r="E299" s="28" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F299" s="28" t="s">
         <v>6</v>
@@ -12445,7 +12637,7 @@
         <v>9</v>
       </c>
       <c r="H299" s="30" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I299" s="32" t="s">
         <v>45</v>
@@ -12465,7 +12657,7 @@
         <v>46348</v>
       </c>
       <c r="E300" s="28" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="F300" s="28" t="s">
         <v>101</v>
@@ -12474,7 +12666,7 @@
         <v>90</v>
       </c>
       <c r="H300" s="30" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I300" s="32" t="s">
         <v>34</v>
@@ -12494,7 +12686,7 @@
         <v>46345</v>
       </c>
       <c r="E301" s="28" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F301" s="28" t="s">
         <v>101</v>
@@ -12503,7 +12695,7 @@
         <v>221</v>
       </c>
       <c r="H301" s="30" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I301" s="32" t="s">
         <v>34</v>
@@ -12523,7 +12715,7 @@
         <v>46349</v>
       </c>
       <c r="E302" s="28" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F302" s="28" t="s">
         <v>506</v>
@@ -12532,7 +12724,7 @@
         <v>4</v>
       </c>
       <c r="H302" s="30" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="I302" s="32" t="s">
         <v>39</v>
@@ -12552,7 +12744,7 @@
         <v>46349</v>
       </c>
       <c r="E303" s="28" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F303" s="28" t="s">
         <v>506</v>
@@ -12561,7 +12753,7 @@
         <v>15</v>
       </c>
       <c r="H303" s="30" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="I303" s="32" t="s">
         <v>39</v>
@@ -12581,7 +12773,7 @@
         <v>46356</v>
       </c>
       <c r="E304" s="28" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F304" s="28" t="s">
         <v>6</v>
@@ -12590,7 +12782,7 @@
         <v>1279</v>
       </c>
       <c r="H304" s="30" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="I304" s="32" t="s">
         <v>43</v>
@@ -12598,7 +12790,7 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="28" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B305" s="29">
         <v>46289</v>
@@ -12610,7 +12802,7 @@
         <v>46360</v>
       </c>
       <c r="E305" s="28" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F305" s="28" t="s">
         <v>6</v>
@@ -12619,9 +12811,995 @@
         <v>117</v>
       </c>
       <c r="H305" s="30" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="I305" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B306" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C306" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D306" s="29">
+        <v>46356</v>
+      </c>
+      <c r="E306" s="28" t="s">
+        <v>639</v>
+      </c>
+      <c r="F306" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G306" s="30">
+        <v>142</v>
+      </c>
+      <c r="H306" s="30" t="s">
+        <v>640</v>
+      </c>
+      <c r="I306" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B307" s="29">
+        <v>46293</v>
+      </c>
+      <c r="C307" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D307" s="29">
+        <v>46325</v>
+      </c>
+      <c r="E307" s="28" t="s">
+        <v>321</v>
+      </c>
+      <c r="F307" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G307" s="30">
+        <v>2</v>
+      </c>
+      <c r="H307" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="I307" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B308" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C308" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D308" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E308" s="28" t="s">
+        <v>641</v>
+      </c>
+      <c r="F308" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G308" s="30">
+        <v>5</v>
+      </c>
+      <c r="H308" s="30" t="s">
+        <v>642</v>
+      </c>
+      <c r="I308" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B309" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C309" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D309" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E309" s="28" t="s">
+        <v>643</v>
+      </c>
+      <c r="F309" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G309" s="30">
+        <v>5</v>
+      </c>
+      <c r="H309" s="30" t="s">
+        <v>644</v>
+      </c>
+      <c r="I309" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B310" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C310" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D310" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E310" s="28" t="s">
+        <v>645</v>
+      </c>
+      <c r="F310" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G310" s="30">
+        <v>5</v>
+      </c>
+      <c r="H310" s="30" t="s">
+        <v>646</v>
+      </c>
+      <c r="I310" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B311" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C311" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D311" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E311" s="28" t="s">
+        <v>647</v>
+      </c>
+      <c r="F311" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G311" s="30">
+        <v>5</v>
+      </c>
+      <c r="H311" s="30" t="s">
+        <v>648</v>
+      </c>
+      <c r="I311" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B312" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C312" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D312" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E312" s="28" t="s">
+        <v>649</v>
+      </c>
+      <c r="F312" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G312" s="30">
+        <v>5</v>
+      </c>
+      <c r="H312" s="30" t="s">
+        <v>650</v>
+      </c>
+      <c r="I312" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B313" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C313" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D313" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E313" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F313" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G313" s="30">
+        <v>5</v>
+      </c>
+      <c r="H313" s="30" t="s">
+        <v>652</v>
+      </c>
+      <c r="I313" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B314" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C314" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D314" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E314" s="28" t="s">
+        <v>653</v>
+      </c>
+      <c r="F314" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G314" s="30">
+        <v>5</v>
+      </c>
+      <c r="H314" s="30" t="s">
+        <v>654</v>
+      </c>
+      <c r="I314" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B315" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C315" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D315" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E315" s="28" t="s">
+        <v>655</v>
+      </c>
+      <c r="F315" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G315" s="30">
+        <v>5</v>
+      </c>
+      <c r="H315" s="30" t="s">
+        <v>656</v>
+      </c>
+      <c r="I315" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B316" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C316" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D316" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E316" s="28" t="s">
+        <v>657</v>
+      </c>
+      <c r="F316" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G316" s="30">
+        <v>5</v>
+      </c>
+      <c r="H316" s="30" t="s">
+        <v>658</v>
+      </c>
+      <c r="I316" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B317" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C317" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D317" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E317" s="28" t="s">
+        <v>659</v>
+      </c>
+      <c r="F317" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G317" s="30">
+        <v>5</v>
+      </c>
+      <c r="H317" s="30" t="s">
+        <v>660</v>
+      </c>
+      <c r="I317" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B318" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C318" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D318" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E318" s="28" t="s">
+        <v>661</v>
+      </c>
+      <c r="F318" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G318" s="30">
+        <v>5</v>
+      </c>
+      <c r="H318" s="30" t="s">
+        <v>662</v>
+      </c>
+      <c r="I318" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B319" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C319" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D319" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E319" s="28" t="s">
+        <v>663</v>
+      </c>
+      <c r="F319" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G319" s="30">
+        <v>5</v>
+      </c>
+      <c r="H319" s="30" t="s">
+        <v>664</v>
+      </c>
+      <c r="I319" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B320" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C320" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D320" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E320" s="28" t="s">
+        <v>665</v>
+      </c>
+      <c r="F320" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G320" s="30">
+        <v>5</v>
+      </c>
+      <c r="H320" s="30" t="s">
+        <v>666</v>
+      </c>
+      <c r="I320" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B321" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C321" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D321" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E321" s="28" t="s">
+        <v>667</v>
+      </c>
+      <c r="F321" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G321" s="30">
+        <v>5</v>
+      </c>
+      <c r="H321" s="30" t="s">
+        <v>668</v>
+      </c>
+      <c r="I321" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B322" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C322" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D322" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E322" s="28" t="s">
+        <v>669</v>
+      </c>
+      <c r="F322" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G322" s="30">
+        <v>5</v>
+      </c>
+      <c r="H322" s="30" t="s">
+        <v>670</v>
+      </c>
+      <c r="I322" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B323" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C323" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D323" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E323" s="28" t="s">
+        <v>671</v>
+      </c>
+      <c r="F323" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G323" s="30">
+        <v>5</v>
+      </c>
+      <c r="H323" s="30" t="s">
+        <v>672</v>
+      </c>
+      <c r="I323" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B324" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C324" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D324" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E324" s="28" t="s">
+        <v>673</v>
+      </c>
+      <c r="F324" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G324" s="30">
+        <v>5</v>
+      </c>
+      <c r="H324" s="30" t="s">
+        <v>674</v>
+      </c>
+      <c r="I324" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B325" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C325" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D325" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E325" s="28" t="s">
+        <v>675</v>
+      </c>
+      <c r="F325" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G325" s="30">
+        <v>5</v>
+      </c>
+      <c r="H325" s="30" t="s">
+        <v>676</v>
+      </c>
+      <c r="I325" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B326" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C326" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D326" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E326" s="28" t="s">
+        <v>677</v>
+      </c>
+      <c r="F326" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G326" s="30">
+        <v>5</v>
+      </c>
+      <c r="H326" s="30" t="s">
+        <v>678</v>
+      </c>
+      <c r="I326" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B327" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C327" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D327" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E327" s="28" t="s">
+        <v>679</v>
+      </c>
+      <c r="F327" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G327" s="30">
+        <v>5</v>
+      </c>
+      <c r="H327" s="30" t="s">
+        <v>680</v>
+      </c>
+      <c r="I327" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B328" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C328" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D328" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E328" s="28" t="s">
+        <v>681</v>
+      </c>
+      <c r="F328" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G328" s="30">
+        <v>5</v>
+      </c>
+      <c r="H328" s="30" t="s">
+        <v>682</v>
+      </c>
+      <c r="I328" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B329" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C329" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D329" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E329" s="28" t="s">
+        <v>683</v>
+      </c>
+      <c r="F329" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G329" s="30">
+        <v>5</v>
+      </c>
+      <c r="H329" s="30" t="s">
+        <v>684</v>
+      </c>
+      <c r="I329" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B330" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C330" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D330" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E330" s="28" t="s">
+        <v>685</v>
+      </c>
+      <c r="F330" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G330" s="30">
+        <v>5</v>
+      </c>
+      <c r="H330" s="30" t="s">
+        <v>686</v>
+      </c>
+      <c r="I330" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B331" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C331" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D331" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E331" s="28" t="s">
+        <v>687</v>
+      </c>
+      <c r="F331" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G331" s="30">
+        <v>5</v>
+      </c>
+      <c r="H331" s="30" t="s">
+        <v>688</v>
+      </c>
+      <c r="I331" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B332" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C332" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D332" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E332" s="28" t="s">
+        <v>687</v>
+      </c>
+      <c r="F332" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G332" s="30">
+        <v>5</v>
+      </c>
+      <c r="H332" s="30" t="s">
+        <v>688</v>
+      </c>
+      <c r="I332" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B333" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C333" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D333" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E333" s="28" t="s">
+        <v>689</v>
+      </c>
+      <c r="F333" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G333" s="30">
+        <v>5</v>
+      </c>
+      <c r="H333" s="30" t="s">
+        <v>690</v>
+      </c>
+      <c r="I333" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B334" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C334" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D334" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E334" s="28" t="s">
+        <v>691</v>
+      </c>
+      <c r="F334" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G334" s="30">
+        <v>5</v>
+      </c>
+      <c r="H334" s="30" t="s">
+        <v>692</v>
+      </c>
+      <c r="I334" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B335" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C335" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D335" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E335" s="28" t="s">
+        <v>693</v>
+      </c>
+      <c r="F335" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G335" s="30">
+        <v>5</v>
+      </c>
+      <c r="H335" s="30" t="s">
+        <v>694</v>
+      </c>
+      <c r="I335" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B336" s="29">
+        <v>46294</v>
+      </c>
+      <c r="C336" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D336" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E336" s="28" t="s">
+        <v>695</v>
+      </c>
+      <c r="F336" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G336" s="30">
+        <v>5</v>
+      </c>
+      <c r="H336" s="30" t="s">
+        <v>696</v>
+      </c>
+      <c r="I336" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B337" s="29">
+        <v>46287</v>
+      </c>
+      <c r="C337" s="29">
+        <v>46294</v>
+      </c>
+      <c r="D337" s="29">
+        <v>46345</v>
+      </c>
+      <c r="E337" s="28" t="s">
+        <v>617</v>
+      </c>
+      <c r="F337" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G337" s="30">
+        <v>221</v>
+      </c>
+      <c r="H337" s="30" t="s">
+        <v>697</v>
+      </c>
+      <c r="I337" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B338" s="29">
+        <v>46295</v>
+      </c>
+      <c r="C338" s="29">
+        <v>46295</v>
+      </c>
+      <c r="D338" s="29">
+        <v>46360</v>
+      </c>
+      <c r="E338" s="28" t="s">
+        <v>698</v>
+      </c>
+      <c r="F338" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G338" s="30">
+        <v>60</v>
+      </c>
+      <c r="H338" s="30" t="s">
+        <v>699</v>
+      </c>
+      <c r="I338" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B339" s="29">
+        <v>46293</v>
+      </c>
+      <c r="C339" s="29">
+        <v>46295</v>
+      </c>
+      <c r="D339" s="29">
+        <v>46356</v>
+      </c>
+      <c r="E339" s="28" t="s">
+        <v>700</v>
+      </c>
+      <c r="F339" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G339" s="30">
+        <v>45</v>
+      </c>
+      <c r="H339" s="30" t="s">
+        <v>701</v>
+      </c>
+      <c r="I339" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -12639,7 +13817,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I305</xm:sqref>
+          <xm:sqref>I3:I339</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12760,7 +13938,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>615</v>
+        <v>637</v>
       </c>
       <c r="E1"/>
     </row>
@@ -13166,16 +14344,16 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="82b749e3-8208-459a-bfc0-9b428d09cbab">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{202114B2-B4C7-4DBF-9F73-E14E8E209566}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E0365A6-CA18-4710-8AB7-938B618E02BB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -13194,7 +14372,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54E8684A-C4C3-4B91-9CDE-763B0A462F40}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409F4C10-51CA-4BD9-8067-110BF64D8B09}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -13202,18 +14380,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAF17A57-25F4-4A94-85EE-ED09DEE3C1C6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E18836B1-4FB4-4BD2-B5FA-2B8E83B417EF}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0171CBA-2858-45DD-9D42-832A6C8771C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F8E3BBB-AF9D-4458-8634-226398412DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="723">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2039,6 +2039,290 @@
     <t>105 Digital Drive  Novato CA 94949</t>
   </si>
   <si>
+    <t>Randstad Inhouse Services, LLC (Dreyer's)</t>
+  </si>
+  <si>
+    <t>Workday Inc.</t>
+  </si>
+  <si>
+    <t>6110 Stoneridge Mall Road  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (1060 N Eastern Ave.)</t>
+  </si>
+  <si>
+    <t>1060 N Eastern Ave.  Los Angeles CA 90063</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (1104 N. Eastern Ave.)</t>
+  </si>
+  <si>
+    <t>1104 N. Eastern Ave.  Los Angeles CA 90063</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (11515 S. Colima Rd.)</t>
+  </si>
+  <si>
+    <t>11515 S. Colima Rd.  Whittier CA 90604</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (11700 S. Alameda St.)</t>
+  </si>
+  <si>
+    <t>11700 S. Alameda St.  Lynwood CA 90262</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (11703 S. Alameda St.)</t>
+  </si>
+  <si>
+    <t>11703 S. Alameda St.  Lynwood CA 90262</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (11703 W. Alameda St.)</t>
+  </si>
+  <si>
+    <t>11703 W. Alameda St.  Lynwood CA 90262</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (12335 Civic Center Dr.)</t>
+  </si>
+  <si>
+    <t>12335 Civic Center Dr.  Norwalk CA 90650</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (1310 W Imperial Hwy)</t>
+  </si>
+  <si>
+    <t>1310 W Imperial Hwy  Los Angeles CA 90044</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (13483 Fiji Way)</t>
+  </si>
+  <si>
+    <t>13483 Fiji Way  Marina Del Rey CA 90242</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (1445 McKinley Ave.)</t>
+  </si>
+  <si>
+    <t>1445 McKinley Ave.  Pomona CA 91767</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (150 N Hudson Ave.)</t>
+  </si>
+  <si>
+    <t>150 N Hudson Ave.  Industry CA 91774</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (21356 S. Avalon Blvd.)</t>
+  </si>
+  <si>
+    <t>21356 S. Avalon Blvd.  Carson CA 90745</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (21695 Valley Blvd.)</t>
+  </si>
+  <si>
+    <t>21695 Valley Blvd.  Walnut CA 91789</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (26123 S. Narbonne Ave.)</t>
+  </si>
+  <si>
+    <t>26123 S. Narbonne Ave.  Lomita CA 90717</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (26201 Golden Valley Rd.)</t>
+  </si>
+  <si>
+    <t>26201 Golden Valley Rd.  Santa Clarita CA 91350</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (270 S. Walnut Ave.)</t>
+  </si>
+  <si>
+    <t>270 S. Walnut Ave.  San Dimas CA 91773</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (270 W. Walnut Ave.)</t>
+  </si>
+  <si>
+    <t>270 W. Walnut Ave.  San Dimas CA 91773</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (27050 Agoura Rd.)</t>
+  </si>
+  <si>
+    <t>27050 Agoura Rd.  Agoura CA 91301</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (29380 The Old Road)</t>
+  </si>
+  <si>
+    <t>29380 The Old Road  Castaic CA 91310</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (441 Bauchet St.)</t>
+  </si>
+  <si>
+    <t>441 Bauchet St.  Los Angeles CA 90012</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (4554 N. Briggs Ave.)</t>
+  </si>
+  <si>
+    <t>4554 N. Briggs Ave.  La Crescenta CA 91214</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (501 W. Lancaster Blvd.)</t>
+  </si>
+  <si>
+    <t>501 W. Lancaster Blvd.  Lancaster CA 93534</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (5019 E 3rd St.)</t>
+  </si>
+  <si>
+    <t>5019 E 3rd St.  Los Angeles CA 90022</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (5130 N. Clark Ave.)</t>
+  </si>
+  <si>
+    <t>5130 N. Clark Ave.  Lakewood CA 90712</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (6631 S Passons Ave.)</t>
+  </si>
+  <si>
+    <t>6631 S Passons Ave.  Pico Riva CA 90660</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (750 E Ave Q)</t>
+  </si>
+  <si>
+    <t>750 E Ave Q  Palmdale CA 93550</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (780 N. San Vicenta Blvd.)</t>
+  </si>
+  <si>
+    <t>780 N. San Vicenta Blvd.  W. Hollywood CA 90069</t>
+  </si>
+  <si>
+    <t>Constellis, LLC (8838 E. Las Tunas Dr.)</t>
+  </si>
+  <si>
+    <t>8838 E. Las Tunas Dr.  Temple City CA 90069</t>
+  </si>
+  <si>
+    <t>970 E Continental Ave  Tulare CA 93274</t>
+  </si>
+  <si>
+    <t>DLVR (A Corp)</t>
+  </si>
+  <si>
+    <t>5750 Mesmer Avenue  Culver City CA 90230</t>
+  </si>
+  <si>
+    <t>McKinley Paper and Packaging Company</t>
+  </si>
+  <si>
+    <t>13012 Midway Place  Cerritos CA 90703</t>
+  </si>
+  <si>
+    <t>Becton, Dickinson and Company (BD)</t>
+  </si>
+  <si>
+    <t>3750 Torrey View Court  San Diego CA 92130</t>
+  </si>
+  <si>
+    <t>TruFusion West Hollywood LLC</t>
+  </si>
+  <si>
+    <t>904 North La Brea Avenue  Los Angeles CA 90038</t>
+  </si>
+  <si>
+    <t>Monroe Operations, LLC, dba Newport Healthcare - Pimlico</t>
+  </si>
+  <si>
+    <t>10813 Pimlico Dr.  Moorpark CA 93021</t>
+  </si>
+  <si>
+    <t>Monroe Operations, LLC, dba Newport Healthcare - Alhambra</t>
+  </si>
+  <si>
+    <t>2565 Alhambra Court  Santa Rosa Valley CA 93012</t>
+  </si>
+  <si>
+    <t>Monroe Operations, LLC, dba Newport Healthcare - Presilla</t>
+  </si>
+  <si>
+    <t>11530 Presilla Rd.  Santa Rosa Valley CA 93012</t>
+  </si>
+  <si>
+    <t>Monroe Operations, LLC, dba Newport Healthcare - Read</t>
+  </si>
+  <si>
+    <t>4914 Read Rd.  Moorpark CA 93021</t>
+  </si>
+  <si>
+    <t>Monroe Operations, LLC, dba Newport Healthcare - Valley Vista</t>
+  </si>
+  <si>
+    <t>683 Valley Vista Dr.  Camarillo CA 93010</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals and Kaiser Foundation Health Plan, Inc.</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals and Kaiser Foundation Health Plan, Inc. (74 N. Pasadena Ave.)</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals and Kaiser Foundation Health Plan, Inc. (393 E. Walnut St.)</t>
+  </si>
+  <si>
+    <t>AMF Bowling Centers, Inc. Castle Park</t>
+  </si>
+  <si>
+    <t>3500 Polk Street  Riverside CA 92505</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">WARN REPORT - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>07/01/26 to 10/06/2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I354.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2058,7 +2342,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 09/30/2026
+01/01/2023 - 10/06/2026
 </t>
     </r>
     <r>
@@ -2072,231 +2356,7 @@
     </r>
   </si>
   <si>
-    <t>Randstad Inhouse Services, LLC (Dreyer's)</t>
-  </si>
-  <si>
-    <t>Workday Inc.</t>
-  </si>
-  <si>
-    <t>6110 Stoneridge Mall Road  Pleasanton CA 94588</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (1060 N Eastern Ave.)</t>
-  </si>
-  <si>
-    <t>1060 N Eastern Ave.  Los Angeles CA 90063</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (1104 N. Eastern Ave.)</t>
-  </si>
-  <si>
-    <t>1104 N. Eastern Ave.  Los Angeles CA 90063</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (11515 S. Colima Rd.)</t>
-  </si>
-  <si>
-    <t>11515 S. Colima Rd.  Whittier CA 90604</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (11700 S. Alameda St.)</t>
-  </si>
-  <si>
-    <t>11700 S. Alameda St.  Lynwood CA 90262</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (11703 S. Alameda St.)</t>
-  </si>
-  <si>
-    <t>11703 S. Alameda St.  Lynwood CA 90262</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (11703 W. Alameda St.)</t>
-  </si>
-  <si>
-    <t>11703 W. Alameda St.  Lynwood CA 90262</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (12335 Civic Center Dr.)</t>
-  </si>
-  <si>
-    <t>12335 Civic Center Dr.  Norwalk CA 90650</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (1310 W Imperial Hwy)</t>
-  </si>
-  <si>
-    <t>1310 W Imperial Hwy  Los Angeles CA 90044</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (13483 Fiji Way)</t>
-  </si>
-  <si>
-    <t>13483 Fiji Way  Marina Del Rey CA 90242</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (1445 McKinley Ave.)</t>
-  </si>
-  <si>
-    <t>1445 McKinley Ave.  Pomona CA 91767</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (150 N Hudson Ave.)</t>
-  </si>
-  <si>
-    <t>150 N Hudson Ave.  Industry CA 91774</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (21356 S. Avalon Blvd.)</t>
-  </si>
-  <si>
-    <t>21356 S. Avalon Blvd.  Carson CA 90745</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (21695 Valley Blvd.)</t>
-  </si>
-  <si>
-    <t>21695 Valley Blvd.  Walnut CA 91789</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (26123 S. Narbonne Ave.)</t>
-  </si>
-  <si>
-    <t>26123 S. Narbonne Ave.  Lomita CA 90717</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (26201 Golden Valley Rd.)</t>
-  </si>
-  <si>
-    <t>26201 Golden Valley Rd.  Santa Clarita CA 91350</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (270 S. Walnut Ave.)</t>
-  </si>
-  <si>
-    <t>270 S. Walnut Ave.  San Dimas CA 91773</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (270 W. Walnut Ave.)</t>
-  </si>
-  <si>
-    <t>270 W. Walnut Ave.  San Dimas CA 91773</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (27050 Agoura Rd.)</t>
-  </si>
-  <si>
-    <t>27050 Agoura Rd.  Agoura CA 91301</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (29380 The Old Road)</t>
-  </si>
-  <si>
-    <t>29380 The Old Road  Castaic CA 91310</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (441 Bauchet St.)</t>
-  </si>
-  <si>
-    <t>441 Bauchet St.  Los Angeles CA 90012</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (4554 N. Briggs Ave.)</t>
-  </si>
-  <si>
-    <t>4554 N. Briggs Ave.  La Crescenta CA 91214</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (501 W. Lancaster Blvd.)</t>
-  </si>
-  <si>
-    <t>501 W. Lancaster Blvd.  Lancaster CA 93534</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (5019 E 3rd St.)</t>
-  </si>
-  <si>
-    <t>5019 E 3rd St.  Los Angeles CA 90022</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (5130 N. Clark Ave.)</t>
-  </si>
-  <si>
-    <t>5130 N. Clark Ave.  Lakewood CA 90712</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (6631 S Passons Ave.)</t>
-  </si>
-  <si>
-    <t>6631 S Passons Ave.  Pico Riva CA 90660</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (750 E Ave Q)</t>
-  </si>
-  <si>
-    <t>750 E Ave Q  Palmdale CA 93550</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (780 N. San Vicenta Blvd.)</t>
-  </si>
-  <si>
-    <t>780 N. San Vicenta Blvd.  W. Hollywood CA 90069</t>
-  </si>
-  <si>
-    <t>Constellis, LLC (8838 E. Las Tunas Dr.)</t>
-  </si>
-  <si>
-    <t>8838 E. Las Tunas Dr.  Temple City CA 90069</t>
-  </si>
-  <si>
-    <t>970 E Continental Ave  Tulare CA 93274</t>
-  </si>
-  <si>
-    <t>DLVR (A Corp)</t>
-  </si>
-  <si>
-    <t>5750 Mesmer Avenue  Culver City CA 90230</t>
-  </si>
-  <si>
-    <t>McKinley Paper and Packaging Company</t>
-  </si>
-  <si>
-    <t>13012 Midway Place  Cerritos CA 90703</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">WARN REPORT - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>07/01/26 to 09/30/2026</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I339.</t>
-    </r>
+    <t>Relocation</t>
   </si>
 </sst>
 </file>
@@ -2559,7 +2619,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2697,6 +2757,24 @@
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -3491,8 +3569,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I339" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I339" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I354" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I354" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -3913,7 +3991,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>16524</v>
+        <v>16885</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3922,7 +4000,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>224</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3949,7 +4027,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3981,7 +4059,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I339"/>
+  <dimension ref="A1:I354"/>
   <sheetFormatPr defaultColWidth="150.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -3997,7 +4075,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>702</v>
+        <v>720</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -8049,7 +8127,7 @@
         <v>338</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>6</v>
+        <v>722</v>
       </c>
       <c r="G141" s="30">
         <v>73</v>
@@ -12512,7 +12590,7 @@
         <v>46345</v>
       </c>
       <c r="E295" s="28" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F295" s="28" t="s">
         <v>101</v>
@@ -12657,7 +12735,7 @@
         <v>46348</v>
       </c>
       <c r="E300" s="28" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F300" s="28" t="s">
         <v>101</v>
@@ -12831,7 +12909,7 @@
         <v>46356</v>
       </c>
       <c r="E306" s="28" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F306" s="28" t="s">
         <v>6</v>
@@ -12840,7 +12918,7 @@
         <v>142</v>
       </c>
       <c r="H306" s="30" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I306" s="32" t="s">
         <v>38</v>
@@ -12889,16 +12967,16 @@
         <v>46326</v>
       </c>
       <c r="E308" s="28" t="s">
+        <v>640</v>
+      </c>
+      <c r="F308" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G308" s="30">
+        <v>5</v>
+      </c>
+      <c r="H308" s="30" t="s">
         <v>641</v>
-      </c>
-      <c r="F308" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G308" s="30">
-        <v>5</v>
-      </c>
-      <c r="H308" s="30" t="s">
-        <v>642</v>
       </c>
       <c r="I308" s="32" t="s">
         <v>43</v>
@@ -12918,16 +12996,16 @@
         <v>46326</v>
       </c>
       <c r="E309" s="28" t="s">
+        <v>642</v>
+      </c>
+      <c r="F309" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G309" s="30">
+        <v>5</v>
+      </c>
+      <c r="H309" s="30" t="s">
         <v>643</v>
-      </c>
-      <c r="F309" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G309" s="30">
-        <v>5</v>
-      </c>
-      <c r="H309" s="30" t="s">
-        <v>644</v>
       </c>
       <c r="I309" s="32" t="s">
         <v>43</v>
@@ -12947,16 +13025,16 @@
         <v>46326</v>
       </c>
       <c r="E310" s="28" t="s">
+        <v>644</v>
+      </c>
+      <c r="F310" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G310" s="30">
+        <v>5</v>
+      </c>
+      <c r="H310" s="30" t="s">
         <v>645</v>
-      </c>
-      <c r="F310" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G310" s="30">
-        <v>5</v>
-      </c>
-      <c r="H310" s="30" t="s">
-        <v>646</v>
       </c>
       <c r="I310" s="32" t="s">
         <v>43</v>
@@ -12976,16 +13054,16 @@
         <v>46326</v>
       </c>
       <c r="E311" s="28" t="s">
+        <v>646</v>
+      </c>
+      <c r="F311" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G311" s="30">
+        <v>5</v>
+      </c>
+      <c r="H311" s="30" t="s">
         <v>647</v>
-      </c>
-      <c r="F311" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G311" s="30">
-        <v>5</v>
-      </c>
-      <c r="H311" s="30" t="s">
-        <v>648</v>
       </c>
       <c r="I311" s="32" t="s">
         <v>43</v>
@@ -13005,16 +13083,16 @@
         <v>46326</v>
       </c>
       <c r="E312" s="28" t="s">
+        <v>648</v>
+      </c>
+      <c r="F312" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G312" s="30">
+        <v>5</v>
+      </c>
+      <c r="H312" s="30" t="s">
         <v>649</v>
-      </c>
-      <c r="F312" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G312" s="30">
-        <v>5</v>
-      </c>
-      <c r="H312" s="30" t="s">
-        <v>650</v>
       </c>
       <c r="I312" s="32" t="s">
         <v>43</v>
@@ -13034,16 +13112,16 @@
         <v>46326</v>
       </c>
       <c r="E313" s="28" t="s">
+        <v>650</v>
+      </c>
+      <c r="F313" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G313" s="30">
+        <v>5</v>
+      </c>
+      <c r="H313" s="30" t="s">
         <v>651</v>
-      </c>
-      <c r="F313" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G313" s="30">
-        <v>5</v>
-      </c>
-      <c r="H313" s="30" t="s">
-        <v>652</v>
       </c>
       <c r="I313" s="32" t="s">
         <v>43</v>
@@ -13063,16 +13141,16 @@
         <v>46326</v>
       </c>
       <c r="E314" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F314" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G314" s="30">
+        <v>5</v>
+      </c>
+      <c r="H314" s="30" t="s">
         <v>653</v>
-      </c>
-      <c r="F314" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G314" s="30">
-        <v>5</v>
-      </c>
-      <c r="H314" s="30" t="s">
-        <v>654</v>
       </c>
       <c r="I314" s="32" t="s">
         <v>43</v>
@@ -13092,16 +13170,16 @@
         <v>46326</v>
       </c>
       <c r="E315" s="28" t="s">
+        <v>654</v>
+      </c>
+      <c r="F315" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G315" s="30">
+        <v>5</v>
+      </c>
+      <c r="H315" s="30" t="s">
         <v>655</v>
-      </c>
-      <c r="F315" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G315" s="30">
-        <v>5</v>
-      </c>
-      <c r="H315" s="30" t="s">
-        <v>656</v>
       </c>
       <c r="I315" s="32" t="s">
         <v>43</v>
@@ -13121,16 +13199,16 @@
         <v>46326</v>
       </c>
       <c r="E316" s="28" t="s">
+        <v>656</v>
+      </c>
+      <c r="F316" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G316" s="30">
+        <v>5</v>
+      </c>
+      <c r="H316" s="30" t="s">
         <v>657</v>
-      </c>
-      <c r="F316" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G316" s="30">
-        <v>5</v>
-      </c>
-      <c r="H316" s="30" t="s">
-        <v>658</v>
       </c>
       <c r="I316" s="32" t="s">
         <v>43</v>
@@ -13150,16 +13228,16 @@
         <v>46326</v>
       </c>
       <c r="E317" s="28" t="s">
+        <v>658</v>
+      </c>
+      <c r="F317" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G317" s="30">
+        <v>5</v>
+      </c>
+      <c r="H317" s="30" t="s">
         <v>659</v>
-      </c>
-      <c r="F317" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G317" s="30">
-        <v>5</v>
-      </c>
-      <c r="H317" s="30" t="s">
-        <v>660</v>
       </c>
       <c r="I317" s="32" t="s">
         <v>43</v>
@@ -13179,16 +13257,16 @@
         <v>46326</v>
       </c>
       <c r="E318" s="28" t="s">
+        <v>660</v>
+      </c>
+      <c r="F318" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G318" s="30">
+        <v>5</v>
+      </c>
+      <c r="H318" s="30" t="s">
         <v>661</v>
-      </c>
-      <c r="F318" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G318" s="30">
-        <v>5</v>
-      </c>
-      <c r="H318" s="30" t="s">
-        <v>662</v>
       </c>
       <c r="I318" s="32" t="s">
         <v>43</v>
@@ -13208,16 +13286,16 @@
         <v>46326</v>
       </c>
       <c r="E319" s="28" t="s">
+        <v>662</v>
+      </c>
+      <c r="F319" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G319" s="30">
+        <v>5</v>
+      </c>
+      <c r="H319" s="30" t="s">
         <v>663</v>
-      </c>
-      <c r="F319" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G319" s="30">
-        <v>5</v>
-      </c>
-      <c r="H319" s="30" t="s">
-        <v>664</v>
       </c>
       <c r="I319" s="32" t="s">
         <v>43</v>
@@ -13237,16 +13315,16 @@
         <v>46326</v>
       </c>
       <c r="E320" s="28" t="s">
+        <v>664</v>
+      </c>
+      <c r="F320" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G320" s="30">
+        <v>5</v>
+      </c>
+      <c r="H320" s="30" t="s">
         <v>665</v>
-      </c>
-      <c r="F320" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G320" s="30">
-        <v>5</v>
-      </c>
-      <c r="H320" s="30" t="s">
-        <v>666</v>
       </c>
       <c r="I320" s="32" t="s">
         <v>43</v>
@@ -13266,16 +13344,16 @@
         <v>46326</v>
       </c>
       <c r="E321" s="28" t="s">
+        <v>666</v>
+      </c>
+      <c r="F321" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G321" s="30">
+        <v>5</v>
+      </c>
+      <c r="H321" s="30" t="s">
         <v>667</v>
-      </c>
-      <c r="F321" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G321" s="30">
-        <v>5</v>
-      </c>
-      <c r="H321" s="30" t="s">
-        <v>668</v>
       </c>
       <c r="I321" s="32" t="s">
         <v>43</v>
@@ -13295,16 +13373,16 @@
         <v>46326</v>
       </c>
       <c r="E322" s="28" t="s">
+        <v>668</v>
+      </c>
+      <c r="F322" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G322" s="30">
+        <v>5</v>
+      </c>
+      <c r="H322" s="30" t="s">
         <v>669</v>
-      </c>
-      <c r="F322" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G322" s="30">
-        <v>5</v>
-      </c>
-      <c r="H322" s="30" t="s">
-        <v>670</v>
       </c>
       <c r="I322" s="32" t="s">
         <v>43</v>
@@ -13324,16 +13402,16 @@
         <v>46326</v>
       </c>
       <c r="E323" s="28" t="s">
+        <v>670</v>
+      </c>
+      <c r="F323" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G323" s="30">
+        <v>5</v>
+      </c>
+      <c r="H323" s="30" t="s">
         <v>671</v>
-      </c>
-      <c r="F323" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G323" s="30">
-        <v>5</v>
-      </c>
-      <c r="H323" s="30" t="s">
-        <v>672</v>
       </c>
       <c r="I323" s="32" t="s">
         <v>43</v>
@@ -13353,16 +13431,16 @@
         <v>46326</v>
       </c>
       <c r="E324" s="28" t="s">
+        <v>672</v>
+      </c>
+      <c r="F324" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G324" s="30">
+        <v>5</v>
+      </c>
+      <c r="H324" s="30" t="s">
         <v>673</v>
-      </c>
-      <c r="F324" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G324" s="30">
-        <v>5</v>
-      </c>
-      <c r="H324" s="30" t="s">
-        <v>674</v>
       </c>
       <c r="I324" s="32" t="s">
         <v>43</v>
@@ -13382,16 +13460,16 @@
         <v>46326</v>
       </c>
       <c r="E325" s="28" t="s">
+        <v>674</v>
+      </c>
+      <c r="F325" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G325" s="30">
+        <v>5</v>
+      </c>
+      <c r="H325" s="30" t="s">
         <v>675</v>
-      </c>
-      <c r="F325" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G325" s="30">
-        <v>5</v>
-      </c>
-      <c r="H325" s="30" t="s">
-        <v>676</v>
       </c>
       <c r="I325" s="32" t="s">
         <v>43</v>
@@ -13411,16 +13489,16 @@
         <v>46326</v>
       </c>
       <c r="E326" s="28" t="s">
+        <v>676</v>
+      </c>
+      <c r="F326" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G326" s="30">
+        <v>5</v>
+      </c>
+      <c r="H326" s="30" t="s">
         <v>677</v>
-      </c>
-      <c r="F326" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G326" s="30">
-        <v>5</v>
-      </c>
-      <c r="H326" s="30" t="s">
-        <v>678</v>
       </c>
       <c r="I326" s="32" t="s">
         <v>43</v>
@@ -13440,16 +13518,16 @@
         <v>46326</v>
       </c>
       <c r="E327" s="28" t="s">
+        <v>678</v>
+      </c>
+      <c r="F327" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G327" s="30">
+        <v>5</v>
+      </c>
+      <c r="H327" s="30" t="s">
         <v>679</v>
-      </c>
-      <c r="F327" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G327" s="30">
-        <v>5</v>
-      </c>
-      <c r="H327" s="30" t="s">
-        <v>680</v>
       </c>
       <c r="I327" s="32" t="s">
         <v>43</v>
@@ -13469,16 +13547,16 @@
         <v>46326</v>
       </c>
       <c r="E328" s="28" t="s">
+        <v>680</v>
+      </c>
+      <c r="F328" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G328" s="30">
+        <v>5</v>
+      </c>
+      <c r="H328" s="30" t="s">
         <v>681</v>
-      </c>
-      <c r="F328" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G328" s="30">
-        <v>5</v>
-      </c>
-      <c r="H328" s="30" t="s">
-        <v>682</v>
       </c>
       <c r="I328" s="32" t="s">
         <v>43</v>
@@ -13498,16 +13576,16 @@
         <v>46326</v>
       </c>
       <c r="E329" s="28" t="s">
+        <v>682</v>
+      </c>
+      <c r="F329" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G329" s="30">
+        <v>5</v>
+      </c>
+      <c r="H329" s="30" t="s">
         <v>683</v>
-      </c>
-      <c r="F329" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G329" s="30">
-        <v>5</v>
-      </c>
-      <c r="H329" s="30" t="s">
-        <v>684</v>
       </c>
       <c r="I329" s="32" t="s">
         <v>43</v>
@@ -13527,16 +13605,16 @@
         <v>46326</v>
       </c>
       <c r="E330" s="28" t="s">
+        <v>684</v>
+      </c>
+      <c r="F330" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G330" s="30">
+        <v>5</v>
+      </c>
+      <c r="H330" s="30" t="s">
         <v>685</v>
-      </c>
-      <c r="F330" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G330" s="30">
-        <v>5</v>
-      </c>
-      <c r="H330" s="30" t="s">
-        <v>686</v>
       </c>
       <c r="I330" s="32" t="s">
         <v>43</v>
@@ -13556,16 +13634,16 @@
         <v>46326</v>
       </c>
       <c r="E331" s="28" t="s">
+        <v>686</v>
+      </c>
+      <c r="F331" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G331" s="30">
+        <v>5</v>
+      </c>
+      <c r="H331" s="30" t="s">
         <v>687</v>
-      </c>
-      <c r="F331" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G331" s="30">
-        <v>5</v>
-      </c>
-      <c r="H331" s="30" t="s">
-        <v>688</v>
       </c>
       <c r="I331" s="32" t="s">
         <v>43</v>
@@ -13585,16 +13663,16 @@
         <v>46326</v>
       </c>
       <c r="E332" s="28" t="s">
+        <v>686</v>
+      </c>
+      <c r="F332" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G332" s="30">
+        <v>5</v>
+      </c>
+      <c r="H332" s="30" t="s">
         <v>687</v>
-      </c>
-      <c r="F332" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G332" s="30">
-        <v>5</v>
-      </c>
-      <c r="H332" s="30" t="s">
-        <v>688</v>
       </c>
       <c r="I332" s="32" t="s">
         <v>43</v>
@@ -13614,16 +13692,16 @@
         <v>46326</v>
       </c>
       <c r="E333" s="28" t="s">
+        <v>688</v>
+      </c>
+      <c r="F333" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G333" s="30">
+        <v>5</v>
+      </c>
+      <c r="H333" s="30" t="s">
         <v>689</v>
-      </c>
-      <c r="F333" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G333" s="30">
-        <v>5</v>
-      </c>
-      <c r="H333" s="30" t="s">
-        <v>690</v>
       </c>
       <c r="I333" s="32" t="s">
         <v>43</v>
@@ -13643,16 +13721,16 @@
         <v>46326</v>
       </c>
       <c r="E334" s="28" t="s">
+        <v>690</v>
+      </c>
+      <c r="F334" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G334" s="30">
+        <v>5</v>
+      </c>
+      <c r="H334" s="30" t="s">
         <v>691</v>
-      </c>
-      <c r="F334" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G334" s="30">
-        <v>5</v>
-      </c>
-      <c r="H334" s="30" t="s">
-        <v>692</v>
       </c>
       <c r="I334" s="32" t="s">
         <v>43</v>
@@ -13672,16 +13750,16 @@
         <v>46326</v>
       </c>
       <c r="E335" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="F335" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G335" s="30">
+        <v>5</v>
+      </c>
+      <c r="H335" s="30" t="s">
         <v>693</v>
-      </c>
-      <c r="F335" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G335" s="30">
-        <v>5</v>
-      </c>
-      <c r="H335" s="30" t="s">
-        <v>694</v>
       </c>
       <c r="I335" s="32" t="s">
         <v>43</v>
@@ -13701,16 +13779,16 @@
         <v>46326</v>
       </c>
       <c r="E336" s="28" t="s">
+        <v>694</v>
+      </c>
+      <c r="F336" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G336" s="30">
+        <v>5</v>
+      </c>
+      <c r="H336" s="30" t="s">
         <v>695</v>
-      </c>
-      <c r="F336" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G336" s="30">
-        <v>5</v>
-      </c>
-      <c r="H336" s="30" t="s">
-        <v>696</v>
       </c>
       <c r="I336" s="32" t="s">
         <v>43</v>
@@ -13739,7 +13817,7 @@
         <v>221</v>
       </c>
       <c r="H337" s="30" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="I337" s="32" t="s">
         <v>34</v>
@@ -13759,7 +13837,7 @@
         <v>46360</v>
       </c>
       <c r="E338" s="28" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F338" s="28" t="s">
         <v>52</v>
@@ -13768,7 +13846,7 @@
         <v>60</v>
       </c>
       <c r="H338" s="30" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="I338" s="32" t="s">
         <v>37</v>
@@ -13788,7 +13866,7 @@
         <v>46356</v>
       </c>
       <c r="E339" s="28" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F339" s="28" t="s">
         <v>52</v>
@@ -13797,10 +13875,445 @@
         <v>45</v>
       </c>
       <c r="H339" s="30" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="I339" s="32" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="B340" s="41">
+        <v>46289</v>
+      </c>
+      <c r="C340" s="41">
+        <v>46296</v>
+      </c>
+      <c r="D340" s="41">
+        <v>46266</v>
+      </c>
+      <c r="E340" s="49" t="s">
+        <v>701</v>
+      </c>
+      <c r="F340" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="G340" s="50">
+        <v>85</v>
+      </c>
+      <c r="H340" s="51" t="s">
+        <v>702</v>
+      </c>
+      <c r="I340" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B341" s="41">
+        <v>46296</v>
+      </c>
+      <c r="C341" s="41">
+        <v>46297</v>
+      </c>
+      <c r="D341" s="41">
+        <v>46356</v>
+      </c>
+      <c r="E341" s="49" t="s">
+        <v>703</v>
+      </c>
+      <c r="F341" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="G341" s="50">
+        <v>92</v>
+      </c>
+      <c r="H341" s="51" t="s">
+        <v>704</v>
+      </c>
+      <c r="I341" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B342" s="41">
+        <v>46296</v>
+      </c>
+      <c r="C342" s="41">
+        <v>46297</v>
+      </c>
+      <c r="D342" s="41">
+        <v>46357</v>
+      </c>
+      <c r="E342" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="F342" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="G342" s="50">
+        <v>5</v>
+      </c>
+      <c r="H342" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="I342" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B343" s="45">
+        <v>46297</v>
+      </c>
+      <c r="C343" s="45">
+        <v>46297</v>
+      </c>
+      <c r="D343" s="45">
+        <v>46360</v>
+      </c>
+      <c r="E343" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="F343" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G343" s="30">
+        <v>3</v>
+      </c>
+      <c r="H343" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="I343" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="B344" s="41">
+        <v>46295</v>
+      </c>
+      <c r="C344" s="41">
+        <v>46297</v>
+      </c>
+      <c r="D344" s="41">
+        <v>46295</v>
+      </c>
+      <c r="E344" s="49" t="s">
+        <v>705</v>
+      </c>
+      <c r="F344" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="G344" s="50">
+        <v>3</v>
+      </c>
+      <c r="H344" s="51" t="s">
+        <v>706</v>
+      </c>
+      <c r="I344" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="B345" s="45">
+        <v>46295</v>
+      </c>
+      <c r="C345" s="45">
+        <v>46297</v>
+      </c>
+      <c r="D345" s="45">
+        <v>46295</v>
+      </c>
+      <c r="E345" s="52" t="s">
+        <v>707</v>
+      </c>
+      <c r="F345" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="G345" s="54">
+        <v>5</v>
+      </c>
+      <c r="H345" s="53" t="s">
+        <v>708</v>
+      </c>
+      <c r="I345" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="B346" s="41">
+        <v>46295</v>
+      </c>
+      <c r="C346" s="41">
+        <v>46297</v>
+      </c>
+      <c r="D346" s="41">
+        <v>46295</v>
+      </c>
+      <c r="E346" s="49" t="s">
+        <v>709</v>
+      </c>
+      <c r="F346" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="G346" s="50">
+        <v>8</v>
+      </c>
+      <c r="H346" s="51" t="s">
+        <v>710</v>
+      </c>
+      <c r="I346" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="B347" s="45">
+        <v>46295</v>
+      </c>
+      <c r="C347" s="45">
+        <v>46297</v>
+      </c>
+      <c r="D347" s="45">
+        <v>46295</v>
+      </c>
+      <c r="E347" s="52" t="s">
+        <v>711</v>
+      </c>
+      <c r="F347" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="G347" s="54">
+        <v>6</v>
+      </c>
+      <c r="H347" s="53" t="s">
+        <v>712</v>
+      </c>
+      <c r="I347" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="B348" s="41">
+        <v>46295</v>
+      </c>
+      <c r="C348" s="41">
+        <v>46297</v>
+      </c>
+      <c r="D348" s="41">
+        <v>46295</v>
+      </c>
+      <c r="E348" s="49" t="s">
+        <v>713</v>
+      </c>
+      <c r="F348" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="G348" s="50">
+        <v>18</v>
+      </c>
+      <c r="H348" s="51" t="s">
+        <v>714</v>
+      </c>
+      <c r="I348" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A349" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B349" s="45">
+        <v>46300</v>
+      </c>
+      <c r="C349" s="45">
+        <v>46300</v>
+      </c>
+      <c r="D349" s="45">
+        <v>46360</v>
+      </c>
+      <c r="E349" s="52" t="s">
+        <v>715</v>
+      </c>
+      <c r="F349" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="G349" s="54">
+        <v>1</v>
+      </c>
+      <c r="H349" s="53" t="s">
+        <v>579</v>
+      </c>
+      <c r="I349" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A350" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B350" s="41">
+        <v>46300</v>
+      </c>
+      <c r="C350" s="41">
+        <v>46300</v>
+      </c>
+      <c r="D350" s="41">
+        <v>46360</v>
+      </c>
+      <c r="E350" s="49" t="s">
+        <v>715</v>
+      </c>
+      <c r="F350" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="G350" s="50">
+        <v>2</v>
+      </c>
+      <c r="H350" s="51" t="s">
+        <v>581</v>
+      </c>
+      <c r="I350" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A351" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B351" s="41">
+        <v>46300</v>
+      </c>
+      <c r="C351" s="41">
+        <v>46300</v>
+      </c>
+      <c r="D351" s="41">
+        <v>46360</v>
+      </c>
+      <c r="E351" s="49" t="s">
+        <v>716</v>
+      </c>
+      <c r="F351" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="G351" s="50">
+        <v>1</v>
+      </c>
+      <c r="H351" s="51" t="s">
+        <v>586</v>
+      </c>
+      <c r="I351" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A352" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B352" s="45">
+        <v>46300</v>
+      </c>
+      <c r="C352" s="45">
+        <v>46300</v>
+      </c>
+      <c r="D352" s="45">
+        <v>46360</v>
+      </c>
+      <c r="E352" s="52" t="s">
+        <v>717</v>
+      </c>
+      <c r="F352" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="G352" s="54">
+        <v>1</v>
+      </c>
+      <c r="H352" s="53" t="s">
+        <v>584</v>
+      </c>
+      <c r="I352" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A353" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="B353" s="41">
+        <v>46300</v>
+      </c>
+      <c r="C353" s="41">
+        <v>46300</v>
+      </c>
+      <c r="D353" s="41">
+        <v>46360</v>
+      </c>
+      <c r="E353" s="49" t="s">
+        <v>715</v>
+      </c>
+      <c r="F353" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="G353" s="50">
+        <v>1</v>
+      </c>
+      <c r="H353" s="51" t="s">
+        <v>603</v>
+      </c>
+      <c r="I353" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="B354" s="41">
+        <v>46300</v>
+      </c>
+      <c r="C354" s="41">
+        <v>46300</v>
+      </c>
+      <c r="D354" s="41">
+        <v>46360</v>
+      </c>
+      <c r="E354" s="49" t="s">
+        <v>718</v>
+      </c>
+      <c r="F354" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="G354" s="50">
+        <v>130</v>
+      </c>
+      <c r="H354" s="51" t="s">
+        <v>719</v>
+      </c>
+      <c r="I354" s="32" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -13817,7 +14330,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I339</xm:sqref>
+          <xm:sqref>I3:I354</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -13938,7 +14451,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>637</v>
+        <v>721</v>
       </c>
       <c r="E1"/>
     </row>
@@ -14353,7 +14866,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E0365A6-CA18-4710-8AB7-938B618E02BB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A98A5496-6405-46D2-AEE4-9AE3F9C2111C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -14372,7 +14885,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409F4C10-51CA-4BD9-8067-110BF64D8B09}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7408BBD4-1E66-4167-890F-91293CA5CD70}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -14380,18 +14893,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E18836B1-4FB4-4BD2-B5FA-2B8E83B417EF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D6C677-D447-4EFB-8A81-433F3B9E70FF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F8E3BBB-AF9D-4458-8634-226398412DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{8EA63960-EED8-4D37-B183-BC467431938F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66D0C2BD-7D03-4B69-87E4-B9EE9F122930}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1851" uniqueCount="733">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2289,6 +2289,69 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WARN REPORT -</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+01/01/2023 - 10/07/2026
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through H3.</t>
+    </r>
+  </si>
+  <si>
+    <t>Caribou Biosciences, Inc.</t>
+  </si>
+  <si>
+    <t>2929 7th Street, Ste 105  Berkeley CA 94710</t>
+  </si>
+  <si>
+    <t>Cayuga Home for Children</t>
+  </si>
+  <si>
+    <t>8616 La Tijera Boulevard  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>Neogen Care Home Health Agency</t>
+  </si>
+  <si>
+    <t>15260 Ventura Boulevard, Suite 670  Sherman Oaks CA 91403</t>
+  </si>
+  <si>
+    <t>ODS Technologies LP and Betfair Interactive US LLC</t>
+  </si>
+  <si>
+    <t>6701 Center Drive West, Suite 160  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>Beachbody, LLC</t>
+  </si>
+  <si>
+    <t>400 North Continental Blvd.  El Segundo CA 90245</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
     <r>
@@ -2299,7 +2362,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 10/06/2026</t>
+      <t>07/01/26 to 10/07/2026</t>
     </r>
     <r>
       <rPr>
@@ -2319,44 +2382,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I354.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I358.</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>WARN REPORT -</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-01/01/2023 - 10/06/2026
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through H3.</t>
-    </r>
-  </si>
-  <si>
-    <t>Relocation</t>
+    <t>Relocation Permanent</t>
   </si>
 </sst>
 </file>
@@ -2619,7 +2649,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2726,20 +2756,11 @@
     <xf numFmtId="164" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
@@ -2747,35 +2768,23 @@
     <xf numFmtId="164" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3569,10 +3578,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I354" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I354" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
-    <sortCondition ref="C2:C42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I358" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I358" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I358">
+    <sortCondition ref="C2:C358"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="29"/>
@@ -3991,7 +4000,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>16885</v>
+        <v>17209</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4000,7 +4009,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4027,7 +4036,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4059,23 +4068,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I354"/>
+  <dimension ref="A1:I358"/>
   <sheetFormatPr defaultColWidth="150.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="65.28515625" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="50.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -6722,22 +6731,22 @@
       <c r="A93" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B93" s="38">
+      <c r="B93" s="34">
         <v>46240</v>
       </c>
-      <c r="C93" s="38">
+      <c r="C93" s="34">
         <v>46240</v>
       </c>
-      <c r="D93" s="38">
+      <c r="D93" s="34">
         <v>46301</v>
       </c>
-      <c r="E93" s="39" t="s">
+      <c r="E93" s="38" t="s">
         <v>248</v>
       </c>
       <c r="F93" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="G93" s="40">
+      <c r="G93" s="39">
         <v>139</v>
       </c>
       <c r="H93" s="28" t="s">
@@ -6751,22 +6760,22 @@
       <c r="A94" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B94" s="38">
+      <c r="B94" s="34">
         <v>46240</v>
       </c>
-      <c r="C94" s="38">
+      <c r="C94" s="34">
         <v>46240</v>
       </c>
-      <c r="D94" s="38">
+      <c r="D94" s="34">
         <v>46301</v>
       </c>
-      <c r="E94" s="39" t="s">
+      <c r="E94" s="38" t="s">
         <v>250</v>
       </c>
       <c r="F94" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="G94" s="40">
+      <c r="G94" s="39">
         <v>58</v>
       </c>
       <c r="H94" s="28" t="s">
@@ -6780,22 +6789,22 @@
       <c r="A95" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B95" s="38">
+      <c r="B95" s="34">
         <v>46240</v>
       </c>
-      <c r="C95" s="38">
+      <c r="C95" s="34">
         <v>46240</v>
       </c>
-      <c r="D95" s="38">
+      <c r="D95" s="34">
         <v>46301</v>
       </c>
-      <c r="E95" s="39" t="s">
+      <c r="E95" s="38" t="s">
         <v>252</v>
       </c>
       <c r="F95" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="G95" s="40">
+      <c r="G95" s="39">
         <v>50</v>
       </c>
       <c r="H95" s="28" t="s">
@@ -6809,22 +6818,22 @@
       <c r="A96" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B96" s="38">
+      <c r="B96" s="34">
         <v>46239</v>
       </c>
-      <c r="C96" s="38">
+      <c r="C96" s="34">
         <v>46240</v>
       </c>
-      <c r="D96" s="38">
+      <c r="D96" s="34">
         <v>46304</v>
       </c>
-      <c r="E96" s="39" t="s">
+      <c r="E96" s="38" t="s">
         <v>254</v>
       </c>
       <c r="F96" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G96" s="40">
+      <c r="G96" s="39">
         <v>109</v>
       </c>
       <c r="H96" s="28" t="s">
@@ -6838,22 +6847,22 @@
       <c r="A97" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="B97" s="38">
+      <c r="B97" s="34">
         <v>46237</v>
       </c>
-      <c r="C97" s="38">
+      <c r="C97" s="34">
         <v>46240</v>
       </c>
-      <c r="D97" s="38">
+      <c r="D97" s="34">
         <v>46298</v>
       </c>
-      <c r="E97" s="39" t="s">
+      <c r="E97" s="38" t="s">
         <v>256</v>
       </c>
       <c r="F97" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G97" s="40">
+      <c r="G97" s="39">
         <v>4</v>
       </c>
       <c r="H97" s="28" t="s">
@@ -6867,22 +6876,22 @@
       <c r="A98" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B98" s="38">
+      <c r="B98" s="34">
         <v>46237</v>
       </c>
-      <c r="C98" s="38">
+      <c r="C98" s="34">
         <v>46240</v>
       </c>
-      <c r="D98" s="38">
+      <c r="D98" s="34">
         <v>46298</v>
       </c>
-      <c r="E98" s="39" t="s">
+      <c r="E98" s="38" t="s">
         <v>256</v>
       </c>
       <c r="F98" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G98" s="40">
+      <c r="G98" s="39">
         <v>99</v>
       </c>
       <c r="H98" s="28" t="s">
@@ -6896,22 +6905,22 @@
       <c r="A99" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="B99" s="38">
+      <c r="B99" s="34">
         <v>46224</v>
       </c>
-      <c r="C99" s="38">
+      <c r="C99" s="34">
         <v>46240</v>
       </c>
-      <c r="D99" s="38">
+      <c r="D99" s="34">
         <v>46224</v>
       </c>
-      <c r="E99" s="39" t="s">
+      <c r="E99" s="38" t="s">
         <v>209</v>
       </c>
       <c r="F99" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="G99" s="40">
+      <c r="G99" s="39">
         <v>60</v>
       </c>
       <c r="H99" s="28" t="s">
@@ -6925,22 +6934,22 @@
       <c r="A100" s="33" t="s">
         <v>260</v>
       </c>
-      <c r="B100" s="38">
+      <c r="B100" s="34">
         <v>46241</v>
       </c>
-      <c r="C100" s="38">
+      <c r="C100" s="34">
         <v>46241</v>
       </c>
-      <c r="D100" s="38">
+      <c r="D100" s="34">
         <v>46310</v>
       </c>
-      <c r="E100" s="39" t="s">
+      <c r="E100" s="38" t="s">
         <v>261</v>
       </c>
       <c r="F100" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="G100" s="40">
+      <c r="G100" s="39">
         <v>91</v>
       </c>
       <c r="H100" s="28" t="s">
@@ -6954,22 +6963,22 @@
       <c r="A101" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="B101" s="38">
+      <c r="B101" s="34">
         <v>46241</v>
       </c>
-      <c r="C101" s="38">
+      <c r="C101" s="34">
         <v>46244</v>
       </c>
-      <c r="D101" s="38">
+      <c r="D101" s="34">
         <v>46301</v>
       </c>
-      <c r="E101" s="39" t="s">
+      <c r="E101" s="38" t="s">
         <v>263</v>
       </c>
       <c r="F101" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="G101" s="40">
+      <c r="G101" s="39">
         <v>66</v>
       </c>
       <c r="H101" s="28" t="s">
@@ -8127,7 +8136,7 @@
         <v>338</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="G141" s="30">
         <v>73</v>
@@ -10492,25 +10501,25 @@
       <c r="A223" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="B223" s="41">
+      <c r="B223" s="44">
         <v>46279</v>
       </c>
-      <c r="C223" s="42">
+      <c r="C223" s="45">
         <v>46280</v>
       </c>
-      <c r="D223" s="41">
+      <c r="D223" s="44">
         <v>46339</v>
       </c>
-      <c r="E223" s="43" t="s">
+      <c r="E223" s="40" t="s">
         <v>486</v>
       </c>
-      <c r="F223" s="43" t="s">
+      <c r="F223" s="40" t="s">
         <v>6</v>
       </c>
       <c r="G223" s="30">
         <v>63</v>
       </c>
-      <c r="H223" s="43" t="s">
+      <c r="H223" s="40" t="s">
         <v>487</v>
       </c>
       <c r="I223" s="32" t="s">
@@ -10521,25 +10530,25 @@
       <c r="A224" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B224" s="41">
+      <c r="B224" s="44">
         <v>46279</v>
       </c>
-      <c r="C224" s="42">
+      <c r="C224" s="45">
         <v>46280</v>
       </c>
-      <c r="D224" s="41">
+      <c r="D224" s="44">
         <v>46339</v>
       </c>
-      <c r="E224" s="43" t="s">
+      <c r="E224" s="40" t="s">
         <v>488</v>
       </c>
-      <c r="F224" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="G224" s="44">
+      <c r="F224" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="G224" s="41">
         <v>279</v>
       </c>
-      <c r="H224" s="43" t="s">
+      <c r="H224" s="40" t="s">
         <v>489</v>
       </c>
       <c r="I224" s="32" t="s">
@@ -10550,25 +10559,25 @@
       <c r="A225" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="B225" s="45">
+      <c r="B225" s="46">
         <v>46279</v>
       </c>
-      <c r="C225" s="46">
+      <c r="C225" s="47">
         <v>46280</v>
       </c>
-      <c r="D225" s="45">
+      <c r="D225" s="46">
         <v>46339</v>
       </c>
-      <c r="E225" s="47" t="s">
+      <c r="E225" s="42" t="s">
         <v>488</v>
       </c>
-      <c r="F225" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="G225" s="48">
+      <c r="F225" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="G225" s="43">
         <v>99</v>
       </c>
-      <c r="H225" s="47" t="s">
+      <c r="H225" s="42" t="s">
         <v>490</v>
       </c>
       <c r="I225" s="32" t="s">
@@ -10579,25 +10588,25 @@
       <c r="A226" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="B226" s="41">
+      <c r="B226" s="44">
         <v>46267</v>
       </c>
-      <c r="C226" s="42">
+      <c r="C226" s="45">
         <v>46280</v>
       </c>
-      <c r="D226" s="41">
+      <c r="D226" s="44">
         <v>46328</v>
       </c>
-      <c r="E226" s="43" t="s">
+      <c r="E226" s="40" t="s">
         <v>491</v>
       </c>
-      <c r="F226" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="G226" s="44">
+      <c r="F226" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="G226" s="41">
         <v>151</v>
       </c>
-      <c r="H226" s="43" t="s">
+      <c r="H226" s="40" t="s">
         <v>153</v>
       </c>
       <c r="I226" s="32" t="s">
@@ -10608,25 +10617,25 @@
       <c r="A227" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="B227" s="45">
+      <c r="B227" s="46">
         <v>46267</v>
       </c>
-      <c r="C227" s="46">
+      <c r="C227" s="47">
         <v>46280</v>
       </c>
-      <c r="D227" s="45">
+      <c r="D227" s="46">
         <v>46328</v>
       </c>
-      <c r="E227" s="47" t="s">
+      <c r="E227" s="42" t="s">
         <v>492</v>
       </c>
-      <c r="F227" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="G227" s="48">
+      <c r="F227" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="G227" s="43">
         <v>102</v>
       </c>
-      <c r="H227" s="47" t="s">
+      <c r="H227" s="42" t="s">
         <v>493</v>
       </c>
       <c r="I227" s="32" t="s">
@@ -10637,25 +10646,25 @@
       <c r="A228" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="B228" s="41">
+      <c r="B228" s="44">
         <v>46280</v>
       </c>
-      <c r="C228" s="42">
+      <c r="C228" s="45">
         <v>46280</v>
       </c>
-      <c r="D228" s="41">
+      <c r="D228" s="44">
         <v>46330</v>
       </c>
-      <c r="E228" s="43" t="s">
+      <c r="E228" s="40" t="s">
         <v>494</v>
       </c>
-      <c r="F228" s="43" t="s">
+      <c r="F228" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="G228" s="44">
+      <c r="G228" s="41">
         <v>91</v>
       </c>
-      <c r="H228" s="43" t="s">
+      <c r="H228" s="40" t="s">
         <v>495</v>
       </c>
       <c r="I228" s="32" t="s">
@@ -10666,25 +10675,25 @@
       <c r="A229" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="B229" s="45">
+      <c r="B229" s="46">
         <v>46280</v>
       </c>
-      <c r="C229" s="46">
+      <c r="C229" s="47">
         <v>46280</v>
       </c>
-      <c r="D229" s="45">
+      <c r="D229" s="46">
         <v>46330</v>
       </c>
-      <c r="E229" s="47" t="s">
+      <c r="E229" s="42" t="s">
         <v>496</v>
       </c>
-      <c r="F229" s="47" t="s">
+      <c r="F229" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="G229" s="48">
+      <c r="G229" s="43">
         <v>19</v>
       </c>
-      <c r="H229" s="47" t="s">
+      <c r="H229" s="42" t="s">
         <v>497</v>
       </c>
       <c r="I229" s="32" t="s">
@@ -10695,25 +10704,25 @@
       <c r="A230" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="B230" s="41">
+      <c r="B230" s="44">
         <v>46279</v>
       </c>
-      <c r="C230" s="42">
+      <c r="C230" s="45">
         <v>46280</v>
       </c>
-      <c r="D230" s="41">
+      <c r="D230" s="44">
         <v>46341</v>
       </c>
-      <c r="E230" s="43" t="s">
+      <c r="E230" s="40" t="s">
         <v>498</v>
       </c>
-      <c r="F230" s="43" t="s">
+      <c r="F230" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="G230" s="44">
+      <c r="G230" s="41">
         <v>7</v>
       </c>
-      <c r="H230" s="43" t="s">
+      <c r="H230" s="40" t="s">
         <v>137</v>
       </c>
       <c r="I230" s="32" t="s">
@@ -10724,25 +10733,25 @@
       <c r="A231" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="B231" s="41">
+      <c r="B231" s="44">
         <v>46266</v>
       </c>
-      <c r="C231" s="42">
+      <c r="C231" s="45">
         <v>46281</v>
       </c>
-      <c r="D231" s="41">
+      <c r="D231" s="44">
         <v>46327</v>
       </c>
-      <c r="E231" s="43" t="s">
+      <c r="E231" s="40" t="s">
         <v>499</v>
       </c>
-      <c r="F231" s="43" t="s">
+      <c r="F231" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="G231" s="44">
+      <c r="G231" s="41">
         <v>35</v>
       </c>
-      <c r="H231" s="43" t="s">
+      <c r="H231" s="40" t="s">
         <v>500</v>
       </c>
       <c r="I231" s="32" t="s">
@@ -10753,25 +10762,25 @@
       <c r="A232" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="B232" s="45">
+      <c r="B232" s="46">
         <v>46266</v>
       </c>
-      <c r="C232" s="46">
+      <c r="C232" s="47">
         <v>46281</v>
       </c>
-      <c r="D232" s="45">
+      <c r="D232" s="46">
         <v>46327</v>
       </c>
-      <c r="E232" s="47" t="s">
+      <c r="E232" s="42" t="s">
         <v>499</v>
       </c>
-      <c r="F232" s="47" t="s">
+      <c r="F232" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="G232" s="48">
+      <c r="G232" s="43">
         <v>32</v>
       </c>
-      <c r="H232" s="47" t="s">
+      <c r="H232" s="42" t="s">
         <v>501</v>
       </c>
       <c r="I232" s="32" t="s">
@@ -13663,7 +13672,7 @@
         <v>46326</v>
       </c>
       <c r="E332" s="28" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="F332" s="28" t="s">
         <v>6</v>
@@ -13672,7 +13681,7 @@
         <v>5</v>
       </c>
       <c r="H332" s="30" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="I332" s="32" t="s">
         <v>43</v>
@@ -13692,7 +13701,7 @@
         <v>46326</v>
       </c>
       <c r="E333" s="28" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F333" s="28" t="s">
         <v>6</v>
@@ -13701,7 +13710,7 @@
         <v>5</v>
       </c>
       <c r="H333" s="30" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="I333" s="32" t="s">
         <v>43</v>
@@ -13721,7 +13730,7 @@
         <v>46326</v>
       </c>
       <c r="E334" s="28" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F334" s="28" t="s">
         <v>6</v>
@@ -13730,7 +13739,7 @@
         <v>5</v>
       </c>
       <c r="H334" s="30" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="I334" s="32" t="s">
         <v>43</v>
@@ -13750,7 +13759,7 @@
         <v>46326</v>
       </c>
       <c r="E335" s="28" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F335" s="28" t="s">
         <v>6</v>
@@ -13759,7 +13768,7 @@
         <v>5</v>
       </c>
       <c r="H335" s="30" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="I335" s="32" t="s">
         <v>43</v>
@@ -13767,60 +13776,60 @@
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" s="28" t="s">
-        <v>5</v>
+        <v>127</v>
       </c>
       <c r="B336" s="29">
-        <v>46294</v>
+        <v>46287</v>
       </c>
       <c r="C336" s="29">
         <v>46294</v>
       </c>
       <c r="D336" s="29">
-        <v>46326</v>
+        <v>46345</v>
       </c>
       <c r="E336" s="28" t="s">
-        <v>694</v>
+        <v>617</v>
       </c>
       <c r="F336" s="28" t="s">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="G336" s="30">
-        <v>5</v>
+        <v>221</v>
       </c>
       <c r="H336" s="30" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="I336" s="32" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" s="28" t="s">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="B337" s="29">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="C337" s="29">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D337" s="29">
-        <v>46345</v>
+        <v>46360</v>
       </c>
       <c r="E337" s="28" t="s">
-        <v>617</v>
+        <v>697</v>
       </c>
       <c r="F337" s="28" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="G337" s="30">
-        <v>221</v>
+        <v>60</v>
       </c>
       <c r="H337" s="30" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I337" s="32" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.25">
@@ -13828,54 +13837,54 @@
         <v>5</v>
       </c>
       <c r="B338" s="29">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C338" s="29">
         <v>46295</v>
       </c>
       <c r="D338" s="29">
-        <v>46360</v>
+        <v>46356</v>
       </c>
       <c r="E338" s="28" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="F338" s="28" t="s">
         <v>52</v>
       </c>
       <c r="G338" s="30">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H338" s="30" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="I338" s="32" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" s="28" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="B339" s="29">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="C339" s="29">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D339" s="29">
-        <v>46356</v>
+        <v>46266</v>
       </c>
       <c r="E339" s="28" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F339" s="28" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="G339" s="30">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="H339" s="30" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="I339" s="32" t="s">
         <v>34</v>
@@ -13883,144 +13892,144 @@
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="B340" s="41">
-        <v>46289</v>
-      </c>
-      <c r="C340" s="41">
+        <v>5</v>
+      </c>
+      <c r="B340" s="34">
         <v>46296</v>
       </c>
-      <c r="D340" s="41">
-        <v>46266</v>
-      </c>
-      <c r="E340" s="49" t="s">
-        <v>701</v>
-      </c>
-      <c r="F340" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="G340" s="50">
-        <v>85</v>
-      </c>
-      <c r="H340" s="51" t="s">
-        <v>702</v>
+      <c r="C340" s="34">
+        <v>46297</v>
+      </c>
+      <c r="D340" s="34">
+        <v>46356</v>
+      </c>
+      <c r="E340" s="38" t="s">
+        <v>703</v>
+      </c>
+      <c r="F340" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="G340" s="39">
+        <v>92</v>
+      </c>
+      <c r="H340" s="28" t="s">
+        <v>704</v>
       </c>
       <c r="I340" s="32" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="B341" s="41">
+        <v>103</v>
+      </c>
+      <c r="B341" s="34">
         <v>46296</v>
       </c>
-      <c r="C341" s="41">
+      <c r="C341" s="34">
         <v>46297</v>
       </c>
-      <c r="D341" s="41">
-        <v>46356</v>
-      </c>
-      <c r="E341" s="49" t="s">
-        <v>703</v>
-      </c>
-      <c r="F341" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="G341" s="50">
-        <v>92</v>
-      </c>
-      <c r="H341" s="51" t="s">
-        <v>704</v>
+      <c r="D341" s="34">
+        <v>46357</v>
+      </c>
+      <c r="E341" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="F341" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G341" s="39">
+        <v>5</v>
+      </c>
+      <c r="H341" s="28" t="s">
+        <v>132</v>
       </c>
       <c r="I341" s="32" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="B342" s="41">
-        <v>46296</v>
-      </c>
-      <c r="C342" s="41">
+        <v>56</v>
+      </c>
+      <c r="B342" s="34">
         <v>46297</v>
       </c>
-      <c r="D342" s="41">
-        <v>46357</v>
-      </c>
-      <c r="E342" s="49" t="s">
-        <v>131</v>
-      </c>
-      <c r="F342" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="G342" s="50">
-        <v>5</v>
-      </c>
-      <c r="H342" s="51" t="s">
-        <v>132</v>
+      <c r="C342" s="34">
+        <v>46297</v>
+      </c>
+      <c r="D342" s="34">
+        <v>46360</v>
+      </c>
+      <c r="E342" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="F342" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="G342" s="39">
+        <v>3</v>
+      </c>
+      <c r="H342" s="28" t="s">
+        <v>63</v>
       </c>
       <c r="I342" s="32" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="B343" s="45">
+        <v>326</v>
+      </c>
+      <c r="B343" s="34">
+        <v>46295</v>
+      </c>
+      <c r="C343" s="34">
         <v>46297</v>
       </c>
-      <c r="C343" s="45">
-        <v>46297</v>
-      </c>
-      <c r="D343" s="45">
-        <v>46360</v>
-      </c>
-      <c r="E343" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="F343" s="52" t="s">
-        <v>52</v>
+      <c r="D343" s="34">
+        <v>46295</v>
+      </c>
+      <c r="E343" s="38" t="s">
+        <v>705</v>
+      </c>
+      <c r="F343" s="38" t="s">
+        <v>6</v>
       </c>
       <c r="G343" s="30">
         <v>3</v>
       </c>
-      <c r="H343" s="53" t="s">
-        <v>63</v>
+      <c r="H343" s="28" t="s">
+        <v>706</v>
       </c>
       <c r="I343" s="32" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="B344" s="41">
+      <c r="B344" s="34">
         <v>46295</v>
       </c>
-      <c r="C344" s="41">
+      <c r="C344" s="34">
         <v>46297</v>
       </c>
-      <c r="D344" s="41">
+      <c r="D344" s="34">
         <v>46295</v>
       </c>
-      <c r="E344" s="49" t="s">
-        <v>705</v>
-      </c>
-      <c r="F344" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="G344" s="50">
-        <v>3</v>
-      </c>
-      <c r="H344" s="51" t="s">
-        <v>706</v>
+      <c r="E344" s="38" t="s">
+        <v>707</v>
+      </c>
+      <c r="F344" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G344" s="39">
+        <v>5</v>
+      </c>
+      <c r="H344" s="28" t="s">
+        <v>708</v>
       </c>
       <c r="I344" s="32" t="s">
         <v>45</v>
@@ -14030,26 +14039,26 @@
       <c r="A345" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="B345" s="45">
+      <c r="B345" s="34">
         <v>46295</v>
       </c>
-      <c r="C345" s="45">
+      <c r="C345" s="34">
         <v>46297</v>
       </c>
-      <c r="D345" s="45">
+      <c r="D345" s="34">
         <v>46295</v>
       </c>
-      <c r="E345" s="52" t="s">
-        <v>707</v>
-      </c>
-      <c r="F345" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="G345" s="54">
-        <v>5</v>
-      </c>
-      <c r="H345" s="53" t="s">
-        <v>708</v>
+      <c r="E345" s="38" t="s">
+        <v>709</v>
+      </c>
+      <c r="F345" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G345" s="39">
+        <v>8</v>
+      </c>
+      <c r="H345" s="28" t="s">
+        <v>710</v>
       </c>
       <c r="I345" s="32" t="s">
         <v>45</v>
@@ -14059,26 +14068,26 @@
       <c r="A346" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="B346" s="41">
+      <c r="B346" s="34">
         <v>46295</v>
       </c>
-      <c r="C346" s="41">
+      <c r="C346" s="34">
         <v>46297</v>
       </c>
-      <c r="D346" s="41">
+      <c r="D346" s="34">
         <v>46295</v>
       </c>
-      <c r="E346" s="49" t="s">
-        <v>709</v>
-      </c>
-      <c r="F346" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="G346" s="50">
-        <v>8</v>
-      </c>
-      <c r="H346" s="51" t="s">
-        <v>710</v>
+      <c r="E346" s="38" t="s">
+        <v>711</v>
+      </c>
+      <c r="F346" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G346" s="39">
+        <v>6</v>
+      </c>
+      <c r="H346" s="28" t="s">
+        <v>712</v>
       </c>
       <c r="I346" s="32" t="s">
         <v>45</v>
@@ -14088,26 +14097,26 @@
       <c r="A347" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="B347" s="45">
+      <c r="B347" s="34">
         <v>46295</v>
       </c>
-      <c r="C347" s="45">
+      <c r="C347" s="34">
         <v>46297</v>
       </c>
-      <c r="D347" s="45">
+      <c r="D347" s="34">
         <v>46295</v>
       </c>
-      <c r="E347" s="52" t="s">
-        <v>711</v>
-      </c>
-      <c r="F347" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="G347" s="54">
-        <v>6</v>
-      </c>
-      <c r="H347" s="53" t="s">
-        <v>712</v>
+      <c r="E347" s="38" t="s">
+        <v>713</v>
+      </c>
+      <c r="F347" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G347" s="39">
+        <v>18</v>
+      </c>
+      <c r="H347" s="28" t="s">
+        <v>714</v>
       </c>
       <c r="I347" s="32" t="s">
         <v>45</v>
@@ -14115,205 +14124,321 @@
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" s="33" t="s">
-        <v>326</v>
-      </c>
-      <c r="B348" s="41">
-        <v>46295</v>
-      </c>
-      <c r="C348" s="41">
-        <v>46297</v>
-      </c>
-      <c r="D348" s="41">
-        <v>46295</v>
-      </c>
-      <c r="E348" s="49" t="s">
-        <v>713</v>
-      </c>
-      <c r="F348" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="G348" s="50">
-        <v>18</v>
-      </c>
-      <c r="H348" s="51" t="s">
-        <v>714</v>
+        <v>76</v>
+      </c>
+      <c r="B348" s="34">
+        <v>46300</v>
+      </c>
+      <c r="C348" s="34">
+        <v>46300</v>
+      </c>
+      <c r="D348" s="34">
+        <v>46360</v>
+      </c>
+      <c r="E348" s="38" t="s">
+        <v>715</v>
+      </c>
+      <c r="F348" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G348" s="39">
+        <v>1</v>
+      </c>
+      <c r="H348" s="28" t="s">
+        <v>579</v>
       </c>
       <c r="I348" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="B349" s="45">
+      <c r="B349" s="34">
         <v>46300</v>
       </c>
-      <c r="C349" s="45">
+      <c r="C349" s="34">
         <v>46300</v>
       </c>
-      <c r="D349" s="45">
+      <c r="D349" s="34">
         <v>46360</v>
       </c>
-      <c r="E349" s="52" t="s">
+      <c r="E349" s="38" t="s">
         <v>715</v>
       </c>
-      <c r="F349" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="G349" s="54">
-        <v>1</v>
-      </c>
-      <c r="H349" s="53" t="s">
-        <v>579</v>
+      <c r="F349" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G349" s="39">
+        <v>2</v>
+      </c>
+      <c r="H349" s="28" t="s">
+        <v>581</v>
       </c>
       <c r="I349" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="B350" s="41">
+        <v>5</v>
+      </c>
+      <c r="B350" s="34">
         <v>46300</v>
       </c>
-      <c r="C350" s="41">
+      <c r="C350" s="34">
         <v>46300</v>
       </c>
-      <c r="D350" s="41">
+      <c r="D350" s="34">
         <v>46360</v>
       </c>
-      <c r="E350" s="49" t="s">
-        <v>715</v>
-      </c>
-      <c r="F350" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="G350" s="50">
-        <v>2</v>
-      </c>
-      <c r="H350" s="51" t="s">
-        <v>581</v>
+      <c r="E350" s="38" t="s">
+        <v>716</v>
+      </c>
+      <c r="F350" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G350" s="39">
+        <v>1</v>
+      </c>
+      <c r="H350" s="28" t="s">
+        <v>586</v>
       </c>
       <c r="I350" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B351" s="41">
+      <c r="B351" s="34">
         <v>46300</v>
       </c>
-      <c r="C351" s="41">
+      <c r="C351" s="34">
         <v>46300</v>
       </c>
-      <c r="D351" s="41">
+      <c r="D351" s="34">
         <v>46360</v>
       </c>
-      <c r="E351" s="49" t="s">
-        <v>716</v>
-      </c>
-      <c r="F351" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="G351" s="50">
+      <c r="E351" s="38" t="s">
+        <v>717</v>
+      </c>
+      <c r="F351" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G351" s="39">
         <v>1</v>
       </c>
-      <c r="H351" s="51" t="s">
-        <v>586</v>
+      <c r="H351" s="28" t="s">
+        <v>584</v>
       </c>
       <c r="I351" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="B352" s="45">
+        <v>207</v>
+      </c>
+      <c r="B352" s="34">
         <v>46300</v>
       </c>
-      <c r="C352" s="45">
+      <c r="C352" s="34">
         <v>46300</v>
       </c>
-      <c r="D352" s="45">
+      <c r="D352" s="34">
         <v>46360</v>
       </c>
-      <c r="E352" s="52" t="s">
-        <v>717</v>
-      </c>
-      <c r="F352" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="G352" s="54">
+      <c r="E352" s="38" t="s">
+        <v>715</v>
+      </c>
+      <c r="F352" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G352" s="39">
         <v>1</v>
       </c>
-      <c r="H352" s="53" t="s">
-        <v>584</v>
+      <c r="H352" s="28" t="s">
+        <v>603</v>
       </c>
       <c r="I352" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="B353" s="41">
+        <v>189</v>
+      </c>
+      <c r="B353" s="34">
         <v>46300</v>
       </c>
-      <c r="C353" s="41">
+      <c r="C353" s="34">
         <v>46300</v>
       </c>
-      <c r="D353" s="41">
+      <c r="D353" s="34">
         <v>46360</v>
       </c>
-      <c r="E353" s="49" t="s">
-        <v>715</v>
-      </c>
-      <c r="F353" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="G353" s="50">
-        <v>1</v>
-      </c>
-      <c r="H353" s="51" t="s">
-        <v>603</v>
+      <c r="E353" s="38" t="s">
+        <v>718</v>
+      </c>
+      <c r="F353" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G353" s="39">
+        <v>130</v>
+      </c>
+      <c r="H353" s="28" t="s">
+        <v>719</v>
       </c>
       <c r="I353" s="32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="B354" s="41">
+        <v>76</v>
+      </c>
+      <c r="B354" s="34">
+        <v>46301</v>
+      </c>
+      <c r="C354" s="34">
+        <v>46301</v>
+      </c>
+      <c r="D354" s="34">
+        <v>46363</v>
+      </c>
+      <c r="E354" s="38" t="s">
+        <v>721</v>
+      </c>
+      <c r="F354" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="G354" s="39">
+        <v>87</v>
+      </c>
+      <c r="H354" s="28" t="s">
+        <v>722</v>
+      </c>
+      <c r="I354" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B355" s="29">
         <v>46300</v>
       </c>
-      <c r="C354" s="41">
-        <v>46300</v>
-      </c>
-      <c r="D354" s="41">
-        <v>46360</v>
-      </c>
-      <c r="E354" s="49" t="s">
-        <v>718</v>
-      </c>
-      <c r="F354" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="G354" s="50">
-        <v>130</v>
-      </c>
-      <c r="H354" s="51" t="s">
-        <v>719</v>
-      </c>
-      <c r="I354" s="32" t="s">
+      <c r="C355" s="29">
+        <v>46301</v>
+      </c>
+      <c r="D355" s="29">
+        <v>46391</v>
+      </c>
+      <c r="E355" s="28" t="s">
+        <v>723</v>
+      </c>
+      <c r="F355" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G355" s="30">
+        <v>12</v>
+      </c>
+      <c r="H355" s="30" t="s">
+        <v>724</v>
+      </c>
+      <c r="I355" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B356" s="29">
+        <v>46295</v>
+      </c>
+      <c r="C356" s="29">
+        <v>46301</v>
+      </c>
+      <c r="D356" s="29">
+        <v>46276</v>
+      </c>
+      <c r="E356" s="28" t="s">
+        <v>725</v>
+      </c>
+      <c r="F356" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G356" s="30">
+        <v>148</v>
+      </c>
+      <c r="H356" s="30" t="s">
+        <v>726</v>
+      </c>
+      <c r="I356" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B357" s="29">
+        <v>46296</v>
+      </c>
+      <c r="C357" s="29">
+        <v>46302</v>
+      </c>
+      <c r="D357" s="29">
+        <v>46356</v>
+      </c>
+      <c r="E357" s="28" t="s">
+        <v>727</v>
+      </c>
+      <c r="F357" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G357" s="30">
+        <v>2</v>
+      </c>
+      <c r="H357" s="30" t="s">
+        <v>728</v>
+      </c>
+      <c r="I357" s="32" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B358" s="29">
+        <v>46301</v>
+      </c>
+      <c r="C358" s="29">
+        <v>46302</v>
+      </c>
+      <c r="D358" s="29">
+        <v>46363</v>
+      </c>
+      <c r="E358" s="28" t="s">
+        <v>729</v>
+      </c>
+      <c r="F358" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G358" s="30">
+        <v>80</v>
+      </c>
+      <c r="H358" s="30" t="s">
+        <v>730</v>
+      </c>
+      <c r="I358" s="32" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -14330,7 +14455,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I354</xm:sqref>
+          <xm:sqref>I3:I358</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -14451,7 +14576,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E1"/>
     </row>
@@ -14866,7 +14991,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A98A5496-6405-46D2-AEE4-9AE3F9C2111C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48B8CB07-104F-4796-83F1-C004B434531E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -14885,7 +15010,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7408BBD4-1E66-4167-890F-91293CA5CD70}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E2FA099-008C-4EDE-BD9D-84353A57EDC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -14893,24 +15018,24 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D6C677-D447-4EFB-8A81-433F3B9E70FF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5881772-74BF-4FAC-848F-7C2FDA9A8D30}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" contentBits="0" removed="0"/>
+  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" removed="0"/>
 </clbl:labelList>
 </file>
--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jchinn2\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{8EA63960-EED8-4D37-B183-BC467431938F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66D0C2BD-7D03-4B69-87E4-B9EE9F122930}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29AF7EE8-79B1-4F51-BE6A-4B705A337962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1851" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="744">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2288,6 +2288,57 @@
     <t>3500 Polk Street  Riverside CA 92505</t>
   </si>
   <si>
+    <t>Caribou Biosciences, Inc.</t>
+  </si>
+  <si>
+    <t>2929 7th Street, Ste 105  Berkeley CA 94710</t>
+  </si>
+  <si>
+    <t>Cayuga Home for Children</t>
+  </si>
+  <si>
+    <t>8616 La Tijera Boulevard  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>Neogen Care Home Health Agency</t>
+  </si>
+  <si>
+    <t>15260 Ventura Boulevard, Suite 670  Sherman Oaks CA 91403</t>
+  </si>
+  <si>
+    <t>ODS Technologies LP and Betfair Interactive US LLC</t>
+  </si>
+  <si>
+    <t>6701 Center Drive West, Suite 160  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>Beachbody, LLC</t>
+  </si>
+  <si>
+    <t>400 North Continental Blvd.  El Segundo CA 90245</t>
+  </si>
+  <si>
+    <t>Jacuzzi</t>
+  </si>
+  <si>
+    <t>Sapporo U.S.A. - Executive Place</t>
+  </si>
+  <si>
+    <t>Sapporo U.S.A - Citracado Parkway</t>
+  </si>
+  <si>
+    <t>Phillips 66 - Wilmington</t>
+  </si>
+  <si>
+    <t>Phillips 66 - Carson</t>
+  </si>
+  <si>
+    <t>14525 Monte Vista Ave.  Chino CA 91710</t>
+  </si>
+  <si>
+    <t>1520 E. Sepulveda Blvd.  Carson CA 90745</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2307,7 +2358,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 10/07/2026
+01/01/2023 - 10/14/2026
 </t>
     </r>
     <r>
@@ -2321,34 +2372,19 @@
     </r>
   </si>
   <si>
-    <t>Caribou Biosciences, Inc.</t>
-  </si>
-  <si>
-    <t>2929 7th Street, Ste 105  Berkeley CA 94710</t>
-  </si>
-  <si>
-    <t>Cayuga Home for Children</t>
-  </si>
-  <si>
-    <t>8616 La Tijera Boulevard  Los Angeles CA 90045</t>
-  </si>
-  <si>
-    <t>Neogen Care Home Health Agency</t>
-  </si>
-  <si>
-    <t>15260 Ventura Boulevard, Suite 670  Sherman Oaks CA 91403</t>
-  </si>
-  <si>
-    <t>ODS Technologies LP and Betfair Interactive US LLC</t>
-  </si>
-  <si>
-    <t>6701 Center Drive West, Suite 160  Los Angeles CA 90045</t>
-  </si>
-  <si>
-    <t>Beachbody, LLC</t>
-  </si>
-  <si>
-    <t>400 North Continental Blvd.  El Segundo CA 90245</t>
+    <t>5820 Owens Dr.  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>The Neil Jones Food Company dba Tomatek</t>
+  </si>
+  <si>
+    <t>2025 N Street  Firebaugh CA 93622</t>
+  </si>
+  <si>
+    <t>Menzies Aviation</t>
+  </si>
+  <si>
+    <t>1 World Way  Los Angeles CA 90045</t>
   </si>
   <si>
     <r>
@@ -2362,7 +2398,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 10/07/2026</t>
+      <t>07/01/26 to 10/14/2026</t>
     </r>
     <r>
       <rPr>
@@ -2382,11 +2418,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I358.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I370.</t>
     </r>
-  </si>
-  <si>
-    <t>Relocation Permanent</t>
   </si>
 </sst>
 </file>
@@ -2502,7 +2535,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2521,14 +2554,8 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
-        <bgColor rgb="FFF0F0F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -2642,6 +2669,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA9A9A9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA9A9A9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA9A9A9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2649,7 +2689,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2735,10 +2775,10 @@
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2762,28 +2802,10 @@
     <xf numFmtId="164" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -3202,42 +3224,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3502,6 +3488,42 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFF9E7"/>
@@ -3564,35 +3586,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BE651B3D-87EE-436C-B33F-C1564840D30D}" name="WarnReportSummary" displayName="WarnReportSummary" ref="A2:B9" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BE651B3D-87EE-436C-B33F-C1564840D30D}" name="WarnReportSummary" displayName="WarnReportSummary" ref="A2:B9" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="A2:B9" xr:uid="{BE651B3D-87EE-436C-B33F-C1564840D30D}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{27E39F38-3125-453D-8079-314461C0A408}" name="Report Summary" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{BC59C82C-A192-4C58-973D-25AB492E21BC}" name="Total" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{27E39F38-3125-453D-8079-314461C0A408}" name="Report Summary" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{BC59C82C-A192-4C58-973D-25AB492E21BC}" name="Total" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I358" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I358" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I370" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A2:I370" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I358">
     <sortCondition ref="C2:C358"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{C6D12265-C94C-4E06-8034-3C717447E155}" name="Processed_x000a_Date" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{B3ED9634-5328-42A8-B322-3BC02B1B09B6}" name="Effective _x000a_Date" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{9D38EF5A-DEC2-4452-98D6-CF4FB3342379}" name="Company" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{211DDDC0-B68A-4CB6-AB53-3FF3E63F26A0}" name="Layoff/_x000a_Closure" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{5A996A7E-F604-41CE-AC0B-D6BC2FB09F5A}" name="No. Of_x000a_Employees" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{6BB24B8B-7A22-4DE0-B907-BC4F68AE8678}" name="Address" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{695F1FD1-01CF-43F8-8B40-37D320A0AC01}" name="Related Industry" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{C6D12265-C94C-4E06-8034-3C717447E155}" name="Processed_x000a_Date" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{B3ED9634-5328-42A8-B322-3BC02B1B09B6}" name="Effective _x000a_Date" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{9D38EF5A-DEC2-4452-98D6-CF4FB3342379}" name="Company" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{211DDDC0-B68A-4CB6-AB53-3FF3E63F26A0}" name="Layoff/_x000a_Closure" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{5A996A7E-F604-41CE-AC0B-D6BC2FB09F5A}" name="No. Of_x000a_Employees" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{6BB24B8B-7A22-4DE0-B907-BC4F68AE8678}" name="Address" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{695F1FD1-01CF-43F8-8B40-37D320A0AC01}" name="Related Industry" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4000,7 +4022,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>17209</v>
+        <v>17617</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4009,7 +4031,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4018,7 +4040,7 @@
       </c>
       <c r="B5" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4036,7 +4058,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4068,7 +4090,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I358"/>
+  <dimension ref="A1:I370"/>
   <sheetFormatPr defaultColWidth="150.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -4084,7 +4106,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -4142,7 +4164,7 @@
       <c r="H3" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="31" t="s">
+      <c r="I3" s="32" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4171,7 +4193,7 @@
       <c r="H4" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="I4" s="32" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4200,7 +4222,7 @@
       <c r="H5" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="I5" s="31" t="s">
+      <c r="I5" s="32" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4229,7 +4251,7 @@
       <c r="H6" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="I6" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4258,7 +4280,7 @@
       <c r="H7" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="31" t="s">
+      <c r="I7" s="32" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4287,7 +4309,7 @@
       <c r="H8" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="32" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4316,7 +4338,7 @@
       <c r="H9" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="I9" s="32" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4345,7 +4367,7 @@
       <c r="H10" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="32" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4374,7 +4396,7 @@
       <c r="H11" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="31" t="s">
+      <c r="I11" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4403,7 +4425,7 @@
       <c r="H12" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="I12" s="32" t="s">
+      <c r="I12" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4432,7 +4454,7 @@
       <c r="H13" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4461,7 +4483,7 @@
       <c r="H14" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="I14" s="32" t="s">
+      <c r="I14" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4490,7 +4512,7 @@
       <c r="H15" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="I15" s="32" t="s">
+      <c r="I15" s="31" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4519,7 +4541,7 @@
       <c r="H16" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="32" t="s">
+      <c r="I16" s="31" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4548,7 +4570,7 @@
       <c r="H17" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="32" t="s">
+      <c r="I17" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4577,7 +4599,7 @@
       <c r="H18" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="I18" s="32" t="s">
+      <c r="I18" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4606,7 +4628,7 @@
       <c r="H19" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="I19" s="32" t="s">
+      <c r="I19" s="31" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4635,7 +4657,7 @@
       <c r="H20" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="I20" s="32" t="s">
+      <c r="I20" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4664,7 +4686,7 @@
       <c r="H21" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="I21" s="32" t="s">
+      <c r="I21" s="31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4693,7 +4715,7 @@
       <c r="H22" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="I22" s="32" t="s">
+      <c r="I22" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4722,7 +4744,7 @@
       <c r="H23" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="I23" s="32" t="s">
+      <c r="I23" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4751,7 +4773,7 @@
       <c r="H24" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="I24" s="32" t="s">
+      <c r="I24" s="31" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4780,7 +4802,7 @@
       <c r="H25" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="I25" s="32" t="s">
+      <c r="I25" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4809,7 +4831,7 @@
       <c r="H26" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="I26" s="32" t="s">
+      <c r="I26" s="31" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4838,7 +4860,7 @@
       <c r="H27" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="I27" s="32" t="s">
+      <c r="I27" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4867,7 +4889,7 @@
       <c r="H28" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="I28" s="32" t="s">
+      <c r="I28" s="31" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4896,7 +4918,7 @@
       <c r="H29" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="I29" s="32" t="s">
+      <c r="I29" s="31" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4925,7 +4947,7 @@
       <c r="H30" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="I30" s="32" t="s">
+      <c r="I30" s="31" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4954,7 +4976,7 @@
       <c r="H31" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="I31" s="32" t="s">
+      <c r="I31" s="31" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4983,7 +5005,7 @@
       <c r="H32" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="I32" s="32" t="s">
+      <c r="I32" s="31" t="s">
         <v>47</v>
       </c>
     </row>
@@ -5012,7 +5034,7 @@
       <c r="H33" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="I33" s="32" t="s">
+      <c r="I33" s="31" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5041,7 +5063,7 @@
       <c r="H34" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="I34" s="32" t="s">
+      <c r="I34" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5070,7 +5092,7 @@
       <c r="H35" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="I35" s="32" t="s">
+      <c r="I35" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5099,7 +5121,7 @@
       <c r="H36" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="I36" s="32" t="s">
+      <c r="I36" s="31" t="s">
         <v>47</v>
       </c>
     </row>
@@ -5128,7 +5150,7 @@
       <c r="H37" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="I37" s="32" t="s">
+      <c r="I37" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5157,7 +5179,7 @@
       <c r="H38" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="I38" s="32" t="s">
+      <c r="I38" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -5186,7 +5208,7 @@
       <c r="H39" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="I39" s="32" t="s">
+      <c r="I39" s="31" t="s">
         <v>36</v>
       </c>
     </row>
@@ -5215,7 +5237,7 @@
       <c r="H40" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="I40" s="32" t="s">
+      <c r="I40" s="31" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5244,7 +5266,7 @@
       <c r="H41" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="I41" s="32" t="s">
+      <c r="I41" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -5273,7 +5295,7 @@
       <c r="H42" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="I42" s="32" t="s">
+      <c r="I42" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -5302,7 +5324,7 @@
       <c r="H43" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="I43" s="32" t="s">
+      <c r="I43" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -5331,7 +5353,7 @@
       <c r="H44" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="I44" s="32" t="s">
+      <c r="I44" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5360,7 +5382,7 @@
       <c r="H45" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="I45" s="32" t="s">
+      <c r="I45" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5389,7 +5411,7 @@
       <c r="H46" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="I46" s="32" t="s">
+      <c r="I46" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5418,7 +5440,7 @@
       <c r="H47" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="I47" s="32" t="s">
+      <c r="I47" s="31" t="s">
         <v>47</v>
       </c>
     </row>
@@ -5447,7 +5469,7 @@
       <c r="H48" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="I48" s="32" t="s">
+      <c r="I48" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5476,7 +5498,7 @@
       <c r="H49" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="I49" s="32" t="s">
+      <c r="I49" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5505,7 +5527,7 @@
       <c r="H50" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="I50" s="32" t="s">
+      <c r="I50" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5534,7 +5556,7 @@
       <c r="H51" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="I51" s="32" t="s">
+      <c r="I51" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5563,7 +5585,7 @@
       <c r="H52" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="I52" s="32" t="s">
+      <c r="I52" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5592,7 +5614,7 @@
       <c r="H53" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="I53" s="32" t="s">
+      <c r="I53" s="31" t="s">
         <v>36</v>
       </c>
     </row>
@@ -5621,7 +5643,7 @@
       <c r="H54" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="I54" s="32" t="s">
+      <c r="I54" s="31" t="s">
         <v>36</v>
       </c>
     </row>
@@ -5650,7 +5672,7 @@
       <c r="H55" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="I55" s="32" t="s">
+      <c r="I55" s="31" t="s">
         <v>47</v>
       </c>
     </row>
@@ -5679,7 +5701,7 @@
       <c r="H56" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="I56" s="32" t="s">
+      <c r="I56" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5708,7 +5730,7 @@
       <c r="H57" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="I57" s="32" t="s">
+      <c r="I57" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5737,7 +5759,7 @@
       <c r="H58" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="I58" s="32" t="s">
+      <c r="I58" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5766,7 +5788,7 @@
       <c r="H59" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="I59" s="32" t="s">
+      <c r="I59" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5795,7 +5817,7 @@
       <c r="H60" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="I60" s="32" t="s">
+      <c r="I60" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5824,7 +5846,7 @@
       <c r="H61" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="I61" s="32" t="s">
+      <c r="I61" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5853,7 +5875,7 @@
       <c r="H62" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="I62" s="32" t="s">
+      <c r="I62" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5882,7 +5904,7 @@
       <c r="H63" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="I63" s="32" t="s">
+      <c r="I63" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5911,7 +5933,7 @@
       <c r="H64" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="I64" s="32" t="s">
+      <c r="I64" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5940,7 +5962,7 @@
       <c r="H65" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="I65" s="32" t="s">
+      <c r="I65" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5969,7 +5991,7 @@
       <c r="H66" s="30" t="s">
         <v>200</v>
       </c>
-      <c r="I66" s="32" t="s">
+      <c r="I66" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5998,7 +6020,7 @@
       <c r="H67" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="I67" s="32" t="s">
+      <c r="I67" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -6027,7 +6049,7 @@
       <c r="H68" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="I68" s="32" t="s">
+      <c r="I68" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -6056,7 +6078,7 @@
       <c r="H69" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="I69" s="32" t="s">
+      <c r="I69" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -6085,7 +6107,7 @@
       <c r="H70" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="I70" s="32" t="s">
+      <c r="I70" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -6114,7 +6136,7 @@
       <c r="H71" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="I71" s="32" t="s">
+      <c r="I71" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -6143,7 +6165,7 @@
       <c r="H72" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="I72" s="32" t="s">
+      <c r="I72" s="31" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6172,7 +6194,7 @@
       <c r="H73" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="I73" s="32" t="s">
+      <c r="I73" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -6201,7 +6223,7 @@
       <c r="H74" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="I74" s="32" t="s">
+      <c r="I74" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -6230,7 +6252,7 @@
       <c r="H75" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="I75" s="32" t="s">
+      <c r="I75" s="31" t="s">
         <v>47</v>
       </c>
     </row>
@@ -6259,7 +6281,7 @@
       <c r="H76" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="I76" s="32" t="s">
+      <c r="I76" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -6288,7 +6310,7 @@
       <c r="H77" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="I77" s="32" t="s">
+      <c r="I77" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -6317,7 +6339,7 @@
       <c r="H78" s="30" t="s">
         <v>223</v>
       </c>
-      <c r="I78" s="32" t="s">
+      <c r="I78" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -6346,7 +6368,7 @@
       <c r="H79" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="I79" s="32" t="s">
+      <c r="I79" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -6375,7 +6397,7 @@
       <c r="H80" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="I80" s="32" t="s">
+      <c r="I80" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -6404,7 +6426,7 @@
       <c r="H81" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="I81" s="32" t="s">
+      <c r="I81" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -6433,7 +6455,7 @@
       <c r="H82" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="I82" s="32" t="s">
+      <c r="I82" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -6462,7 +6484,7 @@
       <c r="H83" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="I83" s="32" t="s">
+      <c r="I83" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6491,7 +6513,7 @@
       <c r="H84" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="I84" s="32" t="s">
+      <c r="I84" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -6520,7 +6542,7 @@
       <c r="H85" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="I85" s="32" t="s">
+      <c r="I85" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6549,7 +6571,7 @@
       <c r="H86" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="I86" s="32" t="s">
+      <c r="I86" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -6578,7 +6600,7 @@
       <c r="H87" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="I87" s="32" t="s">
+      <c r="I87" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -6607,7 +6629,7 @@
       <c r="H88" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="I88" s="32" t="s">
+      <c r="I88" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6636,7 +6658,7 @@
       <c r="H89" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="I89" s="32" t="s">
+      <c r="I89" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -6665,7 +6687,7 @@
       <c r="H90" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="I90" s="32" t="s">
+      <c r="I90" s="31" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6694,7 +6716,7 @@
       <c r="H91" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="I91" s="32" t="s">
+      <c r="I91" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -6723,7 +6745,7 @@
       <c r="H92" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="I92" s="32" t="s">
+      <c r="I92" s="31" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6752,7 +6774,7 @@
       <c r="H93" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="I93" s="32" t="s">
+      <c r="I93" s="31" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6781,7 +6803,7 @@
       <c r="H94" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="I94" s="32" t="s">
+      <c r="I94" s="31" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6810,7 +6832,7 @@
       <c r="H95" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="I95" s="32" t="s">
+      <c r="I95" s="31" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6839,7 +6861,7 @@
       <c r="H96" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="I96" s="32" t="s">
+      <c r="I96" s="31" t="s">
         <v>36</v>
       </c>
     </row>
@@ -6868,7 +6890,7 @@
       <c r="H97" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="I97" s="32" t="s">
+      <c r="I97" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -6897,7 +6919,7 @@
       <c r="H98" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="I98" s="32" t="s">
+      <c r="I98" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -6926,7 +6948,7 @@
       <c r="H99" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="I99" s="32" t="s">
+      <c r="I99" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -6955,7 +6977,7 @@
       <c r="H100" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="I100" s="32" t="s">
+      <c r="I100" s="31" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6984,7 +7006,7 @@
       <c r="H101" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="I101" s="32" t="s">
+      <c r="I101" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -7013,7 +7035,7 @@
       <c r="H102" s="30" t="s">
         <v>267</v>
       </c>
-      <c r="I102" s="32" t="s">
+      <c r="I102" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -7042,7 +7064,7 @@
       <c r="H103" s="30" t="s">
         <v>269</v>
       </c>
-      <c r="I103" s="32" t="s">
+      <c r="I103" s="31" t="s">
         <v>48</v>
       </c>
     </row>
@@ -7071,7 +7093,7 @@
       <c r="H104" s="30" t="s">
         <v>271</v>
       </c>
-      <c r="I104" s="32" t="s">
+      <c r="I104" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -7100,7 +7122,7 @@
       <c r="H105" s="30" t="s">
         <v>271</v>
       </c>
-      <c r="I105" s="32" t="s">
+      <c r="I105" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -7129,7 +7151,7 @@
       <c r="H106" s="30" t="s">
         <v>271</v>
       </c>
-      <c r="I106" s="32" t="s">
+      <c r="I106" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -7158,7 +7180,7 @@
       <c r="H107" s="30" t="s">
         <v>271</v>
       </c>
-      <c r="I107" s="32" t="s">
+      <c r="I107" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -7187,7 +7209,7 @@
       <c r="H108" s="30" t="s">
         <v>271</v>
       </c>
-      <c r="I108" s="32" t="s">
+      <c r="I108" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -7216,7 +7238,7 @@
       <c r="H109" s="30" t="s">
         <v>277</v>
       </c>
-      <c r="I109" s="32" t="s">
+      <c r="I109" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -7245,7 +7267,7 @@
       <c r="H110" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="I110" s="32" t="s">
+      <c r="I110" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7274,7 +7296,7 @@
       <c r="H111" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="I111" s="32" t="s">
+      <c r="I111" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7303,7 +7325,7 @@
       <c r="H112" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="I112" s="32" t="s">
+      <c r="I112" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7332,7 +7354,7 @@
       <c r="H113" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="I113" s="32" t="s">
+      <c r="I113" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7361,7 +7383,7 @@
       <c r="H114" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="I114" s="32" t="s">
+      <c r="I114" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7390,7 +7412,7 @@
       <c r="H115" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="I115" s="32" t="s">
+      <c r="I115" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7419,7 +7441,7 @@
       <c r="H116" s="30" t="s">
         <v>291</v>
       </c>
-      <c r="I116" s="32" t="s">
+      <c r="I116" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7448,7 +7470,7 @@
       <c r="H117" s="30" t="s">
         <v>293</v>
       </c>
-      <c r="I117" s="32" t="s">
+      <c r="I117" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7477,7 +7499,7 @@
       <c r="H118" s="30" t="s">
         <v>295</v>
       </c>
-      <c r="I118" s="32" t="s">
+      <c r="I118" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7506,7 +7528,7 @@
       <c r="H119" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="I119" s="32" t="s">
+      <c r="I119" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7535,7 +7557,7 @@
       <c r="H120" s="30" t="s">
         <v>299</v>
       </c>
-      <c r="I120" s="32" t="s">
+      <c r="I120" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7564,7 +7586,7 @@
       <c r="H121" s="30" t="s">
         <v>301</v>
       </c>
-      <c r="I121" s="32" t="s">
+      <c r="I121" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7593,7 +7615,7 @@
       <c r="H122" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="I122" s="32" t="s">
+      <c r="I122" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7622,7 +7644,7 @@
       <c r="H123" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="I123" s="32" t="s">
+      <c r="I123" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7651,7 +7673,7 @@
       <c r="H124" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="I124" s="32" t="s">
+      <c r="I124" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7680,7 +7702,7 @@
       <c r="H125" s="30" t="s">
         <v>309</v>
       </c>
-      <c r="I125" s="32" t="s">
+      <c r="I125" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7709,7 +7731,7 @@
       <c r="H126" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="I126" s="32" t="s">
+      <c r="I126" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7738,7 +7760,7 @@
       <c r="H127" s="30" t="s">
         <v>313</v>
       </c>
-      <c r="I127" s="32" t="s">
+      <c r="I127" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7767,7 +7789,7 @@
       <c r="H128" s="30" t="s">
         <v>315</v>
       </c>
-      <c r="I128" s="32" t="s">
+      <c r="I128" s="31" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7796,7 +7818,7 @@
       <c r="H129" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="I129" s="32" t="s">
+      <c r="I129" s="31" t="s">
         <v>38</v>
       </c>
     </row>
@@ -7825,7 +7847,7 @@
       <c r="H130" s="30" t="s">
         <v>318</v>
       </c>
-      <c r="I130" s="32" t="s">
+      <c r="I130" s="31" t="s">
         <v>38</v>
       </c>
     </row>
@@ -7854,7 +7876,7 @@
       <c r="H131" s="30" t="s">
         <v>320</v>
       </c>
-      <c r="I131" s="32" t="s">
+      <c r="I131" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -7883,7 +7905,7 @@
       <c r="H132" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="I132" s="32" t="s">
+      <c r="I132" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -7912,7 +7934,7 @@
       <c r="H133" s="30" t="s">
         <v>322</v>
       </c>
-      <c r="I133" s="32" t="s">
+      <c r="I133" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -7941,7 +7963,7 @@
       <c r="H134" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="I134" s="32" t="s">
+      <c r="I134" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -7970,7 +7992,7 @@
       <c r="H135" s="30" t="s">
         <v>328</v>
       </c>
-      <c r="I135" s="32" t="s">
+      <c r="I135" s="31" t="s">
         <v>47</v>
       </c>
     </row>
@@ -7999,7 +8021,7 @@
       <c r="H136" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="I136" s="32" t="s">
+      <c r="I136" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8028,7 +8050,7 @@
       <c r="H137" s="30" t="s">
         <v>332</v>
       </c>
-      <c r="I137" s="32" t="s">
+      <c r="I137" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8057,7 +8079,7 @@
       <c r="H138" s="30" t="s">
         <v>334</v>
       </c>
-      <c r="I138" s="32" t="s">
+      <c r="I138" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8086,7 +8108,7 @@
       <c r="H139" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="I139" s="32" t="s">
+      <c r="I139" s="31" t="s">
         <v>47</v>
       </c>
     </row>
@@ -8115,7 +8137,7 @@
       <c r="H140" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="I140" s="32" t="s">
+      <c r="I140" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8136,7 +8158,7 @@
         <v>338</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>732</v>
+        <v>6</v>
       </c>
       <c r="G141" s="30">
         <v>73</v>
@@ -8144,7 +8166,7 @@
       <c r="H141" s="30" t="s">
         <v>339</v>
       </c>
-      <c r="I141" s="32" t="s">
+      <c r="I141" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8173,7 +8195,7 @@
       <c r="H142" s="30" t="s">
         <v>341</v>
       </c>
-      <c r="I142" s="32" t="s">
+      <c r="I142" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -8202,7 +8224,7 @@
       <c r="H143" s="30" t="s">
         <v>344</v>
       </c>
-      <c r="I143" s="32" t="s">
+      <c r="I143" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -8231,7 +8253,7 @@
       <c r="H144" s="30" t="s">
         <v>346</v>
       </c>
-      <c r="I144" s="32" t="s">
+      <c r="I144" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -8260,7 +8282,7 @@
       <c r="H145" s="30" t="s">
         <v>347</v>
       </c>
-      <c r="I145" s="32" t="s">
+      <c r="I145" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -8289,7 +8311,7 @@
       <c r="H146" s="30" t="s">
         <v>348</v>
       </c>
-      <c r="I146" s="32" t="s">
+      <c r="I146" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -8318,7 +8340,7 @@
       <c r="H147" s="30" t="s">
         <v>349</v>
       </c>
-      <c r="I147" s="32" t="s">
+      <c r="I147" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -8347,7 +8369,7 @@
       <c r="H148" s="30" t="s">
         <v>350</v>
       </c>
-      <c r="I148" s="32" t="s">
+      <c r="I148" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -8376,7 +8398,7 @@
       <c r="H149" s="30" t="s">
         <v>351</v>
       </c>
-      <c r="I149" s="32" t="s">
+      <c r="I149" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -8405,7 +8427,7 @@
       <c r="H150" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="I150" s="32" t="s">
+      <c r="I150" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -8434,7 +8456,7 @@
       <c r="H151" s="30" t="s">
         <v>355</v>
       </c>
-      <c r="I151" s="32" t="s">
+      <c r="I151" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8463,7 +8485,7 @@
       <c r="H152" s="30" t="s">
         <v>357</v>
       </c>
-      <c r="I152" s="32" t="s">
+      <c r="I152" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8492,7 +8514,7 @@
       <c r="H153" s="30" t="s">
         <v>359</v>
       </c>
-      <c r="I153" s="32" t="s">
+      <c r="I153" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8521,7 +8543,7 @@
       <c r="H154" s="30" t="s">
         <v>361</v>
       </c>
-      <c r="I154" s="32" t="s">
+      <c r="I154" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8550,7 +8572,7 @@
       <c r="H155" s="30" t="s">
         <v>363</v>
       </c>
-      <c r="I155" s="32" t="s">
+      <c r="I155" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8579,7 +8601,7 @@
       <c r="H156" s="30" t="s">
         <v>364</v>
       </c>
-      <c r="I156" s="32" t="s">
+      <c r="I156" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8608,7 +8630,7 @@
       <c r="H157" s="30" t="s">
         <v>366</v>
       </c>
-      <c r="I157" s="32" t="s">
+      <c r="I157" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -8637,7 +8659,7 @@
       <c r="H158" s="30" t="s">
         <v>368</v>
       </c>
-      <c r="I158" s="32" t="s">
+      <c r="I158" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -8666,7 +8688,7 @@
       <c r="H159" s="30" t="s">
         <v>370</v>
       </c>
-      <c r="I159" s="32" t="s">
+      <c r="I159" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -8695,7 +8717,7 @@
       <c r="H160" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="I160" s="32" t="s">
+      <c r="I160" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -8724,7 +8746,7 @@
       <c r="H161" s="30" t="s">
         <v>374</v>
       </c>
-      <c r="I161" s="32" t="s">
+      <c r="I161" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -8753,7 +8775,7 @@
       <c r="H162" s="30" t="s">
         <v>376</v>
       </c>
-      <c r="I162" s="32" t="s">
+      <c r="I162" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -8782,7 +8804,7 @@
       <c r="H163" s="30" t="s">
         <v>378</v>
       </c>
-      <c r="I163" s="32" t="s">
+      <c r="I163" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -8811,7 +8833,7 @@
       <c r="H164" s="30" t="s">
         <v>378</v>
       </c>
-      <c r="I164" s="32" t="s">
+      <c r="I164" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -8840,7 +8862,7 @@
       <c r="H165" s="30" t="s">
         <v>380</v>
       </c>
-      <c r="I165" s="32" t="s">
+      <c r="I165" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -8869,7 +8891,7 @@
       <c r="H166" s="30" t="s">
         <v>382</v>
       </c>
-      <c r="I166" s="32" t="s">
+      <c r="I166" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -8898,7 +8920,7 @@
       <c r="H167" s="30" t="s">
         <v>384</v>
       </c>
-      <c r="I167" s="32" t="s">
+      <c r="I167" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -8927,7 +8949,7 @@
       <c r="H168" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="I168" s="32" t="s">
+      <c r="I168" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -8956,7 +8978,7 @@
       <c r="H169" s="30" t="s">
         <v>374</v>
       </c>
-      <c r="I169" s="32" t="s">
+      <c r="I169" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -8985,7 +9007,7 @@
       <c r="H170" s="30" t="s">
         <v>388</v>
       </c>
-      <c r="I170" s="32" t="s">
+      <c r="I170" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -9014,7 +9036,7 @@
       <c r="H171" s="30" t="s">
         <v>380</v>
       </c>
-      <c r="I171" s="32" t="s">
+      <c r="I171" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -9043,7 +9065,7 @@
       <c r="H172" s="30" t="s">
         <v>388</v>
       </c>
-      <c r="I172" s="32" t="s">
+      <c r="I172" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -9072,7 +9094,7 @@
       <c r="H173" s="30" t="s">
         <v>392</v>
       </c>
-      <c r="I173" s="32" t="s">
+      <c r="I173" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9101,7 +9123,7 @@
       <c r="H174" s="30" t="s">
         <v>394</v>
       </c>
-      <c r="I174" s="32" t="s">
+      <c r="I174" s="31" t="s">
         <v>36</v>
       </c>
     </row>
@@ -9130,7 +9152,7 @@
       <c r="H175" s="30" t="s">
         <v>396</v>
       </c>
-      <c r="I175" s="32" t="s">
+      <c r="I175" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -9159,7 +9181,7 @@
       <c r="H176" s="30" t="s">
         <v>398</v>
       </c>
-      <c r="I176" s="32" t="s">
+      <c r="I176" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -9188,7 +9210,7 @@
       <c r="H177" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="I177" s="32" t="s">
+      <c r="I177" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9217,7 +9239,7 @@
       <c r="H178" s="30" t="s">
         <v>400</v>
       </c>
-      <c r="I178" s="32" t="s">
+      <c r="I178" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -9246,7 +9268,7 @@
       <c r="H179" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="I179" s="32" t="s">
+      <c r="I179" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -9275,7 +9297,7 @@
       <c r="H180" s="30" t="s">
         <v>404</v>
       </c>
-      <c r="I180" s="32" t="s">
+      <c r="I180" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -9304,7 +9326,7 @@
       <c r="H181" s="30" t="s">
         <v>406</v>
       </c>
-      <c r="I181" s="32" t="s">
+      <c r="I181" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -9333,7 +9355,7 @@
       <c r="H182" s="30" t="s">
         <v>408</v>
       </c>
-      <c r="I182" s="32" t="s">
+      <c r="I182" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -9362,7 +9384,7 @@
       <c r="H183" s="30" t="s">
         <v>410</v>
       </c>
-      <c r="I183" s="32" t="s">
+      <c r="I183" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -9391,7 +9413,7 @@
       <c r="H184" s="30" t="s">
         <v>412</v>
       </c>
-      <c r="I184" s="32" t="s">
+      <c r="I184" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -9420,7 +9442,7 @@
       <c r="H185" s="30" t="s">
         <v>414</v>
       </c>
-      <c r="I185" s="32" t="s">
+      <c r="I185" s="31" t="s">
         <v>38</v>
       </c>
     </row>
@@ -9449,7 +9471,7 @@
       <c r="H186" s="30" t="s">
         <v>416</v>
       </c>
-      <c r="I186" s="32" t="s">
+      <c r="I186" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -9478,7 +9500,7 @@
       <c r="H187" s="30" t="s">
         <v>418</v>
       </c>
-      <c r="I187" s="32" t="s">
+      <c r="I187" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -9507,7 +9529,7 @@
       <c r="H188" s="30" t="s">
         <v>425</v>
       </c>
-      <c r="I188" s="32" t="s">
+      <c r="I188" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9536,7 +9558,7 @@
       <c r="H189" s="30" t="s">
         <v>427</v>
       </c>
-      <c r="I189" s="32" t="s">
+      <c r="I189" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -9565,7 +9587,7 @@
       <c r="H190" s="30" t="s">
         <v>422</v>
       </c>
-      <c r="I190" s="32" t="s">
+      <c r="I190" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -9594,7 +9616,7 @@
       <c r="H191" s="30" t="s">
         <v>420</v>
       </c>
-      <c r="I191" s="32" t="s">
+      <c r="I191" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9623,7 +9645,7 @@
       <c r="H192" s="30" t="s">
         <v>428</v>
       </c>
-      <c r="I192" s="32" t="s">
+      <c r="I192" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9652,7 +9674,7 @@
       <c r="H193" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="I193" s="32" t="s">
+      <c r="I193" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9681,7 +9703,7 @@
       <c r="H194" s="30" t="s">
         <v>430</v>
       </c>
-      <c r="I194" s="32" t="s">
+      <c r="I194" s="31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -9710,7 +9732,7 @@
       <c r="H195" s="30" t="s">
         <v>433</v>
       </c>
-      <c r="I195" s="32" t="s">
+      <c r="I195" s="31" t="s">
         <v>47</v>
       </c>
     </row>
@@ -9739,7 +9761,7 @@
       <c r="H196" s="30" t="s">
         <v>435</v>
       </c>
-      <c r="I196" s="32" t="s">
+      <c r="I196" s="31" t="s">
         <v>47</v>
       </c>
     </row>
@@ -9768,7 +9790,7 @@
       <c r="H197" s="30" t="s">
         <v>437</v>
       </c>
-      <c r="I197" s="32" t="s">
+      <c r="I197" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -9797,7 +9819,7 @@
       <c r="H198" s="30" t="s">
         <v>439</v>
       </c>
-      <c r="I198" s="32" t="s">
+      <c r="I198" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -9826,7 +9848,7 @@
       <c r="H199" s="30" t="s">
         <v>441</v>
       </c>
-      <c r="I199" s="32" t="s">
+      <c r="I199" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -9855,7 +9877,7 @@
       <c r="H200" s="30" t="s">
         <v>443</v>
       </c>
-      <c r="I200" s="32" t="s">
+      <c r="I200" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9884,7 +9906,7 @@
       <c r="H201" s="30" t="s">
         <v>445</v>
       </c>
-      <c r="I201" s="32" t="s">
+      <c r="I201" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9913,7 +9935,7 @@
       <c r="H202" s="30" t="s">
         <v>447</v>
       </c>
-      <c r="I202" s="32" t="s">
+      <c r="I202" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9942,7 +9964,7 @@
       <c r="H203" s="30" t="s">
         <v>449</v>
       </c>
-      <c r="I203" s="32" t="s">
+      <c r="I203" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9971,7 +9993,7 @@
       <c r="H204" s="30" t="s">
         <v>451</v>
       </c>
-      <c r="I204" s="32" t="s">
+      <c r="I204" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10000,7 +10022,7 @@
       <c r="H205" s="30" t="s">
         <v>453</v>
       </c>
-      <c r="I205" s="32" t="s">
+      <c r="I205" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -10029,7 +10051,7 @@
       <c r="H206" s="30" t="s">
         <v>455</v>
       </c>
-      <c r="I206" s="32" t="s">
+      <c r="I206" s="31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -10058,7 +10080,7 @@
       <c r="H207" s="30" t="s">
         <v>457</v>
       </c>
-      <c r="I207" s="32" t="s">
+      <c r="I207" s="31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -10087,7 +10109,7 @@
       <c r="H208" s="30" t="s">
         <v>459</v>
       </c>
-      <c r="I208" s="32" t="s">
+      <c r="I208" s="31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -10116,7 +10138,7 @@
       <c r="H209" s="30" t="s">
         <v>461</v>
       </c>
-      <c r="I209" s="32" t="s">
+      <c r="I209" s="31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -10145,7 +10167,7 @@
       <c r="H210" s="30" t="s">
         <v>463</v>
       </c>
-      <c r="I210" s="32" t="s">
+      <c r="I210" s="31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -10174,7 +10196,7 @@
       <c r="H211" s="30" t="s">
         <v>465</v>
       </c>
-      <c r="I211" s="32" t="s">
+      <c r="I211" s="31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -10203,7 +10225,7 @@
       <c r="H212" s="30" t="s">
         <v>467</v>
       </c>
-      <c r="I212" s="32" t="s">
+      <c r="I212" s="31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -10232,7 +10254,7 @@
       <c r="H213" s="30" t="s">
         <v>469</v>
       </c>
-      <c r="I213" s="32" t="s">
+      <c r="I213" s="31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -10261,7 +10283,7 @@
       <c r="H214" s="30" t="s">
         <v>471</v>
       </c>
-      <c r="I214" s="32" t="s">
+      <c r="I214" s="31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -10290,7 +10312,7 @@
       <c r="H215" s="30" t="s">
         <v>473</v>
       </c>
-      <c r="I215" s="32" t="s">
+      <c r="I215" s="31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -10319,7 +10341,7 @@
       <c r="H216" s="30" t="s">
         <v>334</v>
       </c>
-      <c r="I216" s="32" t="s">
+      <c r="I216" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10348,7 +10370,7 @@
       <c r="H217" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="I217" s="32" t="s">
+      <c r="I217" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10377,7 +10399,7 @@
       <c r="H218" s="30" t="s">
         <v>477</v>
       </c>
-      <c r="I218" s="32" t="s">
+      <c r="I218" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10406,7 +10428,7 @@
       <c r="H219" s="30" t="s">
         <v>479</v>
       </c>
-      <c r="I219" s="32" t="s">
+      <c r="I219" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10435,7 +10457,7 @@
       <c r="H220" s="30" t="s">
         <v>481</v>
       </c>
-      <c r="I220" s="32" t="s">
+      <c r="I220" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10464,7 +10486,7 @@
       <c r="H221" s="30" t="s">
         <v>483</v>
       </c>
-      <c r="I221" s="32" t="s">
+      <c r="I221" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -10493,7 +10515,7 @@
       <c r="H222" s="30" t="s">
         <v>485</v>
       </c>
-      <c r="I222" s="32" t="s">
+      <c r="I222" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -10501,28 +10523,28 @@
       <c r="A223" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="B223" s="44">
+      <c r="B223" s="34">
         <v>46279</v>
       </c>
-      <c r="C223" s="45">
+      <c r="C223" s="35">
         <v>46280</v>
       </c>
-      <c r="D223" s="44">
+      <c r="D223" s="34">
         <v>46339</v>
       </c>
-      <c r="E223" s="40" t="s">
+      <c r="E223" s="36" t="s">
         <v>486</v>
       </c>
-      <c r="F223" s="40" t="s">
+      <c r="F223" s="36" t="s">
         <v>6</v>
       </c>
       <c r="G223" s="30">
         <v>63</v>
       </c>
-      <c r="H223" s="40" t="s">
+      <c r="H223" s="36" t="s">
         <v>487</v>
       </c>
-      <c r="I223" s="32" t="s">
+      <c r="I223" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10530,28 +10552,28 @@
       <c r="A224" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B224" s="44">
+      <c r="B224" s="34">
         <v>46279</v>
       </c>
-      <c r="C224" s="45">
+      <c r="C224" s="35">
         <v>46280</v>
       </c>
-      <c r="D224" s="44">
+      <c r="D224" s="34">
         <v>46339</v>
       </c>
-      <c r="E224" s="40" t="s">
+      <c r="E224" s="36" t="s">
         <v>488</v>
       </c>
-      <c r="F224" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="G224" s="41">
+      <c r="F224" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G224" s="39">
         <v>279</v>
       </c>
-      <c r="H224" s="40" t="s">
+      <c r="H224" s="36" t="s">
         <v>489</v>
       </c>
-      <c r="I224" s="32" t="s">
+      <c r="I224" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10559,28 +10581,28 @@
       <c r="A225" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="B225" s="46">
+      <c r="B225" s="34">
         <v>46279</v>
       </c>
-      <c r="C225" s="47">
+      <c r="C225" s="35">
         <v>46280</v>
       </c>
-      <c r="D225" s="46">
+      <c r="D225" s="34">
         <v>46339</v>
       </c>
-      <c r="E225" s="42" t="s">
+      <c r="E225" s="36" t="s">
         <v>488</v>
       </c>
-      <c r="F225" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="G225" s="43">
+      <c r="F225" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G225" s="39">
         <v>99</v>
       </c>
-      <c r="H225" s="42" t="s">
+      <c r="H225" s="36" t="s">
         <v>490</v>
       </c>
-      <c r="I225" s="32" t="s">
+      <c r="I225" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10588,28 +10610,28 @@
       <c r="A226" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="B226" s="44">
+      <c r="B226" s="34">
         <v>46267</v>
       </c>
-      <c r="C226" s="45">
+      <c r="C226" s="35">
         <v>46280</v>
       </c>
-      <c r="D226" s="44">
+      <c r="D226" s="34">
         <v>46328</v>
       </c>
-      <c r="E226" s="40" t="s">
+      <c r="E226" s="36" t="s">
         <v>491</v>
       </c>
-      <c r="F226" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="G226" s="41">
+      <c r="F226" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G226" s="39">
         <v>151</v>
       </c>
-      <c r="H226" s="40" t="s">
+      <c r="H226" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="I226" s="32" t="s">
+      <c r="I226" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -10617,28 +10639,28 @@
       <c r="A227" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="B227" s="46">
+      <c r="B227" s="34">
         <v>46267</v>
       </c>
-      <c r="C227" s="47">
+      <c r="C227" s="35">
         <v>46280</v>
       </c>
-      <c r="D227" s="46">
+      <c r="D227" s="34">
         <v>46328</v>
       </c>
-      <c r="E227" s="42" t="s">
+      <c r="E227" s="36" t="s">
         <v>492</v>
       </c>
-      <c r="F227" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="G227" s="43">
+      <c r="F227" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G227" s="39">
         <v>102</v>
       </c>
-      <c r="H227" s="42" t="s">
+      <c r="H227" s="36" t="s">
         <v>493</v>
       </c>
-      <c r="I227" s="32" t="s">
+      <c r="I227" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -10646,28 +10668,28 @@
       <c r="A228" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="B228" s="44">
+      <c r="B228" s="34">
         <v>46280</v>
       </c>
-      <c r="C228" s="45">
+      <c r="C228" s="35">
         <v>46280</v>
       </c>
-      <c r="D228" s="44">
+      <c r="D228" s="34">
         <v>46330</v>
       </c>
-      <c r="E228" s="40" t="s">
+      <c r="E228" s="36" t="s">
         <v>494</v>
       </c>
-      <c r="F228" s="40" t="s">
+      <c r="F228" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G228" s="41">
+      <c r="G228" s="39">
         <v>91</v>
       </c>
-      <c r="H228" s="40" t="s">
+      <c r="H228" s="36" t="s">
         <v>495</v>
       </c>
-      <c r="I228" s="32" t="s">
+      <c r="I228" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -10675,28 +10697,28 @@
       <c r="A229" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="B229" s="46">
+      <c r="B229" s="34">
         <v>46280</v>
       </c>
-      <c r="C229" s="47">
+      <c r="C229" s="35">
         <v>46280</v>
       </c>
-      <c r="D229" s="46">
+      <c r="D229" s="34">
         <v>46330</v>
       </c>
-      <c r="E229" s="42" t="s">
+      <c r="E229" s="36" t="s">
         <v>496</v>
       </c>
-      <c r="F229" s="42" t="s">
+      <c r="F229" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G229" s="43">
+      <c r="G229" s="39">
         <v>19</v>
       </c>
-      <c r="H229" s="42" t="s">
+      <c r="H229" s="36" t="s">
         <v>497</v>
       </c>
-      <c r="I229" s="32" t="s">
+      <c r="I229" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -10704,28 +10726,28 @@
       <c r="A230" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="B230" s="44">
+      <c r="B230" s="34">
         <v>46279</v>
       </c>
-      <c r="C230" s="45">
+      <c r="C230" s="35">
         <v>46280</v>
       </c>
-      <c r="D230" s="44">
+      <c r="D230" s="34">
         <v>46341</v>
       </c>
-      <c r="E230" s="40" t="s">
+      <c r="E230" s="36" t="s">
         <v>498</v>
       </c>
-      <c r="F230" s="40" t="s">
+      <c r="F230" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G230" s="41">
+      <c r="G230" s="39">
         <v>7</v>
       </c>
-      <c r="H230" s="40" t="s">
+      <c r="H230" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="I230" s="32" t="s">
+      <c r="I230" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10733,28 +10755,28 @@
       <c r="A231" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="B231" s="44">
+      <c r="B231" s="34">
         <v>46266</v>
       </c>
-      <c r="C231" s="45">
+      <c r="C231" s="35">
         <v>46281</v>
       </c>
-      <c r="D231" s="44">
+      <c r="D231" s="34">
         <v>46327</v>
       </c>
-      <c r="E231" s="40" t="s">
+      <c r="E231" s="36" t="s">
         <v>499</v>
       </c>
-      <c r="F231" s="40" t="s">
+      <c r="F231" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G231" s="41">
+      <c r="G231" s="39">
         <v>35</v>
       </c>
-      <c r="H231" s="40" t="s">
+      <c r="H231" s="36" t="s">
         <v>500</v>
       </c>
-      <c r="I231" s="32" t="s">
+      <c r="I231" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -10762,28 +10784,28 @@
       <c r="A232" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="B232" s="46">
+      <c r="B232" s="34">
         <v>46266</v>
       </c>
-      <c r="C232" s="47">
+      <c r="C232" s="35">
         <v>46281</v>
       </c>
-      <c r="D232" s="46">
+      <c r="D232" s="34">
         <v>46327</v>
       </c>
-      <c r="E232" s="42" t="s">
+      <c r="E232" s="36" t="s">
         <v>499</v>
       </c>
-      <c r="F232" s="42" t="s">
+      <c r="F232" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G232" s="43">
+      <c r="G232" s="39">
         <v>32</v>
       </c>
-      <c r="H232" s="42" t="s">
+      <c r="H232" s="36" t="s">
         <v>501</v>
       </c>
-      <c r="I232" s="32" t="s">
+      <c r="I232" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -10812,7 +10834,7 @@
       <c r="H233" s="30" t="s">
         <v>504</v>
       </c>
-      <c r="I233" s="32" t="s">
+      <c r="I233" s="31" t="s">
         <v>38</v>
       </c>
     </row>
@@ -10841,7 +10863,7 @@
       <c r="H234" s="30" t="s">
         <v>507</v>
       </c>
-      <c r="I234" s="32" t="s">
+      <c r="I234" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -10870,7 +10892,7 @@
       <c r="H235" s="30" t="s">
         <v>509</v>
       </c>
-      <c r="I235" s="32" t="s">
+      <c r="I235" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -10899,7 +10921,7 @@
       <c r="H236" s="30" t="s">
         <v>511</v>
       </c>
-      <c r="I236" s="32" t="s">
+      <c r="I236" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -10928,7 +10950,7 @@
       <c r="H237" s="30" t="s">
         <v>513</v>
       </c>
-      <c r="I237" s="32" t="s">
+      <c r="I237" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -10957,7 +10979,7 @@
       <c r="H238" s="30" t="s">
         <v>515</v>
       </c>
-      <c r="I238" s="32" t="s">
+      <c r="I238" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -10986,7 +11008,7 @@
       <c r="H239" s="30" t="s">
         <v>517</v>
       </c>
-      <c r="I239" s="32" t="s">
+      <c r="I239" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11015,7 +11037,7 @@
       <c r="H240" s="30" t="s">
         <v>519</v>
       </c>
-      <c r="I240" s="32" t="s">
+      <c r="I240" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11044,7 +11066,7 @@
       <c r="H241" s="30" t="s">
         <v>521</v>
       </c>
-      <c r="I241" s="32" t="s">
+      <c r="I241" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11073,7 +11095,7 @@
       <c r="H242" s="30" t="s">
         <v>523</v>
       </c>
-      <c r="I242" s="32" t="s">
+      <c r="I242" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11102,7 +11124,7 @@
       <c r="H243" s="30" t="s">
         <v>525</v>
       </c>
-      <c r="I243" s="32" t="s">
+      <c r="I243" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11131,7 +11153,7 @@
       <c r="H244" s="30" t="s">
         <v>527</v>
       </c>
-      <c r="I244" s="32" t="s">
+      <c r="I244" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11160,7 +11182,7 @@
       <c r="H245" s="30" t="s">
         <v>529</v>
       </c>
-      <c r="I245" s="32" t="s">
+      <c r="I245" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11189,7 +11211,7 @@
       <c r="H246" s="30" t="s">
         <v>531</v>
       </c>
-      <c r="I246" s="32" t="s">
+      <c r="I246" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11218,7 +11240,7 @@
       <c r="H247" s="30" t="s">
         <v>533</v>
       </c>
-      <c r="I247" s="32" t="s">
+      <c r="I247" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11247,7 +11269,7 @@
       <c r="H248" s="30" t="s">
         <v>535</v>
       </c>
-      <c r="I248" s="32" t="s">
+      <c r="I248" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11276,7 +11298,7 @@
       <c r="H249" s="30" t="s">
         <v>537</v>
       </c>
-      <c r="I249" s="32" t="s">
+      <c r="I249" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11305,7 +11327,7 @@
       <c r="H250" s="30" t="s">
         <v>539</v>
       </c>
-      <c r="I250" s="32" t="s">
+      <c r="I250" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11334,7 +11356,7 @@
       <c r="H251" s="30" t="s">
         <v>541</v>
       </c>
-      <c r="I251" s="32" t="s">
+      <c r="I251" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11363,7 +11385,7 @@
       <c r="H252" s="30" t="s">
         <v>543</v>
       </c>
-      <c r="I252" s="32" t="s">
+      <c r="I252" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11392,7 +11414,7 @@
       <c r="H253" s="30" t="s">
         <v>545</v>
       </c>
-      <c r="I253" s="32" t="s">
+      <c r="I253" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11421,7 +11443,7 @@
       <c r="H254" s="30" t="s">
         <v>547</v>
       </c>
-      <c r="I254" s="32" t="s">
+      <c r="I254" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11450,7 +11472,7 @@
       <c r="H255" s="30" t="s">
         <v>549</v>
       </c>
-      <c r="I255" s="32" t="s">
+      <c r="I255" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11479,7 +11501,7 @@
       <c r="H256" s="30" t="s">
         <v>551</v>
       </c>
-      <c r="I256" s="32" t="s">
+      <c r="I256" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11508,7 +11530,7 @@
       <c r="H257" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="I257" s="32" t="s">
+      <c r="I257" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11537,7 +11559,7 @@
       <c r="H258" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="I258" s="32" t="s">
+      <c r="I258" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11566,7 +11588,7 @@
       <c r="H259" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="I259" s="32" t="s">
+      <c r="I259" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11595,7 +11617,7 @@
       <c r="H260" s="30" t="s">
         <v>559</v>
       </c>
-      <c r="I260" s="32" t="s">
+      <c r="I260" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11624,7 +11646,7 @@
       <c r="H261" s="30" t="s">
         <v>561</v>
       </c>
-      <c r="I261" s="32" t="s">
+      <c r="I261" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11653,7 +11675,7 @@
       <c r="H262" s="30" t="s">
         <v>563</v>
       </c>
-      <c r="I262" s="32" t="s">
+      <c r="I262" s="31" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11682,7 +11704,7 @@
       <c r="H263" s="30" t="s">
         <v>565</v>
       </c>
-      <c r="I263" s="32" t="s">
+      <c r="I263" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -11711,7 +11733,7 @@
       <c r="H264" s="30" t="s">
         <v>567</v>
       </c>
-      <c r="I264" s="32" t="s">
+      <c r="I264" s="31" t="s">
         <v>36</v>
       </c>
     </row>
@@ -11740,7 +11762,7 @@
       <c r="H265" s="30" t="s">
         <v>569</v>
       </c>
-      <c r="I265" s="32" t="s">
+      <c r="I265" s="31" t="s">
         <v>36</v>
       </c>
     </row>
@@ -11769,7 +11791,7 @@
       <c r="H266" s="30" t="s">
         <v>570</v>
       </c>
-      <c r="I266" s="32" t="s">
+      <c r="I266" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -11798,7 +11820,7 @@
       <c r="H267" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="I267" s="32" t="s">
+      <c r="I267" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -11827,7 +11849,7 @@
       <c r="H268" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="I268" s="32" t="s">
+      <c r="I268" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -11856,7 +11878,7 @@
       <c r="H269" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="I269" s="32" t="s">
+      <c r="I269" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -11885,7 +11907,7 @@
       <c r="H270" s="30" t="s">
         <v>574</v>
       </c>
-      <c r="I270" s="32" t="s">
+      <c r="I270" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -11914,7 +11936,7 @@
       <c r="H271" s="30" t="s">
         <v>575</v>
       </c>
-      <c r="I271" s="32" t="s">
+      <c r="I271" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -11943,7 +11965,7 @@
       <c r="H272" s="30" t="s">
         <v>577</v>
       </c>
-      <c r="I272" s="32" t="s">
+      <c r="I272" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -11972,7 +11994,7 @@
       <c r="H273" s="30" t="s">
         <v>579</v>
       </c>
-      <c r="I273" s="32" t="s">
+      <c r="I273" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12001,7 +12023,7 @@
       <c r="H274" s="30" t="s">
         <v>581</v>
       </c>
-      <c r="I274" s="32" t="s">
+      <c r="I274" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12030,7 +12052,7 @@
       <c r="H275" s="30" t="s">
         <v>582</v>
       </c>
-      <c r="I275" s="32" t="s">
+      <c r="I275" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12059,7 +12081,7 @@
       <c r="H276" s="30" t="s">
         <v>584</v>
       </c>
-      <c r="I276" s="32" t="s">
+      <c r="I276" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12088,7 +12110,7 @@
       <c r="H277" s="30" t="s">
         <v>586</v>
       </c>
-      <c r="I277" s="32" t="s">
+      <c r="I277" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12117,7 +12139,7 @@
       <c r="H278" s="30" t="s">
         <v>588</v>
       </c>
-      <c r="I278" s="32" t="s">
+      <c r="I278" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12146,7 +12168,7 @@
       <c r="H279" s="30" t="s">
         <v>590</v>
       </c>
-      <c r="I279" s="32" t="s">
+      <c r="I279" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12175,7 +12197,7 @@
       <c r="H280" s="30" t="s">
         <v>591</v>
       </c>
-      <c r="I280" s="32" t="s">
+      <c r="I280" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12204,7 +12226,7 @@
       <c r="H281" s="30" t="s">
         <v>593</v>
       </c>
-      <c r="I281" s="32" t="s">
+      <c r="I281" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12233,7 +12255,7 @@
       <c r="H282" s="30" t="s">
         <v>595</v>
       </c>
-      <c r="I282" s="32" t="s">
+      <c r="I282" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12262,7 +12284,7 @@
       <c r="H283" s="30" t="s">
         <v>596</v>
       </c>
-      <c r="I283" s="32" t="s">
+      <c r="I283" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12291,7 +12313,7 @@
       <c r="H284" s="30" t="s">
         <v>597</v>
       </c>
-      <c r="I284" s="32" t="s">
+      <c r="I284" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12320,7 +12342,7 @@
       <c r="H285" s="30" t="s">
         <v>599</v>
       </c>
-      <c r="I285" s="32" t="s">
+      <c r="I285" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12349,7 +12371,7 @@
       <c r="H286" s="30" t="s">
         <v>601</v>
       </c>
-      <c r="I286" s="32" t="s">
+      <c r="I286" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12378,7 +12400,7 @@
       <c r="H287" s="30" t="s">
         <v>603</v>
       </c>
-      <c r="I287" s="32" t="s">
+      <c r="I287" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12407,7 +12429,7 @@
       <c r="H288" s="30" t="s">
         <v>604</v>
       </c>
-      <c r="I288" s="32" t="s">
+      <c r="I288" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -12436,7 +12458,7 @@
       <c r="H289" s="30" t="s">
         <v>606</v>
       </c>
-      <c r="I289" s="32" t="s">
+      <c r="I289" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -12465,7 +12487,7 @@
       <c r="H290" s="30" t="s">
         <v>608</v>
       </c>
-      <c r="I290" s="32" t="s">
+      <c r="I290" s="31" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12494,7 +12516,7 @@
       <c r="H291" s="30" t="s">
         <v>610</v>
       </c>
-      <c r="I291" s="32" t="s">
+      <c r="I291" s="31" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12523,7 +12545,7 @@
       <c r="H292" s="30" t="s">
         <v>612</v>
       </c>
-      <c r="I292" s="32" t="s">
+      <c r="I292" s="31" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12552,7 +12574,7 @@
       <c r="H293" s="30" t="s">
         <v>614</v>
       </c>
-      <c r="I293" s="32" t="s">
+      <c r="I293" s="31" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12581,7 +12603,7 @@
       <c r="H294" s="30" t="s">
         <v>616</v>
       </c>
-      <c r="I294" s="32" t="s">
+      <c r="I294" s="31" t="s">
         <v>31</v>
       </c>
     </row>
@@ -12610,7 +12632,7 @@
       <c r="H295" s="30" t="s">
         <v>618</v>
       </c>
-      <c r="I295" s="32" t="s">
+      <c r="I295" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -12639,7 +12661,7 @@
       <c r="H296" s="30" t="s">
         <v>620</v>
       </c>
-      <c r="I296" s="32" t="s">
+      <c r="I296" s="31" t="s">
         <v>31</v>
       </c>
     </row>
@@ -12668,7 +12690,7 @@
       <c r="H297" s="30" t="s">
         <v>622</v>
       </c>
-      <c r="I297" s="32" t="s">
+      <c r="I297" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12697,7 +12719,7 @@
       <c r="H298" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="I298" s="32" t="s">
+      <c r="I298" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12726,7 +12748,7 @@
       <c r="H299" s="30" t="s">
         <v>626</v>
       </c>
-      <c r="I299" s="32" t="s">
+      <c r="I299" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12755,7 +12777,7 @@
       <c r="H300" s="30" t="s">
         <v>627</v>
       </c>
-      <c r="I300" s="32" t="s">
+      <c r="I300" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -12784,7 +12806,7 @@
       <c r="H301" s="30" t="s">
         <v>618</v>
       </c>
-      <c r="I301" s="32" t="s">
+      <c r="I301" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -12813,7 +12835,7 @@
       <c r="H302" s="30" t="s">
         <v>629</v>
       </c>
-      <c r="I302" s="32" t="s">
+      <c r="I302" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -12842,7 +12864,7 @@
       <c r="H303" s="30" t="s">
         <v>631</v>
       </c>
-      <c r="I303" s="32" t="s">
+      <c r="I303" s="31" t="s">
         <v>39</v>
       </c>
     </row>
@@ -12871,7 +12893,7 @@
       <c r="H304" s="30" t="s">
         <v>633</v>
       </c>
-      <c r="I304" s="32" t="s">
+      <c r="I304" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -12900,7 +12922,7 @@
       <c r="H305" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="I305" s="32" t="s">
+      <c r="I305" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -12929,7 +12951,7 @@
       <c r="H306" s="30" t="s">
         <v>639</v>
       </c>
-      <c r="I306" s="32" t="s">
+      <c r="I306" s="31" t="s">
         <v>38</v>
       </c>
     </row>
@@ -12958,7 +12980,7 @@
       <c r="H307" s="30" t="s">
         <v>322</v>
       </c>
-      <c r="I307" s="32" t="s">
+      <c r="I307" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -12987,7 +13009,7 @@
       <c r="H308" s="30" t="s">
         <v>641</v>
       </c>
-      <c r="I308" s="32" t="s">
+      <c r="I308" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13016,7 +13038,7 @@
       <c r="H309" s="30" t="s">
         <v>643</v>
       </c>
-      <c r="I309" s="32" t="s">
+      <c r="I309" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13045,7 +13067,7 @@
       <c r="H310" s="30" t="s">
         <v>645</v>
       </c>
-      <c r="I310" s="32" t="s">
+      <c r="I310" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13074,7 +13096,7 @@
       <c r="H311" s="30" t="s">
         <v>647</v>
       </c>
-      <c r="I311" s="32" t="s">
+      <c r="I311" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13103,7 +13125,7 @@
       <c r="H312" s="30" t="s">
         <v>649</v>
       </c>
-      <c r="I312" s="32" t="s">
+      <c r="I312" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13132,7 +13154,7 @@
       <c r="H313" s="30" t="s">
         <v>651</v>
       </c>
-      <c r="I313" s="32" t="s">
+      <c r="I313" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13161,7 +13183,7 @@
       <c r="H314" s="30" t="s">
         <v>653</v>
       </c>
-      <c r="I314" s="32" t="s">
+      <c r="I314" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13190,7 +13212,7 @@
       <c r="H315" s="30" t="s">
         <v>655</v>
       </c>
-      <c r="I315" s="32" t="s">
+      <c r="I315" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13219,7 +13241,7 @@
       <c r="H316" s="30" t="s">
         <v>657</v>
       </c>
-      <c r="I316" s="32" t="s">
+      <c r="I316" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13248,7 +13270,7 @@
       <c r="H317" s="30" t="s">
         <v>659</v>
       </c>
-      <c r="I317" s="32" t="s">
+      <c r="I317" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13277,7 +13299,7 @@
       <c r="H318" s="30" t="s">
         <v>661</v>
       </c>
-      <c r="I318" s="32" t="s">
+      <c r="I318" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13306,7 +13328,7 @@
       <c r="H319" s="30" t="s">
         <v>663</v>
       </c>
-      <c r="I319" s="32" t="s">
+      <c r="I319" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13335,7 +13357,7 @@
       <c r="H320" s="30" t="s">
         <v>665</v>
       </c>
-      <c r="I320" s="32" t="s">
+      <c r="I320" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13364,7 +13386,7 @@
       <c r="H321" s="30" t="s">
         <v>667</v>
       </c>
-      <c r="I321" s="32" t="s">
+      <c r="I321" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13393,7 +13415,7 @@
       <c r="H322" s="30" t="s">
         <v>669</v>
       </c>
-      <c r="I322" s="32" t="s">
+      <c r="I322" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13422,7 +13444,7 @@
       <c r="H323" s="30" t="s">
         <v>671</v>
       </c>
-      <c r="I323" s="32" t="s">
+      <c r="I323" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13451,7 +13473,7 @@
       <c r="H324" s="30" t="s">
         <v>673</v>
       </c>
-      <c r="I324" s="32" t="s">
+      <c r="I324" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13480,7 +13502,7 @@
       <c r="H325" s="30" t="s">
         <v>675</v>
       </c>
-      <c r="I325" s="32" t="s">
+      <c r="I325" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13509,7 +13531,7 @@
       <c r="H326" s="30" t="s">
         <v>677</v>
       </c>
-      <c r="I326" s="32" t="s">
+      <c r="I326" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13538,7 +13560,7 @@
       <c r="H327" s="30" t="s">
         <v>679</v>
       </c>
-      <c r="I327" s="32" t="s">
+      <c r="I327" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13567,7 +13589,7 @@
       <c r="H328" s="30" t="s">
         <v>681</v>
       </c>
-      <c r="I328" s="32" t="s">
+      <c r="I328" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13596,7 +13618,7 @@
       <c r="H329" s="30" t="s">
         <v>683</v>
       </c>
-      <c r="I329" s="32" t="s">
+      <c r="I329" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13625,7 +13647,7 @@
       <c r="H330" s="30" t="s">
         <v>685</v>
       </c>
-      <c r="I330" s="32" t="s">
+      <c r="I330" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13654,7 +13676,7 @@
       <c r="H331" s="30" t="s">
         <v>687</v>
       </c>
-      <c r="I331" s="32" t="s">
+      <c r="I331" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13683,7 +13705,7 @@
       <c r="H332" s="30" t="s">
         <v>689</v>
       </c>
-      <c r="I332" s="32" t="s">
+      <c r="I332" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13712,7 +13734,7 @@
       <c r="H333" s="30" t="s">
         <v>691</v>
       </c>
-      <c r="I333" s="32" t="s">
+      <c r="I333" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13741,7 +13763,7 @@
       <c r="H334" s="30" t="s">
         <v>693</v>
       </c>
-      <c r="I334" s="32" t="s">
+      <c r="I334" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13770,7 +13792,7 @@
       <c r="H335" s="30" t="s">
         <v>695</v>
       </c>
-      <c r="I335" s="32" t="s">
+      <c r="I335" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13799,7 +13821,7 @@
       <c r="H336" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="I336" s="32" t="s">
+      <c r="I336" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -13828,7 +13850,7 @@
       <c r="H337" s="30" t="s">
         <v>698</v>
       </c>
-      <c r="I337" s="32" t="s">
+      <c r="I337" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -13857,7 +13879,7 @@
       <c r="H338" s="30" t="s">
         <v>700</v>
       </c>
-      <c r="I338" s="32" t="s">
+      <c r="I338" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -13886,7 +13908,7 @@
       <c r="H339" s="30" t="s">
         <v>702</v>
       </c>
-      <c r="I339" s="32" t="s">
+      <c r="I339" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -13915,7 +13937,7 @@
       <c r="H340" s="28" t="s">
         <v>704</v>
       </c>
-      <c r="I340" s="32" t="s">
+      <c r="I340" s="31" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13944,7 +13966,7 @@
       <c r="H341" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="I341" s="32" t="s">
+      <c r="I341" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -13973,7 +13995,7 @@
       <c r="H342" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="I342" s="32" t="s">
+      <c r="I342" s="31" t="s">
         <v>34</v>
       </c>
     </row>
@@ -14002,7 +14024,7 @@
       <c r="H343" s="28" t="s">
         <v>706</v>
       </c>
-      <c r="I343" s="32" t="s">
+      <c r="I343" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -14031,7 +14053,7 @@
       <c r="H344" s="28" t="s">
         <v>708</v>
       </c>
-      <c r="I344" s="32" t="s">
+      <c r="I344" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -14060,7 +14082,7 @@
       <c r="H345" s="28" t="s">
         <v>710</v>
       </c>
-      <c r="I345" s="32" t="s">
+      <c r="I345" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -14089,7 +14111,7 @@
       <c r="H346" s="28" t="s">
         <v>712</v>
       </c>
-      <c r="I346" s="32" t="s">
+      <c r="I346" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -14118,7 +14140,7 @@
       <c r="H347" s="28" t="s">
         <v>714</v>
       </c>
-      <c r="I347" s="32" t="s">
+      <c r="I347" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -14147,7 +14169,7 @@
       <c r="H348" s="28" t="s">
         <v>579</v>
       </c>
-      <c r="I348" s="32" t="s">
+      <c r="I348" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -14176,7 +14198,7 @@
       <c r="H349" s="28" t="s">
         <v>581</v>
       </c>
-      <c r="I349" s="32" t="s">
+      <c r="I349" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -14205,7 +14227,7 @@
       <c r="H350" s="28" t="s">
         <v>586</v>
       </c>
-      <c r="I350" s="32" t="s">
+      <c r="I350" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -14234,7 +14256,7 @@
       <c r="H351" s="28" t="s">
         <v>584</v>
       </c>
-      <c r="I351" s="32" t="s">
+      <c r="I351" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -14263,7 +14285,7 @@
       <c r="H352" s="28" t="s">
         <v>603</v>
       </c>
-      <c r="I352" s="32" t="s">
+      <c r="I352" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -14292,7 +14314,7 @@
       <c r="H353" s="28" t="s">
         <v>719</v>
       </c>
-      <c r="I353" s="32" t="s">
+      <c r="I353" s="31" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14310,7 +14332,7 @@
         <v>46363</v>
       </c>
       <c r="E354" s="38" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F354" s="38" t="s">
         <v>52</v>
@@ -14319,9 +14341,9 @@
         <v>87</v>
       </c>
       <c r="H354" s="28" t="s">
-        <v>722</v>
-      </c>
-      <c r="I354" s="32" t="s">
+        <v>721</v>
+      </c>
+      <c r="I354" s="31" t="s">
         <v>41</v>
       </c>
     </row>
@@ -14339,7 +14361,7 @@
         <v>46391</v>
       </c>
       <c r="E355" s="28" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F355" s="28" t="s">
         <v>52</v>
@@ -14348,9 +14370,9 @@
         <v>12</v>
       </c>
       <c r="H355" s="30" t="s">
-        <v>724</v>
-      </c>
-      <c r="I355" s="32" t="s">
+        <v>723</v>
+      </c>
+      <c r="I355" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -14368,7 +14390,7 @@
         <v>46276</v>
       </c>
       <c r="E356" s="28" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="F356" s="28" t="s">
         <v>52</v>
@@ -14377,9 +14399,9 @@
         <v>148</v>
       </c>
       <c r="H356" s="30" t="s">
-        <v>726</v>
-      </c>
-      <c r="I356" s="32" t="s">
+        <v>725</v>
+      </c>
+      <c r="I356" s="31" t="s">
         <v>45</v>
       </c>
     </row>
@@ -14397,7 +14419,7 @@
         <v>46356</v>
       </c>
       <c r="E357" s="28" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F357" s="28" t="s">
         <v>6</v>
@@ -14406,9 +14428,9 @@
         <v>2</v>
       </c>
       <c r="H357" s="30" t="s">
-        <v>728</v>
-      </c>
-      <c r="I357" s="32" t="s">
+        <v>727</v>
+      </c>
+      <c r="I357" s="31" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14426,7 +14448,7 @@
         <v>46363</v>
       </c>
       <c r="E358" s="28" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F358" s="28" t="s">
         <v>6</v>
@@ -14435,10 +14457,358 @@
         <v>80</v>
       </c>
       <c r="H358" s="30" t="s">
+        <v>729</v>
+      </c>
+      <c r="I358" s="31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B359" s="41">
+        <v>46303</v>
+      </c>
+      <c r="C359" s="41">
+        <v>46303</v>
+      </c>
+      <c r="D359" s="41">
+        <v>46363</v>
+      </c>
+      <c r="E359" s="38" t="s">
         <v>730</v>
       </c>
-      <c r="I358" s="32" t="s">
-        <v>41</v>
+      <c r="F359" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="G359" s="39">
+        <v>42</v>
+      </c>
+      <c r="H359" s="28" t="s">
+        <v>735</v>
+      </c>
+      <c r="I359" s="31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="B360" s="34">
+        <v>46302</v>
+      </c>
+      <c r="C360" s="34">
+        <v>46303</v>
+      </c>
+      <c r="D360" s="34">
+        <v>46391</v>
+      </c>
+      <c r="E360" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="F360" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G360" s="39">
+        <v>74</v>
+      </c>
+      <c r="H360" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="I360" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="B361" s="34">
+        <v>46304</v>
+      </c>
+      <c r="C361" s="34">
+        <v>46304</v>
+      </c>
+      <c r="D361" s="34">
+        <v>46367</v>
+      </c>
+      <c r="E361" s="38" t="s">
+        <v>731</v>
+      </c>
+      <c r="F361" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="G361" s="39">
+        <v>1</v>
+      </c>
+      <c r="H361" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="I361" s="31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="B362" s="34">
+        <v>46304</v>
+      </c>
+      <c r="C362" s="34">
+        <v>46304</v>
+      </c>
+      <c r="D362" s="34">
+        <v>46367</v>
+      </c>
+      <c r="E362" s="38" t="s">
+        <v>732</v>
+      </c>
+      <c r="F362" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="G362" s="39">
+        <v>2</v>
+      </c>
+      <c r="H362" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="I362" s="31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B363" s="34">
+        <v>46304</v>
+      </c>
+      <c r="C363" s="34">
+        <v>46307</v>
+      </c>
+      <c r="D363" s="34">
+        <v>46365</v>
+      </c>
+      <c r="E363" s="38" t="s">
+        <v>733</v>
+      </c>
+      <c r="F363" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="G363" s="39">
+        <v>5</v>
+      </c>
+      <c r="H363" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="I363" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A364" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B364" s="34">
+        <v>46304</v>
+      </c>
+      <c r="C364" s="34">
+        <v>46307</v>
+      </c>
+      <c r="D364" s="34">
+        <v>46365</v>
+      </c>
+      <c r="E364" s="38" t="s">
+        <v>734</v>
+      </c>
+      <c r="F364" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="G364" s="39">
+        <v>3</v>
+      </c>
+      <c r="H364" s="28" t="s">
+        <v>736</v>
+      </c>
+      <c r="I364" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A365" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B365" s="29">
+        <v>46307</v>
+      </c>
+      <c r="C365" s="29">
+        <v>46308</v>
+      </c>
+      <c r="D365" s="29">
+        <v>46367</v>
+      </c>
+      <c r="E365" s="28" t="s">
+        <v>715</v>
+      </c>
+      <c r="F365" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G365" s="30">
+        <v>7</v>
+      </c>
+      <c r="H365" s="30" t="s">
+        <v>738</v>
+      </c>
+      <c r="I365" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A366" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B366" s="29">
+        <v>46307</v>
+      </c>
+      <c r="C366" s="29">
+        <v>46308</v>
+      </c>
+      <c r="D366" s="29">
+        <v>46367</v>
+      </c>
+      <c r="E366" s="28" t="s">
+        <v>715</v>
+      </c>
+      <c r="F366" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G366" s="30">
+        <v>1</v>
+      </c>
+      <c r="H366" s="30" t="s">
+        <v>597</v>
+      </c>
+      <c r="I366" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A367" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B367" s="29">
+        <v>46308</v>
+      </c>
+      <c r="C367" s="29">
+        <v>46308</v>
+      </c>
+      <c r="D367" s="29">
+        <v>46370</v>
+      </c>
+      <c r="E367" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="F367" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G367" s="30">
+        <v>2</v>
+      </c>
+      <c r="H367" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="I367" s="31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A368" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B368" s="29">
+        <v>46308</v>
+      </c>
+      <c r="C368" s="29">
+        <v>46308</v>
+      </c>
+      <c r="D368" s="29">
+        <v>46370</v>
+      </c>
+      <c r="E368" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="F368" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G368" s="30">
+        <v>18</v>
+      </c>
+      <c r="H368" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="I368" s="31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A369" s="28" t="s">
+        <v>502</v>
+      </c>
+      <c r="B369" s="29">
+        <v>46309</v>
+      </c>
+      <c r="C369" s="29">
+        <v>46309</v>
+      </c>
+      <c r="D369" s="29">
+        <v>46370</v>
+      </c>
+      <c r="E369" s="28" t="s">
+        <v>739</v>
+      </c>
+      <c r="F369" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G369" s="30">
+        <v>116</v>
+      </c>
+      <c r="H369" s="30" t="s">
+        <v>740</v>
+      </c>
+      <c r="I369" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A370" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B370" s="29">
+        <v>46300</v>
+      </c>
+      <c r="C370" s="29">
+        <v>46309</v>
+      </c>
+      <c r="D370" s="29">
+        <v>46345</v>
+      </c>
+      <c r="E370" s="28" t="s">
+        <v>741</v>
+      </c>
+      <c r="F370" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G370" s="30">
+        <v>137</v>
+      </c>
+      <c r="H370" s="30" t="s">
+        <v>742</v>
+      </c>
+      <c r="I370" s="31" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -14455,7 +14825,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I358</xm:sqref>
+          <xm:sqref>I3:I370</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -14576,7 +14946,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>720</v>
+        <v>737</v>
       </c>
       <c r="E1"/>
     </row>
@@ -14764,6 +15134,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82b749e3-8208-459a-bfc0-9b428d09cbab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E614ED5C53901F4C88FF6AEBBF3D8E0D" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="529ed3825ab478a5ffdc44eb265dc6f5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="82b749e3-8208-459a-bfc0-9b428d09cbab" xmlns:ns3="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7c2030912f9588e16c624efbe24e62a" ns2:_="" ns3:_="">
     <xsd:import namespace="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
@@ -14970,28 +15360,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEAC05D-976A-4D1B-BF88-C07869576FC8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82b749e3-8208-459a-bfc0-9b428d09cbab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50F94E65-68E1-47F0-9BED-AA8CE5F487F1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48B8CB07-104F-4796-83F1-C004B434531E}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78C5D531-1085-40EB-9017-D3176F92DEED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -15009,31 +15404,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E2FA099-008C-4EDE-BD9D-84353A57EDC8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5881772-74BF-4FAC-848F-7C2FDA9A8D30}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" removed="0"/>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jchinn2\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29AF7EE8-79B1-4F51-BE6A-4B705A337962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFE79D4D-0B77-47F4-A288-FAD4FDF0655F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -15363,14 +15363,14 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEAC05D-976A-4D1B-BF88-C07869576FC8}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jchinn2\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFE79D4D-0B77-47F4-A288-FAD4FDF0655F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66561CC6-3A32-444D-BAF5-6F490CB904D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="771">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2339,6 +2339,81 @@
     <t>1520 E. Sepulveda Blvd.  Carson CA 90745</t>
   </si>
   <si>
+    <t>5820 Owens Dr.  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>The Neil Jones Food Company dba Tomatek</t>
+  </si>
+  <si>
+    <t>2025 N Street  Firebaugh CA 93622</t>
+  </si>
+  <si>
+    <t>Menzies Aviation</t>
+  </si>
+  <si>
+    <t>1 World Way  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>Fender Musical Instruments Corporation</t>
+  </si>
+  <si>
+    <t>311 Cessna Circle  Corona CA 92878</t>
+  </si>
+  <si>
+    <t>Myers Power Products, Inc.</t>
+  </si>
+  <si>
+    <t>2950 East Philadelphia Street  Ontario CA 91761</t>
+  </si>
+  <si>
+    <t>Formagrid Inc. dba Airtable</t>
+  </si>
+  <si>
+    <t>One Front Street, 28th Floor  San Francisco CA 94111</t>
+  </si>
+  <si>
+    <t>Silverado Senior Living Managment Inc.</t>
+  </si>
+  <si>
+    <t>514 North Prospect Avenue  Redondo Beach CA 90277</t>
+  </si>
+  <si>
+    <t>Baloian Farms</t>
+  </si>
+  <si>
+    <t>446 N. Blythe Ave.  Fresno CA 93706</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals and Kaiser Foundation Health Plan, Inc. (1800 Harrison St.)</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals and Kaiser Foundation Health Plan, Inc. (One Kaiser Plaza)</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals and Kaiser Foundation Health Plan, Inc. (75 N. Fair Oaks Ave.)</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals and Kaiser Foundation Health Plan, Inc. (99 S. Oakland Ave.)</t>
+  </si>
+  <si>
+    <t>1650 Los Gamos Dr.  San Rafael CA 94903</t>
+  </si>
+  <si>
+    <t>Tree Service Unlimited Inc.</t>
+  </si>
+  <si>
+    <t>4080 Plaza Goldorado Circle Ste A  Cameron Park CA 95682</t>
+  </si>
+  <si>
+    <t>5808 Sunset Blvd  Los Angeles CA 90028</t>
+  </si>
+  <si>
+    <t>121 Albright Way  Los Gatos CA 95032</t>
+  </si>
+  <si>
+    <t>Relocation Permanent</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2358,7 +2433,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 10/14/2026
+01/01/2023 - 10/21/2026
 </t>
     </r>
     <r>
@@ -2372,19 +2447,25 @@
     </r>
   </si>
   <si>
-    <t>5820 Owens Dr.  Pleasanton CA 94588</t>
-  </si>
-  <si>
-    <t>The Neil Jones Food Company dba Tomatek</t>
-  </si>
-  <si>
-    <t>2025 N Street  Firebaugh CA 93622</t>
-  </si>
-  <si>
-    <t>Menzies Aviation</t>
-  </si>
-  <si>
-    <t>1 World Way  Los Angeles CA 90045</t>
+    <t>Safeway, Inc.</t>
+  </si>
+  <si>
+    <t>905 South 34th Street  Richmond CA 94804</t>
+  </si>
+  <si>
+    <t>Randstad (Dreyer's Grand Ice Cream)</t>
+  </si>
+  <si>
+    <t>eBay Inc.</t>
+  </si>
+  <si>
+    <t>2025 Hamilton Ave  San Jose CA 95125</t>
+  </si>
+  <si>
+    <t>4941 Allison Parkway Suite B Vacaville CA 95688</t>
+  </si>
+  <si>
+    <t>970 E Continental  Tulare CA 93274</t>
   </si>
   <si>
     <r>
@@ -2398,7 +2479,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 10/14/2026</t>
+      <t>07/01/26 to 10/21/2026</t>
     </r>
     <r>
       <rPr>
@@ -2418,7 +2499,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I370.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I392.</t>
     </r>
   </si>
 </sst>
@@ -3224,6 +3305,42 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3488,42 +3605,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFF9E7"/>
@@ -3586,35 +3667,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BE651B3D-87EE-436C-B33F-C1564840D30D}" name="WarnReportSummary" displayName="WarnReportSummary" ref="A2:B9" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BE651B3D-87EE-436C-B33F-C1564840D30D}" name="WarnReportSummary" displayName="WarnReportSummary" ref="A2:B9" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A2:B9" xr:uid="{BE651B3D-87EE-436C-B33F-C1564840D30D}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{27E39F38-3125-453D-8079-314461C0A408}" name="Report Summary" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{BC59C82C-A192-4C58-973D-25AB492E21BC}" name="Total" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{27E39F38-3125-453D-8079-314461C0A408}" name="Report Summary" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{BC59C82C-A192-4C58-973D-25AB492E21BC}" name="Total" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I370" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A2:I370" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I392" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I392" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I358">
     <sortCondition ref="C2:C358"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{C6D12265-C94C-4E06-8034-3C717447E155}" name="Processed_x000a_Date" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{B3ED9634-5328-42A8-B322-3BC02B1B09B6}" name="Effective _x000a_Date" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{9D38EF5A-DEC2-4452-98D6-CF4FB3342379}" name="Company" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{211DDDC0-B68A-4CB6-AB53-3FF3E63F26A0}" name="Layoff/_x000a_Closure" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{5A996A7E-F604-41CE-AC0B-D6BC2FB09F5A}" name="No. Of_x000a_Employees" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{6BB24B8B-7A22-4DE0-B907-BC4F68AE8678}" name="Address" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{695F1FD1-01CF-43F8-8B40-37D320A0AC01}" name="Related Industry" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{C6D12265-C94C-4E06-8034-3C717447E155}" name="Processed_x000a_Date" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{B3ED9634-5328-42A8-B322-3BC02B1B09B6}" name="Effective _x000a_Date" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{9D38EF5A-DEC2-4452-98D6-CF4FB3342379}" name="Company" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{211DDDC0-B68A-4CB6-AB53-3FF3E63F26A0}" name="Layoff/_x000a_Closure" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{5A996A7E-F604-41CE-AC0B-D6BC2FB09F5A}" name="No. Of_x000a_Employees" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{6BB24B8B-7A22-4DE0-B907-BC4F68AE8678}" name="Address" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{695F1FD1-01CF-43F8-8B40-37D320A0AC01}" name="Related Industry" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4022,7 +4103,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>17617</v>
+        <v>21262</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4031,7 +4112,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>244</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4040,7 +4121,7 @@
       </c>
       <c r="B5" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4058,7 +4139,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4067,7 +4148,7 @@
       </c>
       <c r="B8" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4090,7 +4171,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I370"/>
+  <dimension ref="A1:I392"/>
   <sheetFormatPr defaultColWidth="150.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -4106,7 +4187,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -8158,7 +8239,7 @@
         <v>338</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>6</v>
+        <v>761</v>
       </c>
       <c r="G141" s="30">
         <v>73</v>
@@ -14660,7 +14741,7 @@
         <v>7</v>
       </c>
       <c r="H365" s="30" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="I365" s="31" t="s">
         <v>45</v>
@@ -14767,7 +14848,7 @@
         <v>46370</v>
       </c>
       <c r="E369" s="28" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F369" s="28" t="s">
         <v>129</v>
@@ -14776,7 +14857,7 @@
         <v>116</v>
       </c>
       <c r="H369" s="30" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="I369" s="31" t="s">
         <v>34</v>
@@ -14796,7 +14877,7 @@
         <v>46345</v>
       </c>
       <c r="E370" s="28" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F370" s="28" t="s">
         <v>6</v>
@@ -14805,10 +14886,648 @@
         <v>137</v>
       </c>
       <c r="H370" s="30" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I370" s="31" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B371" s="29">
+        <v>46310</v>
+      </c>
+      <c r="C371" s="29">
+        <v>46310</v>
+      </c>
+      <c r="D371" s="29">
+        <v>46370</v>
+      </c>
+      <c r="E371" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F371" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G371" s="30">
+        <v>533</v>
+      </c>
+      <c r="H371" s="30" t="s">
+        <v>743</v>
+      </c>
+      <c r="I371" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B372" s="29">
+        <v>46304</v>
+      </c>
+      <c r="C372" s="29">
+        <v>46310</v>
+      </c>
+      <c r="D372" s="29">
+        <v>46371</v>
+      </c>
+      <c r="E372" s="28" t="s">
+        <v>744</v>
+      </c>
+      <c r="F372" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G372" s="30">
+        <v>206</v>
+      </c>
+      <c r="H372" s="30" t="s">
+        <v>745</v>
+      </c>
+      <c r="I372" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B373" s="29">
+        <v>46310</v>
+      </c>
+      <c r="C373" s="29">
+        <v>46310</v>
+      </c>
+      <c r="D373" s="29">
+        <v>46402</v>
+      </c>
+      <c r="E373" s="28" t="s">
+        <v>746</v>
+      </c>
+      <c r="F373" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G373" s="30">
+        <v>190</v>
+      </c>
+      <c r="H373" s="30" t="s">
+        <v>747</v>
+      </c>
+      <c r="I373" s="31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B374" s="29">
+        <v>46309</v>
+      </c>
+      <c r="C374" s="29">
+        <v>46310</v>
+      </c>
+      <c r="D374" s="29">
+        <v>46371</v>
+      </c>
+      <c r="E374" s="28" t="s">
+        <v>748</v>
+      </c>
+      <c r="F374" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G374" s="30">
+        <v>7</v>
+      </c>
+      <c r="H374" s="30" t="s">
+        <v>749</v>
+      </c>
+      <c r="I374" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" s="28" t="s">
+        <v>502</v>
+      </c>
+      <c r="B375" s="29">
+        <v>46296</v>
+      </c>
+      <c r="C375" s="29">
+        <v>46311</v>
+      </c>
+      <c r="D375" s="29">
+        <v>46325</v>
+      </c>
+      <c r="E375" s="28" t="s">
+        <v>750</v>
+      </c>
+      <c r="F375" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G375" s="30">
+        <v>106</v>
+      </c>
+      <c r="H375" s="30" t="s">
+        <v>751</v>
+      </c>
+      <c r="I375" s="31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B376" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C376" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D376" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E376" s="28" t="s">
+        <v>752</v>
+      </c>
+      <c r="F376" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G376" s="30">
+        <v>1</v>
+      </c>
+      <c r="H376" s="30" t="s">
+        <v>577</v>
+      </c>
+      <c r="I376" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B377" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C377" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D377" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E377" s="28" t="s">
+        <v>753</v>
+      </c>
+      <c r="F377" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G377" s="30">
+        <v>5</v>
+      </c>
+      <c r="H377" s="30" t="s">
+        <v>579</v>
+      </c>
+      <c r="I377" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B378" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C378" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D378" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E378" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="F378" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G378" s="30">
+        <v>1</v>
+      </c>
+      <c r="H378" s="30" t="s">
+        <v>588</v>
+      </c>
+      <c r="I378" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B379" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C379" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D379" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E379" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="F379" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G379" s="30">
+        <v>1</v>
+      </c>
+      <c r="H379" s="30" t="s">
+        <v>590</v>
+      </c>
+      <c r="I379" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" s="28" t="s">
+        <v>634</v>
+      </c>
+      <c r="B380" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C380" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D380" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E380" s="28" t="s">
+        <v>715</v>
+      </c>
+      <c r="F380" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G380" s="30">
+        <v>1</v>
+      </c>
+      <c r="H380" s="30" t="s">
+        <v>756</v>
+      </c>
+      <c r="I380" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A381" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B381" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C381" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D381" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E381" s="28" t="s">
+        <v>715</v>
+      </c>
+      <c r="F381" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G381" s="30">
+        <v>1</v>
+      </c>
+      <c r="H381" s="30" t="s">
+        <v>595</v>
+      </c>
+      <c r="I381" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A382" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B382" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C382" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D382" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E382" s="28" t="s">
+        <v>715</v>
+      </c>
+      <c r="F382" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G382" s="30">
+        <v>1</v>
+      </c>
+      <c r="H382" s="30" t="s">
+        <v>596</v>
+      </c>
+      <c r="I382" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A383" s="28" t="s">
+        <v>342</v>
+      </c>
+      <c r="B383" s="29">
+        <v>46308</v>
+      </c>
+      <c r="C383" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D383" s="29">
+        <v>46370</v>
+      </c>
+      <c r="E383" s="28" t="s">
+        <v>757</v>
+      </c>
+      <c r="F383" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G383" s="30">
+        <v>137</v>
+      </c>
+      <c r="H383" s="30" t="s">
+        <v>758</v>
+      </c>
+      <c r="I383" s="31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A384" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B384" s="29">
+        <v>46311</v>
+      </c>
+      <c r="C384" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D384" s="29">
+        <v>46279</v>
+      </c>
+      <c r="E384" s="28" t="s">
+        <v>317</v>
+      </c>
+      <c r="F384" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G384" s="30">
+        <v>267</v>
+      </c>
+      <c r="H384" s="30" t="s">
+        <v>759</v>
+      </c>
+      <c r="I384" s="31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A385" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B385" s="29">
+        <v>46311</v>
+      </c>
+      <c r="C385" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D385" s="29">
+        <v>46279</v>
+      </c>
+      <c r="E385" s="28" t="s">
+        <v>317</v>
+      </c>
+      <c r="F385" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G385" s="30">
+        <v>227</v>
+      </c>
+      <c r="H385" s="30" t="s">
+        <v>760</v>
+      </c>
+      <c r="I385" s="31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A386" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B386" s="29">
+        <v>46315</v>
+      </c>
+      <c r="C386" s="29">
+        <v>46315</v>
+      </c>
+      <c r="D386" s="29">
+        <v>46375</v>
+      </c>
+      <c r="E386" s="28" t="s">
+        <v>617</v>
+      </c>
+      <c r="F386" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G386" s="30">
+        <v>380</v>
+      </c>
+      <c r="H386" s="30" t="s">
+        <v>618</v>
+      </c>
+      <c r="I386" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A387" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B387" s="29">
+        <v>46315</v>
+      </c>
+      <c r="C387" s="29">
+        <v>46315</v>
+      </c>
+      <c r="D387" s="29">
+        <v>46376</v>
+      </c>
+      <c r="E387" s="28" t="s">
+        <v>763</v>
+      </c>
+      <c r="F387" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G387" s="30">
+        <v>92</v>
+      </c>
+      <c r="H387" s="30" t="s">
+        <v>764</v>
+      </c>
+      <c r="I387" s="31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A388" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B388" s="29">
+        <v>46315</v>
+      </c>
+      <c r="C388" s="29">
+        <v>46315</v>
+      </c>
+      <c r="D388" s="29">
+        <v>46375</v>
+      </c>
+      <c r="E388" s="28" t="s">
+        <v>765</v>
+      </c>
+      <c r="F388" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G388" s="30">
+        <v>91</v>
+      </c>
+      <c r="H388" s="30" t="s">
+        <v>627</v>
+      </c>
+      <c r="I388" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A389" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B389" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C389" s="29">
+        <v>46316</v>
+      </c>
+      <c r="D389" s="29">
+        <v>46375</v>
+      </c>
+      <c r="E389" s="28" t="s">
+        <v>617</v>
+      </c>
+      <c r="F389" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G389" s="30">
+        <v>715</v>
+      </c>
+      <c r="H389" s="30" t="s">
+        <v>618</v>
+      </c>
+      <c r="I389" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A390" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B390" s="29">
+        <v>46316</v>
+      </c>
+      <c r="C390" s="29">
+        <v>46316</v>
+      </c>
+      <c r="D390" s="29">
+        <v>46316</v>
+      </c>
+      <c r="E390" s="28" t="s">
+        <v>766</v>
+      </c>
+      <c r="F390" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G390" s="30">
+        <v>229</v>
+      </c>
+      <c r="H390" s="30" t="s">
+        <v>767</v>
+      </c>
+      <c r="I390" s="31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A391" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B391" s="29">
+        <v>46316</v>
+      </c>
+      <c r="C391" s="29">
+        <v>46316</v>
+      </c>
+      <c r="D391" s="29">
+        <v>46379</v>
+      </c>
+      <c r="E391" s="28" t="s">
+        <v>498</v>
+      </c>
+      <c r="F391" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G391" s="30">
+        <v>6</v>
+      </c>
+      <c r="H391" s="30" t="s">
+        <v>768</v>
+      </c>
+      <c r="I391" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A392" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B392" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C392" s="29">
+        <v>46316</v>
+      </c>
+      <c r="D392" s="29">
+        <v>46375</v>
+      </c>
+      <c r="E392" s="28" t="s">
+        <v>617</v>
+      </c>
+      <c r="F392" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G392" s="30">
+        <v>448</v>
+      </c>
+      <c r="H392" s="30" t="s">
+        <v>769</v>
+      </c>
+      <c r="I392" s="31" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -14825,7 +15544,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I370</xm:sqref>
+          <xm:sqref>I3:I392</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -14946,7 +15665,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>737</v>
+        <v>762</v>
       </c>
       <c r="E1"/>
     </row>
@@ -15134,26 +15853,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82b749e3-8208-459a-bfc0-9b428d09cbab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E614ED5C53901F4C88FF6AEBBF3D8E0D" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="529ed3825ab478a5ffdc44eb265dc6f5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="82b749e3-8208-459a-bfc0-9b428d09cbab" xmlns:ns3="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7c2030912f9588e16c624efbe24e62a" ns2:_="" ns3:_="">
     <xsd:import namespace="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
@@ -15360,33 +16059,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEAC05D-976A-4D1B-BF88-C07869576FC8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50F94E65-68E1-47F0-9BED-AA8CE5F487F1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82b749e3-8208-459a-bfc0-9b428d09cbab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78C5D531-1085-40EB-9017-D3176F92DEED}">
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{177B7A0E-FF32-4156-AD26-40F8A8D9C534}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -15404,8 +16098,33 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F132A3CF-F853-4244-80FB-C7965FFC7437}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B30A08B-9F6D-4095-B44F-A85D48EE2410}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" removed="0"/>
+  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" contentBits="0" removed="0"/>
 </clbl:labelList>
 </file>
--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66561CC6-3A32-444D-BAF5-6F490CB904D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46201A9A-59F8-4028-AF33-2BE8FF906E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="784">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2414,6 +2414,27 @@
     <t>Relocation Permanent</t>
   </si>
   <si>
+    <t>Safeway, Inc.</t>
+  </si>
+  <si>
+    <t>905 South 34th Street  Richmond CA 94804</t>
+  </si>
+  <si>
+    <t>Randstad (Dreyer's Grand Ice Cream)</t>
+  </si>
+  <si>
+    <t>eBay Inc.</t>
+  </si>
+  <si>
+    <t>2025 Hamilton Ave  San Jose CA 95125</t>
+  </si>
+  <si>
+    <t>4941 Allison Parkway Suite B Vacaville CA 95688</t>
+  </si>
+  <si>
+    <t>970 E Continental  Tulare CA 93274</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2433,7 +2454,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 10/21/2026
+01/01/2023 - 10/26/2026
 </t>
     </r>
     <r>
@@ -2447,25 +2468,43 @@
     </r>
   </si>
   <si>
-    <t>Safeway, Inc.</t>
-  </si>
-  <si>
-    <t>905 South 34th Street  Richmond CA 94804</t>
-  </si>
-  <si>
-    <t>Randstad (Dreyer's Grand Ice Cream)</t>
-  </si>
-  <si>
-    <t>eBay Inc.</t>
-  </si>
-  <si>
-    <t>2025 Hamilton Ave  San Jose CA 95125</t>
-  </si>
-  <si>
-    <t>4941 Allison Parkway Suite B Vacaville CA 95688</t>
-  </si>
-  <si>
-    <t>970 E Continental  Tulare CA 93274</t>
+    <t>Georg Fischer Signet LLC</t>
+  </si>
+  <si>
+    <t>5462 North Irwindale Avenue  Baldwin Park CA 91706</t>
+  </si>
+  <si>
+    <t>Intel Corporation</t>
+  </si>
+  <si>
+    <t>1900 Prairie City Road  Folsom CA 95630</t>
+  </si>
+  <si>
+    <t>24Hr Homecare</t>
+  </si>
+  <si>
+    <t>Conduent State &amp; Local Solutions, Inc.</t>
+  </si>
+  <si>
+    <t>375 Beale Street  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>The Madrona</t>
+  </si>
+  <si>
+    <t>1001 Westside Road  Healdsburg CA 95448</t>
+  </si>
+  <si>
+    <t>Everidge Inc.</t>
+  </si>
+  <si>
+    <t>8886 White Oak Ave  Rancho Cucamonga CA 91730</t>
+  </si>
+  <si>
+    <t>Tawa, Inc. dba 99 Ranch Market</t>
+  </si>
+  <si>
+    <t>4024 Grand Avenue  Chino CA 91710</t>
   </si>
   <si>
     <r>
@@ -2479,7 +2518,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 10/21/2026</t>
+      <t>07/01/26 to 10/26/2026</t>
     </r>
     <r>
       <rPr>
@@ -2499,7 +2538,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I392.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I399.</t>
     </r>
   </si>
 </sst>
@@ -3681,10 +3720,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I392" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I392" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I358">
-    <sortCondition ref="C2:C358"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I399" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I399" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I399">
+    <sortCondition ref="C2:C399"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="29"/>
@@ -4103,7 +4142,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>21262</v>
+        <v>22591</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4112,7 +4151,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4139,7 +4178,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4148,7 +4187,7 @@
       </c>
       <c r="B8" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4171,7 +4210,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I392"/>
+  <dimension ref="A1:I399"/>
   <sheetFormatPr defaultColWidth="150.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -4187,7 +4226,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>770</v>
+        <v>783</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -14590,7 +14629,7 @@
         <v>338</v>
       </c>
       <c r="F360" s="38" t="s">
-        <v>6</v>
+        <v>761</v>
       </c>
       <c r="G360" s="39">
         <v>74</v>
@@ -15370,7 +15409,7 @@
         <v>46376</v>
       </c>
       <c r="E387" s="28" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F387" s="28" t="s">
         <v>52</v>
@@ -15379,7 +15418,7 @@
         <v>92</v>
       </c>
       <c r="H387" s="30" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="I387" s="31" t="s">
         <v>36</v>
@@ -15399,7 +15438,7 @@
         <v>46375</v>
       </c>
       <c r="E388" s="28" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F388" s="28" t="s">
         <v>101</v>
@@ -15457,7 +15496,7 @@
         <v>46316</v>
       </c>
       <c r="E390" s="28" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F390" s="28" t="s">
         <v>6</v>
@@ -15466,7 +15505,7 @@
         <v>229</v>
       </c>
       <c r="H390" s="30" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="I390" s="31" t="s">
         <v>36</v>
@@ -15495,7 +15534,7 @@
         <v>6</v>
       </c>
       <c r="H391" s="30" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="I391" s="31" t="s">
         <v>34</v>
@@ -15524,10 +15563,213 @@
         <v>448</v>
       </c>
       <c r="H392" s="30" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="I392" s="31" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A393" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B393" s="29">
+        <v>46317</v>
+      </c>
+      <c r="C393" s="29">
+        <v>46317</v>
+      </c>
+      <c r="D393" s="29">
+        <v>46377</v>
+      </c>
+      <c r="E393" s="28" t="s">
+        <v>770</v>
+      </c>
+      <c r="F393" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G393" s="30">
+        <v>107</v>
+      </c>
+      <c r="H393" s="30" t="s">
+        <v>771</v>
+      </c>
+      <c r="I393" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A394" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B394" s="29">
+        <v>46317</v>
+      </c>
+      <c r="C394" s="29">
+        <v>46317</v>
+      </c>
+      <c r="D394" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E394" s="28" t="s">
+        <v>772</v>
+      </c>
+      <c r="F394" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G394" s="30">
+        <v>67</v>
+      </c>
+      <c r="H394" s="30" t="s">
+        <v>773</v>
+      </c>
+      <c r="I394" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A395" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B395" s="29">
+        <v>46296</v>
+      </c>
+      <c r="C395" s="29">
+        <v>46317</v>
+      </c>
+      <c r="D395" s="29">
+        <v>46373</v>
+      </c>
+      <c r="E395" s="28" t="s">
+        <v>774</v>
+      </c>
+      <c r="F395" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G395" s="30">
+        <v>875</v>
+      </c>
+      <c r="H395" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="I395" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A396" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B396" s="29">
+        <v>46318</v>
+      </c>
+      <c r="C396" s="29">
+        <v>46318</v>
+      </c>
+      <c r="D396" s="29">
+        <v>46378</v>
+      </c>
+      <c r="E396" s="28" t="s">
+        <v>775</v>
+      </c>
+      <c r="F396" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G396" s="30">
+        <v>64</v>
+      </c>
+      <c r="H396" s="30" t="s">
+        <v>776</v>
+      </c>
+      <c r="I396" s="31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A397" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B397" s="29">
+        <v>46318</v>
+      </c>
+      <c r="C397" s="29">
+        <v>46318</v>
+      </c>
+      <c r="D397" s="29">
+        <v>46390</v>
+      </c>
+      <c r="E397" s="28" t="s">
+        <v>777</v>
+      </c>
+      <c r="F397" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G397" s="30">
+        <v>77</v>
+      </c>
+      <c r="H397" s="30" t="s">
+        <v>778</v>
+      </c>
+      <c r="I397" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A398" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B398" s="29">
+        <v>46320</v>
+      </c>
+      <c r="C398" s="29">
+        <v>46321</v>
+      </c>
+      <c r="D398" s="29">
+        <v>46444</v>
+      </c>
+      <c r="E398" s="28" t="s">
+        <v>779</v>
+      </c>
+      <c r="F398" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G398" s="30">
+        <v>90</v>
+      </c>
+      <c r="H398" s="30" t="s">
+        <v>780</v>
+      </c>
+      <c r="I398" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A399" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B399" s="29">
+        <v>46321</v>
+      </c>
+      <c r="C399" s="29">
+        <v>46321</v>
+      </c>
+      <c r="D399" s="29">
+        <v>46341</v>
+      </c>
+      <c r="E399" s="28" t="s">
+        <v>781</v>
+      </c>
+      <c r="F399" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G399" s="30">
+        <v>49</v>
+      </c>
+      <c r="H399" s="30" t="s">
+        <v>782</v>
+      </c>
+      <c r="I399" s="31" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -15544,7 +15786,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I392</xm:sqref>
+          <xm:sqref>I3:I399</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -15665,7 +15907,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="E1"/>
     </row>
@@ -16080,7 +16322,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{177B7A0E-FF32-4156-AD26-40F8A8D9C534}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06AAF0C6-DE3D-476D-9B1D-F81EEFA6A2CB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -16099,7 +16341,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F132A3CF-F853-4244-80FB-C7965FFC7437}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CABCB53B-22C4-40C0-95FE-544F4A875480}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -16107,18 +16349,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B30A08B-9F6D-4095-B44F-A85D48EE2410}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFF7ECC-0EEC-4B7B-ADE7-60BC8E4EAFF1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46201A9A-59F8-4028-AF33-2BE8FF906E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A42485FE-752A-45F7-9928-3A53A1E2F048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="796">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2435,6 +2435,45 @@
     <t>970 E Continental  Tulare CA 93274</t>
   </si>
   <si>
+    <t>Georg Fischer Signet LLC</t>
+  </si>
+  <si>
+    <t>5462 North Irwindale Avenue  Baldwin Park CA 91706</t>
+  </si>
+  <si>
+    <t>Intel Corporation</t>
+  </si>
+  <si>
+    <t>1900 Prairie City Road  Folsom CA 95630</t>
+  </si>
+  <si>
+    <t>24Hr Homecare</t>
+  </si>
+  <si>
+    <t>Conduent State &amp; Local Solutions, Inc.</t>
+  </si>
+  <si>
+    <t>375 Beale Street  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>The Madrona</t>
+  </si>
+  <si>
+    <t>1001 Westside Road  Healdsburg CA 95448</t>
+  </si>
+  <si>
+    <t>Everidge Inc.</t>
+  </si>
+  <si>
+    <t>8886 White Oak Ave  Rancho Cucamonga CA 91730</t>
+  </si>
+  <si>
+    <t>Tawa, Inc. dba 99 Ranch Market</t>
+  </si>
+  <si>
+    <t>4024 Grand Avenue  Chino CA 91710</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2454,7 +2493,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 10/26/2026
+01/01/2023 - 10/28/2026
 </t>
     </r>
     <r>
@@ -2468,43 +2507,40 @@
     </r>
   </si>
   <si>
-    <t>Georg Fischer Signet LLC</t>
-  </si>
-  <si>
-    <t>5462 North Irwindale Avenue  Baldwin Park CA 91706</t>
-  </si>
-  <si>
-    <t>Intel Corporation</t>
-  </si>
-  <si>
-    <t>1900 Prairie City Road  Folsom CA 95630</t>
-  </si>
-  <si>
-    <t>24Hr Homecare</t>
-  </si>
-  <si>
-    <t>Conduent State &amp; Local Solutions, Inc.</t>
-  </si>
-  <si>
-    <t>375 Beale Street  San Francisco CA 94105</t>
-  </si>
-  <si>
-    <t>The Madrona</t>
-  </si>
-  <si>
-    <t>1001 Westside Road  Healdsburg CA 95448</t>
-  </si>
-  <si>
-    <t>Everidge Inc.</t>
-  </si>
-  <si>
-    <t>8886 White Oak Ave  Rancho Cucamonga CA 91730</t>
-  </si>
-  <si>
-    <t>Tawa, Inc. dba 99 Ranch Market</t>
-  </si>
-  <si>
-    <t>4024 Grand Avenue  Chino CA 91710</t>
+    <t>4299 Rosewood Drive  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>Frontapp, Inc.</t>
+  </si>
+  <si>
+    <t>One Montgomery Street, Suite 1300  San Francisco CA 94104</t>
+  </si>
+  <si>
+    <t>Walt Disney Parks &amp; Resorts US, Inc.</t>
+  </si>
+  <si>
+    <t>1401 Flower Street  Glendale CA 91201</t>
+  </si>
+  <si>
+    <t>Levy</t>
+  </si>
+  <si>
+    <t>7000 S Coliseum Way  Oakland CA 94621</t>
+  </si>
+  <si>
+    <t>Artiva Biotherapeutics, Inc.</t>
+  </si>
+  <si>
+    <t>5505 Morehouse Drive, Suite 100  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>Dropbox, Inc.</t>
+  </si>
+  <si>
+    <t>50 Hawthorne Street  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>24 Hr Homecare</t>
   </si>
   <si>
     <r>
@@ -2518,7 +2554,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 10/26/2026</t>
+      <t>07/01/26 to 10/28/2026</t>
     </r>
     <r>
       <rPr>
@@ -2538,7 +2574,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I399.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I406.</t>
     </r>
   </si>
 </sst>
@@ -3720,8 +3756,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I399" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I399" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I406" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I406" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I399">
     <sortCondition ref="C2:C399"/>
   </sortState>
@@ -4142,7 +4178,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>22591</v>
+        <v>23240</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4151,7 +4187,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4178,7 +4214,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4210,7 +4246,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I399"/>
+  <dimension ref="A1:I406"/>
   <sheetFormatPr defaultColWidth="150.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -4226,7 +4262,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -15583,7 +15619,7 @@
         <v>46377</v>
       </c>
       <c r="E393" s="28" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F393" s="28" t="s">
         <v>101</v>
@@ -15592,7 +15628,7 @@
         <v>107</v>
       </c>
       <c r="H393" s="30" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="I393" s="31" t="s">
         <v>34</v>
@@ -15612,7 +15648,7 @@
         <v>46326</v>
       </c>
       <c r="E394" s="28" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F394" s="28" t="s">
         <v>6</v>
@@ -15621,7 +15657,7 @@
         <v>67</v>
       </c>
       <c r="H394" s="30" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="I394" s="31" t="s">
         <v>34</v>
@@ -15641,7 +15677,7 @@
         <v>46373</v>
       </c>
       <c r="E395" s="28" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F395" s="28" t="s">
         <v>6</v>
@@ -15670,7 +15706,7 @@
         <v>46378</v>
       </c>
       <c r="E396" s="28" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F396" s="28" t="s">
         <v>6</v>
@@ -15679,7 +15715,7 @@
         <v>64</v>
       </c>
       <c r="H396" s="30" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="I396" s="31" t="s">
         <v>41</v>
@@ -15699,7 +15735,7 @@
         <v>46390</v>
       </c>
       <c r="E397" s="28" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F397" s="28" t="s">
         <v>101</v>
@@ -15708,7 +15744,7 @@
         <v>77</v>
       </c>
       <c r="H397" s="30" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="I397" s="31" t="s">
         <v>47</v>
@@ -15728,7 +15764,7 @@
         <v>46444</v>
       </c>
       <c r="E398" s="28" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F398" s="28" t="s">
         <v>52</v>
@@ -15737,7 +15773,7 @@
         <v>90</v>
       </c>
       <c r="H398" s="30" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="I398" s="31" t="s">
         <v>34</v>
@@ -15757,7 +15793,7 @@
         <v>46341</v>
       </c>
       <c r="E399" s="28" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F399" s="28" t="s">
         <v>52</v>
@@ -15766,10 +15802,213 @@
         <v>49</v>
       </c>
       <c r="H399" s="30" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="I399" s="31" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A400" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B400" s="29">
+        <v>46321</v>
+      </c>
+      <c r="C400" s="29">
+        <v>46322</v>
+      </c>
+      <c r="D400" s="29">
+        <v>46361</v>
+      </c>
+      <c r="E400" s="28" t="s">
+        <v>780</v>
+      </c>
+      <c r="F400" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G400" s="30">
+        <v>54</v>
+      </c>
+      <c r="H400" s="30" t="s">
+        <v>783</v>
+      </c>
+      <c r="I400" s="31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A401" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B401" s="29">
+        <v>46322</v>
+      </c>
+      <c r="C401" s="29">
+        <v>46322</v>
+      </c>
+      <c r="D401" s="29">
+        <v>46322</v>
+      </c>
+      <c r="E401" s="28" t="s">
+        <v>784</v>
+      </c>
+      <c r="F401" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G401" s="30">
+        <v>53</v>
+      </c>
+      <c r="H401" s="30" t="s">
+        <v>785</v>
+      </c>
+      <c r="I401" s="31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A402" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B402" s="29">
+        <v>46322</v>
+      </c>
+      <c r="C402" s="29">
+        <v>46322</v>
+      </c>
+      <c r="D402" s="29">
+        <v>46385</v>
+      </c>
+      <c r="E402" s="28" t="s">
+        <v>786</v>
+      </c>
+      <c r="F402" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G402" s="30">
+        <v>159</v>
+      </c>
+      <c r="H402" s="30" t="s">
+        <v>787</v>
+      </c>
+      <c r="I402" s="31" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A403" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B403" s="29">
+        <v>46321</v>
+      </c>
+      <c r="C403" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D403" s="29">
+        <v>46387</v>
+      </c>
+      <c r="E403" s="28" t="s">
+        <v>788</v>
+      </c>
+      <c r="F403" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G403" s="30">
+        <v>181</v>
+      </c>
+      <c r="H403" s="30" t="s">
+        <v>789</v>
+      </c>
+      <c r="I403" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A404" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B404" s="29">
+        <v>46322</v>
+      </c>
+      <c r="C404" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D404" s="29">
+        <v>46387</v>
+      </c>
+      <c r="E404" s="28" t="s">
+        <v>790</v>
+      </c>
+      <c r="F404" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G404" s="30">
+        <v>131</v>
+      </c>
+      <c r="H404" s="30" t="s">
+        <v>791</v>
+      </c>
+      <c r="I404" s="31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A405" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B405" s="29">
+        <v>46323</v>
+      </c>
+      <c r="C405" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D405" s="29">
+        <v>46344</v>
+      </c>
+      <c r="E405" s="28" t="s">
+        <v>792</v>
+      </c>
+      <c r="F405" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G405" s="30">
+        <v>57</v>
+      </c>
+      <c r="H405" s="30" t="s">
+        <v>793</v>
+      </c>
+      <c r="I405" s="31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A406" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B406" s="29">
+        <v>46323</v>
+      </c>
+      <c r="C406" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D406" s="29">
+        <v>46388</v>
+      </c>
+      <c r="E406" s="28" t="s">
+        <v>794</v>
+      </c>
+      <c r="F406" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G406" s="30">
+        <v>14</v>
+      </c>
+      <c r="H406" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="I406" s="31" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -15786,7 +16025,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I399</xm:sqref>
+          <xm:sqref>I3:I406</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -15907,7 +16146,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>769</v>
+        <v>782</v>
       </c>
       <c r="E1"/>
     </row>
@@ -16322,7 +16561,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06AAF0C6-DE3D-476D-9B1D-F81EEFA6A2CB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87E374AB-C302-426A-962E-8F6AA4A44C39}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -16341,7 +16580,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CABCB53B-22C4-40C0-95FE-544F4A875480}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5906BE0B-8873-41DD-ABB1-29AA0AF4902E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -16349,18 +16588,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFF7ECC-0EEC-4B7B-ADE7-60BC8E4EAFF1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C4E6149-676B-4118-B2C4-FCABD412CE0D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
